--- a/Журнал.xlsx
+++ b/Журнал.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mallb\Documents\GitHub\26-27-IT-Support-Labs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B1A7B6-4830-454D-A985-F5F97276245F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-семестр" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1095,7 +1101,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
@@ -1442,7 +1448,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1475,9 +1481,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1510,6 +1533,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -1685,7 +1725,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
@@ -1995,7 +2035,9 @@
       <c r="V9" s="13">
         <v>0</v>
       </c>
-      <c r="W9" s="4"/>
+      <c r="W9" s="13">
+        <v>0</v>
+      </c>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
@@ -2040,7 +2082,9 @@
       <c r="V10" s="12">
         <v>3</v>
       </c>
-      <c r="W10" s="7"/>
+      <c r="W10" s="12">
+        <v>2</v>
+      </c>
       <c r="X10" s="7"/>
       <c r="Y10" s="7"/>
       <c r="Z10" s="7"/>
@@ -2085,7 +2129,9 @@
       <c r="V11" s="12">
         <v>0</v>
       </c>
-      <c r="W11" s="7"/>
+      <c r="W11" s="12">
+        <v>0</v>
+      </c>
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
       <c r="Z11" s="7"/>
@@ -2130,7 +2176,9 @@
       <c r="V12" s="12">
         <v>3</v>
       </c>
-      <c r="W12" s="7"/>
+      <c r="W12" s="12">
+        <v>3</v>
+      </c>
       <c r="X12" s="7"/>
       <c r="Y12" s="7"/>
       <c r="Z12" s="7"/>
@@ -2175,7 +2223,9 @@
       <c r="V13" s="12">
         <v>0</v>
       </c>
-      <c r="W13" s="7"/>
+      <c r="W13" s="12">
+        <v>0</v>
+      </c>
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
       <c r="Z13" s="7"/>
@@ -2220,7 +2270,9 @@
       <c r="V14" s="12">
         <v>3</v>
       </c>
-      <c r="W14" s="7"/>
+      <c r="W14" s="12">
+        <v>3</v>
+      </c>
       <c r="X14" s="7"/>
       <c r="Y14" s="7"/>
       <c r="Z14" s="7"/>
@@ -2265,7 +2317,9 @@
       <c r="V15" s="12">
         <v>3</v>
       </c>
-      <c r="W15" s="7"/>
+      <c r="W15" s="12">
+        <v>3</v>
+      </c>
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
       <c r="Z15" s="7"/>
@@ -2310,7 +2364,9 @@
       <c r="V16" s="12">
         <v>3</v>
       </c>
-      <c r="W16" s="7"/>
+      <c r="W16" s="12">
+        <v>3</v>
+      </c>
       <c r="X16" s="7"/>
       <c r="Y16" s="7"/>
       <c r="Z16" s="7"/>
@@ -2355,7 +2411,9 @@
       <c r="V17" s="12">
         <v>0</v>
       </c>
-      <c r="W17" s="7"/>
+      <c r="W17" s="12">
+        <v>0</v>
+      </c>
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
       <c r="Z17" s="7"/>
@@ -2400,7 +2458,9 @@
       <c r="V18" s="12">
         <v>0</v>
       </c>
-      <c r="W18" s="7"/>
+      <c r="W18" s="12">
+        <v>0</v>
+      </c>
       <c r="X18" s="7"/>
       <c r="Y18" s="7"/>
       <c r="Z18" s="7"/>
@@ -2445,7 +2505,9 @@
       <c r="V19" s="12">
         <v>3</v>
       </c>
-      <c r="W19" s="7"/>
+      <c r="W19" s="12">
+        <v>3</v>
+      </c>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="7"/>
@@ -2490,7 +2552,9 @@
       <c r="V20" s="12">
         <v>0</v>
       </c>
-      <c r="W20" s="7"/>
+      <c r="W20" s="12">
+        <v>0</v>
+      </c>
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
       <c r="Z20" s="7"/>
@@ -2535,7 +2599,9 @@
       <c r="V21" s="12">
         <v>3</v>
       </c>
-      <c r="W21" s="7"/>
+      <c r="W21" s="12">
+        <v>3</v>
+      </c>
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
       <c r="Z21" s="7"/>
@@ -2580,7 +2646,9 @@
       <c r="V22" s="12">
         <v>0</v>
       </c>
-      <c r="W22" s="7"/>
+      <c r="W22" s="12">
+        <v>0</v>
+      </c>
       <c r="X22" s="7"/>
       <c r="Y22" s="7"/>
       <c r="Z22" s="7"/>
@@ -2625,7 +2693,9 @@
       <c r="V23" s="12">
         <v>3</v>
       </c>
-      <c r="W23" s="7"/>
+      <c r="W23" s="12">
+        <v>3</v>
+      </c>
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="7"/>
@@ -2670,7 +2740,9 @@
       <c r="V24" s="12">
         <v>3</v>
       </c>
-      <c r="W24" s="7"/>
+      <c r="W24" s="12">
+        <v>3</v>
+      </c>
       <c r="X24" s="7"/>
       <c r="Y24" s="7"/>
       <c r="Z24" s="7"/>
@@ -2715,7 +2787,9 @@
       <c r="V25" s="12">
         <v>2</v>
       </c>
-      <c r="W25" s="7"/>
+      <c r="W25" s="12">
+        <v>0</v>
+      </c>
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
       <c r="Z25" s="7"/>
@@ -2760,7 +2834,9 @@
       <c r="V26" s="12">
         <v>0</v>
       </c>
-      <c r="W26" s="7"/>
+      <c r="W26" s="12">
+        <v>0</v>
+      </c>
       <c r="X26" s="7"/>
       <c r="Y26" s="7"/>
       <c r="Z26" s="7"/>
@@ -2805,7 +2881,9 @@
       <c r="V27" s="12">
         <v>1</v>
       </c>
-      <c r="W27" s="7"/>
+      <c r="W27" s="12">
+        <v>3</v>
+      </c>
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
       <c r="Z27" s="7"/>
@@ -2850,7 +2928,9 @@
       <c r="V28" s="12">
         <v>3</v>
       </c>
-      <c r="W28" s="7"/>
+      <c r="W28" s="12">
+        <v>3</v>
+      </c>
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
       <c r="Z28" s="7"/>
@@ -2895,7 +2975,9 @@
       <c r="V29" s="12">
         <v>2</v>
       </c>
-      <c r="W29" s="7"/>
+      <c r="W29" s="12">
+        <v>0</v>
+      </c>
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="7"/>
@@ -2940,7 +3022,9 @@
       <c r="V30" s="12">
         <v>0</v>
       </c>
-      <c r="W30" s="7"/>
+      <c r="W30" s="12">
+        <v>0</v>
+      </c>
       <c r="X30" s="7"/>
       <c r="Y30" s="7"/>
       <c r="Z30" s="7"/>
@@ -2985,7 +3069,9 @@
       <c r="V31" s="12">
         <v>3</v>
       </c>
-      <c r="W31" s="7"/>
+      <c r="W31" s="12">
+        <v>0</v>
+      </c>
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
       <c r="Z31" s="7"/>
@@ -3030,7 +3116,9 @@
       <c r="V32" s="12">
         <v>0</v>
       </c>
-      <c r="W32" s="7"/>
+      <c r="W32" s="12">
+        <v>0</v>
+      </c>
       <c r="X32" s="7"/>
       <c r="Y32" s="7"/>
       <c r="Z32" s="7"/>
@@ -3075,7 +3163,9 @@
       <c r="V33" s="12">
         <v>3</v>
       </c>
-      <c r="W33" s="7"/>
+      <c r="W33" s="12">
+        <v>3</v>
+      </c>
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="7"/>
@@ -3251,7 +3341,9 @@
       <c r="V37" s="13">
         <v>0</v>
       </c>
-      <c r="W37" s="4"/>
+      <c r="W37" s="13">
+        <v>0</v>
+      </c>
       <c r="X37" s="4"/>
       <c r="Y37" s="4"/>
       <c r="Z37" s="4"/>
@@ -3296,7 +3388,9 @@
       <c r="V38" s="13">
         <v>0</v>
       </c>
-      <c r="W38" s="7"/>
+      <c r="W38" s="12">
+        <v>0</v>
+      </c>
       <c r="X38" s="7"/>
       <c r="Y38" s="7"/>
       <c r="Z38" s="7"/>
@@ -3341,7 +3435,9 @@
       <c r="V39" s="13">
         <v>0</v>
       </c>
-      <c r="W39" s="7"/>
+      <c r="W39" s="12">
+        <v>0</v>
+      </c>
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="7"/>
@@ -3386,7 +3482,9 @@
       <c r="V40" s="13">
         <v>0</v>
       </c>
-      <c r="W40" s="7"/>
+      <c r="W40" s="12">
+        <v>0</v>
+      </c>
       <c r="X40" s="7"/>
       <c r="Y40" s="7"/>
       <c r="Z40" s="7"/>
@@ -3431,7 +3529,9 @@
       <c r="V41" s="13">
         <v>0</v>
       </c>
-      <c r="W41" s="7"/>
+      <c r="W41" s="12">
+        <v>0</v>
+      </c>
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="7"/>
@@ -3476,7 +3576,9 @@
       <c r="V42" s="13">
         <v>0</v>
       </c>
-      <c r="W42" s="7"/>
+      <c r="W42" s="12">
+        <v>0</v>
+      </c>
       <c r="X42" s="7"/>
       <c r="Y42" s="7"/>
       <c r="Z42" s="7"/>
@@ -3521,7 +3623,9 @@
       <c r="V43" s="13">
         <v>0</v>
       </c>
-      <c r="W43" s="7"/>
+      <c r="W43" s="12">
+        <v>0</v>
+      </c>
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
       <c r="Z43" s="7"/>
@@ -3566,7 +3670,9 @@
       <c r="V44" s="13">
         <v>0</v>
       </c>
-      <c r="W44" s="7"/>
+      <c r="W44" s="12">
+        <v>0</v>
+      </c>
       <c r="X44" s="7"/>
       <c r="Y44" s="7"/>
       <c r="Z44" s="7"/>
@@ -3611,7 +3717,9 @@
       <c r="V45" s="13">
         <v>0</v>
       </c>
-      <c r="W45" s="7"/>
+      <c r="W45" s="12">
+        <v>0</v>
+      </c>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
       <c r="Z45" s="7"/>
@@ -3656,7 +3764,9 @@
       <c r="V46" s="12">
         <v>2</v>
       </c>
-      <c r="W46" s="7"/>
+      <c r="W46" s="12">
+        <v>0</v>
+      </c>
       <c r="X46" s="7"/>
       <c r="Y46" s="7"/>
       <c r="Z46" s="7"/>
@@ -3701,7 +3811,9 @@
       <c r="V47" s="12">
         <v>0</v>
       </c>
-      <c r="W47" s="7"/>
+      <c r="W47" s="12">
+        <v>0</v>
+      </c>
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
       <c r="Z47" s="7"/>
@@ -3746,7 +3858,9 @@
       <c r="V48" s="12">
         <v>0</v>
       </c>
-      <c r="W48" s="7"/>
+      <c r="W48" s="12">
+        <v>0</v>
+      </c>
       <c r="X48" s="7"/>
       <c r="Y48" s="7"/>
       <c r="Z48" s="7"/>
@@ -3791,7 +3905,9 @@
       <c r="V49" s="12">
         <v>3</v>
       </c>
-      <c r="W49" s="7"/>
+      <c r="W49" s="12">
+        <v>3</v>
+      </c>
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
       <c r="Z49" s="7"/>
@@ -3836,7 +3952,9 @@
       <c r="V50" s="12">
         <v>0</v>
       </c>
-      <c r="W50" s="7"/>
+      <c r="W50" s="12">
+        <v>0</v>
+      </c>
       <c r="X50" s="7"/>
       <c r="Y50" s="7"/>
       <c r="Z50" s="7"/>
@@ -3881,7 +3999,9 @@
       <c r="V51" s="12">
         <v>0</v>
       </c>
-      <c r="W51" s="7"/>
+      <c r="W51" s="12">
+        <v>0</v>
+      </c>
       <c r="X51" s="7"/>
       <c r="Y51" s="7"/>
       <c r="Z51" s="7"/>
@@ -3926,7 +4046,9 @@
       <c r="V52" s="12">
         <v>0</v>
       </c>
-      <c r="W52" s="7"/>
+      <c r="W52" s="12">
+        <v>0</v>
+      </c>
       <c r="X52" s="7"/>
       <c r="Y52" s="7"/>
       <c r="Z52" s="7"/>
@@ -3971,7 +4093,9 @@
       <c r="V53" s="12">
         <v>2</v>
       </c>
-      <c r="W53" s="7"/>
+      <c r="W53" s="12">
+        <v>1</v>
+      </c>
       <c r="X53" s="7"/>
       <c r="Y53" s="7"/>
       <c r="Z53" s="7"/>
@@ -4016,7 +4140,9 @@
       <c r="V54" s="12">
         <v>0</v>
       </c>
-      <c r="W54" s="7"/>
+      <c r="W54" s="12">
+        <v>0</v>
+      </c>
       <c r="X54" s="7"/>
       <c r="Y54" s="7"/>
       <c r="Z54" s="7"/>
@@ -4061,7 +4187,9 @@
       <c r="V55" s="12">
         <v>0</v>
       </c>
-      <c r="W55" s="7"/>
+      <c r="W55" s="12">
+        <v>0</v>
+      </c>
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
       <c r="Z55" s="7"/>
@@ -4106,7 +4234,9 @@
       <c r="V56" s="12">
         <v>0</v>
       </c>
-      <c r="W56" s="7"/>
+      <c r="W56" s="12">
+        <v>0</v>
+      </c>
       <c r="X56" s="7"/>
       <c r="Y56" s="7"/>
       <c r="Z56" s="7"/>
@@ -4151,7 +4281,9 @@
       <c r="V57" s="12">
         <v>0</v>
       </c>
-      <c r="W57" s="7"/>
+      <c r="W57" s="12">
+        <v>0</v>
+      </c>
       <c r="X57" s="7"/>
       <c r="Y57" s="7"/>
       <c r="Z57" s="7"/>
@@ -4196,7 +4328,9 @@
       <c r="V58" s="12">
         <v>0</v>
       </c>
-      <c r="W58" s="7"/>
+      <c r="W58" s="12">
+        <v>0</v>
+      </c>
       <c r="X58" s="7"/>
       <c r="Y58" s="7"/>
       <c r="Z58" s="7"/>
@@ -4241,7 +4375,9 @@
       <c r="V59" s="12">
         <v>0</v>
       </c>
-      <c r="W59" s="7"/>
+      <c r="W59" s="12">
+        <v>0</v>
+      </c>
       <c r="X59" s="7"/>
       <c r="Y59" s="7"/>
       <c r="Z59" s="7"/>
@@ -4286,7 +4422,9 @@
       <c r="V60" s="12">
         <v>0</v>
       </c>
-      <c r="W60" s="7"/>
+      <c r="W60" s="12">
+        <v>0</v>
+      </c>
       <c r="X60" s="7"/>
       <c r="Y60" s="7"/>
       <c r="Z60" s="7"/>
@@ -4331,7 +4469,9 @@
       <c r="V61" s="12">
         <v>2</v>
       </c>
-      <c r="W61" s="7"/>
+      <c r="W61" s="12">
+        <v>0</v>
+      </c>
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
       <c r="Z61" s="7"/>
@@ -4376,7 +4516,9 @@
       <c r="V62" s="12">
         <v>3</v>
       </c>
-      <c r="W62" s="7"/>
+      <c r="W62" s="12">
+        <v>3</v>
+      </c>
       <c r="X62" s="7"/>
       <c r="Y62" s="7"/>
       <c r="Z62" s="7"/>
@@ -4421,7 +4563,9 @@
       <c r="V63" s="12">
         <v>0</v>
       </c>
-      <c r="W63" s="7"/>
+      <c r="W63" s="12">
+        <v>0</v>
+      </c>
       <c r="X63" s="7"/>
       <c r="Y63" s="7"/>
       <c r="Z63" s="7"/>
@@ -4466,7 +4610,9 @@
       <c r="V64" s="12">
         <v>0</v>
       </c>
-      <c r="W64" s="7"/>
+      <c r="W64" s="12">
+        <v>0</v>
+      </c>
       <c r="X64" s="7"/>
       <c r="Y64" s="7"/>
       <c r="Z64" s="7"/>
@@ -4511,7 +4657,9 @@
       <c r="V65" s="12">
         <v>0</v>
       </c>
-      <c r="W65" s="7"/>
+      <c r="W65" s="12">
+        <v>0</v>
+      </c>
       <c r="X65" s="7"/>
       <c r="Y65" s="7"/>
       <c r="Z65" s="7"/>
@@ -4556,7 +4704,9 @@
       <c r="V66" s="12">
         <v>0</v>
       </c>
-      <c r="W66" s="7"/>
+      <c r="W66" s="12">
+        <v>0</v>
+      </c>
       <c r="X66" s="7"/>
       <c r="Y66" s="7"/>
       <c r="Z66" s="7"/>
@@ -4734,7 +4884,9 @@
       <c r="V70" s="13">
         <v>0</v>
       </c>
-      <c r="W70" s="4"/>
+      <c r="W70" s="13">
+        <v>0</v>
+      </c>
       <c r="X70" s="4"/>
       <c r="Y70" s="4"/>
       <c r="Z70" s="4"/>
@@ -4779,7 +4931,9 @@
       <c r="V71" s="12">
         <v>2</v>
       </c>
-      <c r="W71" s="7"/>
+      <c r="W71" s="12">
+        <v>3</v>
+      </c>
       <c r="X71" s="7"/>
       <c r="Y71" s="7"/>
       <c r="Z71" s="7"/>
@@ -4824,7 +4978,9 @@
       <c r="V72" s="12">
         <v>2</v>
       </c>
-      <c r="W72" s="7"/>
+      <c r="W72" s="12">
+        <v>3</v>
+      </c>
       <c r="X72" s="7"/>
       <c r="Y72" s="7"/>
       <c r="Z72" s="7"/>
@@ -4869,7 +5025,9 @@
       <c r="V73" s="12">
         <v>2</v>
       </c>
-      <c r="W73" s="7"/>
+      <c r="W73" s="12">
+        <v>0</v>
+      </c>
       <c r="X73" s="7"/>
       <c r="Y73" s="7"/>
       <c r="Z73" s="7"/>
@@ -4914,7 +5072,9 @@
       <c r="V74" s="12">
         <v>0</v>
       </c>
-      <c r="W74" s="7"/>
+      <c r="W74" s="12">
+        <v>0</v>
+      </c>
       <c r="X74" s="7"/>
       <c r="Y74" s="7"/>
       <c r="Z74" s="7"/>
@@ -4959,7 +5119,9 @@
       <c r="V75" s="12">
         <v>0</v>
       </c>
-      <c r="W75" s="7"/>
+      <c r="W75" s="12">
+        <v>0</v>
+      </c>
       <c r="X75" s="7"/>
       <c r="Y75" s="7"/>
       <c r="Z75" s="7"/>
@@ -5004,7 +5166,9 @@
       <c r="V76" s="12">
         <v>0</v>
       </c>
-      <c r="W76" s="7"/>
+      <c r="W76" s="12">
+        <v>0</v>
+      </c>
       <c r="X76" s="7"/>
       <c r="Y76" s="7"/>
       <c r="Z76" s="7"/>
@@ -5049,7 +5213,9 @@
       <c r="V77" s="12">
         <v>2</v>
       </c>
-      <c r="W77" s="7"/>
+      <c r="W77" s="12">
+        <v>0</v>
+      </c>
       <c r="X77" s="7"/>
       <c r="Y77" s="7"/>
       <c r="Z77" s="7"/>
@@ -5094,7 +5260,9 @@
       <c r="V78" s="12">
         <v>2</v>
       </c>
-      <c r="W78" s="7"/>
+      <c r="W78" s="12">
+        <v>0</v>
+      </c>
       <c r="X78" s="7"/>
       <c r="Y78" s="7"/>
       <c r="Z78" s="7"/>
@@ -5139,7 +5307,9 @@
       <c r="V79" s="12">
         <v>0</v>
       </c>
-      <c r="W79" s="7"/>
+      <c r="W79" s="12">
+        <v>0</v>
+      </c>
       <c r="X79" s="7"/>
       <c r="Y79" s="7"/>
       <c r="Z79" s="7"/>
@@ -5184,7 +5354,9 @@
       <c r="V80" s="12">
         <v>0</v>
       </c>
-      <c r="W80" s="7"/>
+      <c r="W80" s="12">
+        <v>0</v>
+      </c>
       <c r="X80" s="7"/>
       <c r="Y80" s="7"/>
       <c r="Z80" s="7"/>
@@ -5229,7 +5401,9 @@
       <c r="V81" s="12">
         <v>0</v>
       </c>
-      <c r="W81" s="7"/>
+      <c r="W81" s="12">
+        <v>0</v>
+      </c>
       <c r="X81" s="7"/>
       <c r="Y81" s="7"/>
       <c r="Z81" s="7"/>
@@ -5274,7 +5448,9 @@
       <c r="V82" s="12">
         <v>0</v>
       </c>
-      <c r="W82" s="7"/>
+      <c r="W82" s="12">
+        <v>0</v>
+      </c>
       <c r="X82" s="7"/>
       <c r="Y82" s="7"/>
       <c r="Z82" s="7"/>
@@ -5319,7 +5495,9 @@
       <c r="V83" s="12">
         <v>0</v>
       </c>
-      <c r="W83" s="7"/>
+      <c r="W83" s="12">
+        <v>0</v>
+      </c>
       <c r="X83" s="7"/>
       <c r="Y83" s="7"/>
       <c r="Z83" s="7"/>
@@ -5364,7 +5542,9 @@
       <c r="V84" s="12">
         <v>0</v>
       </c>
-      <c r="W84" s="7"/>
+      <c r="W84" s="12">
+        <v>0</v>
+      </c>
       <c r="X84" s="7"/>
       <c r="Y84" s="7"/>
       <c r="Z84" s="7"/>
@@ -5409,7 +5589,9 @@
       <c r="V85" s="12">
         <v>0</v>
       </c>
-      <c r="W85" s="7"/>
+      <c r="W85" s="12">
+        <v>0</v>
+      </c>
       <c r="X85" s="7"/>
       <c r="Y85" s="7"/>
       <c r="Z85" s="7"/>
@@ -5454,7 +5636,9 @@
       <c r="V86" s="12">
         <v>0</v>
       </c>
-      <c r="W86" s="7"/>
+      <c r="W86" s="12">
+        <v>0</v>
+      </c>
       <c r="X86" s="7"/>
       <c r="Y86" s="7"/>
       <c r="Z86" s="7"/>
@@ -5499,7 +5683,9 @@
       <c r="V87" s="12">
         <v>0</v>
       </c>
-      <c r="W87" s="7"/>
+      <c r="W87" s="12">
+        <v>0</v>
+      </c>
       <c r="X87" s="7"/>
       <c r="Y87" s="7"/>
       <c r="Z87" s="7"/>
@@ -5544,7 +5730,9 @@
       <c r="V88" s="12">
         <v>0</v>
       </c>
-      <c r="W88" s="7"/>
+      <c r="W88" s="12">
+        <v>0</v>
+      </c>
       <c r="X88" s="7"/>
       <c r="Y88" s="7"/>
       <c r="Z88" s="7"/>
@@ -5589,7 +5777,9 @@
       <c r="V89" s="12">
         <v>0</v>
       </c>
-      <c r="W89" s="7"/>
+      <c r="W89" s="12">
+        <v>0</v>
+      </c>
       <c r="X89" s="7"/>
       <c r="Y89" s="7"/>
       <c r="Z89" s="7"/>
@@ -5634,7 +5824,9 @@
       <c r="V90" s="12">
         <v>0</v>
       </c>
-      <c r="W90" s="7"/>
+      <c r="W90" s="12">
+        <v>0</v>
+      </c>
       <c r="X90" s="7"/>
       <c r="Y90" s="7"/>
       <c r="Z90" s="7"/>
@@ -5679,7 +5871,9 @@
       <c r="V91" s="12">
         <v>0</v>
       </c>
-      <c r="W91" s="7"/>
+      <c r="W91" s="12">
+        <v>0</v>
+      </c>
       <c r="X91" s="7"/>
       <c r="Y91" s="7"/>
       <c r="Z91" s="7"/>
@@ -5724,7 +5918,9 @@
       <c r="V92" s="12">
         <v>0</v>
       </c>
-      <c r="W92" s="7"/>
+      <c r="W92" s="12">
+        <v>0</v>
+      </c>
       <c r="X92" s="7"/>
       <c r="Y92" s="7"/>
       <c r="Z92" s="7"/>
@@ -5769,7 +5965,9 @@
       <c r="V93" s="12">
         <v>0</v>
       </c>
-      <c r="W93" s="7"/>
+      <c r="W93" s="12">
+        <v>0</v>
+      </c>
       <c r="X93" s="7"/>
       <c r="Y93" s="7"/>
       <c r="Z93" s="7"/>
@@ -5814,7 +6012,9 @@
       <c r="V94" s="12">
         <v>0</v>
       </c>
-      <c r="W94" s="7"/>
+      <c r="W94" s="12">
+        <v>0</v>
+      </c>
       <c r="X94" s="7"/>
       <c r="Y94" s="7"/>
       <c r="Z94" s="7"/>
@@ -5859,7 +6059,9 @@
       <c r="V95" s="12">
         <v>0</v>
       </c>
-      <c r="W95" s="7"/>
+      <c r="W95" s="12">
+        <v>0</v>
+      </c>
       <c r="X95" s="7"/>
       <c r="Y95" s="7"/>
       <c r="Z95" s="7"/>
@@ -5904,7 +6106,9 @@
       <c r="V96" s="12">
         <v>0</v>
       </c>
-      <c r="W96" s="7"/>
+      <c r="W96" s="12">
+        <v>0</v>
+      </c>
       <c r="X96" s="7"/>
       <c r="Y96" s="7"/>
       <c r="Z96" s="7"/>
@@ -5949,7 +6153,9 @@
       <c r="V97" s="12">
         <v>0</v>
       </c>
-      <c r="W97" s="7"/>
+      <c r="W97" s="12">
+        <v>0</v>
+      </c>
       <c r="X97" s="7"/>
       <c r="Y97" s="7"/>
       <c r="Z97" s="7"/>
@@ -5994,7 +6200,9 @@
       <c r="V98" s="12">
         <v>0</v>
       </c>
-      <c r="W98" s="7"/>
+      <c r="W98" s="12">
+        <v>0</v>
+      </c>
       <c r="X98" s="7"/>
       <c r="Y98" s="7"/>
       <c r="Z98" s="7"/>
@@ -6039,7 +6247,9 @@
       <c r="V99" s="12">
         <v>0</v>
       </c>
-      <c r="W99" s="7"/>
+      <c r="W99" s="12">
+        <v>0</v>
+      </c>
       <c r="X99" s="7"/>
       <c r="Y99" s="7"/>
       <c r="Z99" s="7"/>
@@ -6216,7 +6426,9 @@
       <c r="V103" s="13">
         <v>3</v>
       </c>
-      <c r="W103" s="4"/>
+      <c r="W103" s="13">
+        <v>0</v>
+      </c>
       <c r="X103" s="4"/>
       <c r="Y103" s="4"/>
       <c r="Z103" s="4"/>
@@ -6261,7 +6473,9 @@
       <c r="V104" s="12">
         <v>0</v>
       </c>
-      <c r="W104" s="7"/>
+      <c r="W104" s="12">
+        <v>0</v>
+      </c>
       <c r="X104" s="7"/>
       <c r="Y104" s="7"/>
       <c r="Z104" s="7"/>
@@ -6306,7 +6520,9 @@
       <c r="V105" s="12">
         <v>0</v>
       </c>
-      <c r="W105" s="7"/>
+      <c r="W105" s="12">
+        <v>0</v>
+      </c>
       <c r="X105" s="7"/>
       <c r="Y105" s="7"/>
       <c r="Z105" s="7"/>
@@ -6351,7 +6567,9 @@
       <c r="V106" s="12">
         <v>0</v>
       </c>
-      <c r="W106" s="7"/>
+      <c r="W106" s="12">
+        <v>0</v>
+      </c>
       <c r="X106" s="7"/>
       <c r="Y106" s="7"/>
       <c r="Z106" s="7"/>
@@ -6396,7 +6614,9 @@
       <c r="V107" s="12">
         <v>0</v>
       </c>
-      <c r="W107" s="7"/>
+      <c r="W107" s="12">
+        <v>0</v>
+      </c>
       <c r="X107" s="7"/>
       <c r="Y107" s="7"/>
       <c r="Z107" s="7"/>
@@ -6441,7 +6661,9 @@
       <c r="V108" s="12">
         <v>3</v>
       </c>
-      <c r="W108" s="7"/>
+      <c r="W108" s="12">
+        <v>3</v>
+      </c>
       <c r="X108" s="7"/>
       <c r="Y108" s="7"/>
       <c r="Z108" s="7"/>
@@ -6486,7 +6708,9 @@
       <c r="V109" s="12">
         <v>0</v>
       </c>
-      <c r="W109" s="7"/>
+      <c r="W109" s="12">
+        <v>0</v>
+      </c>
       <c r="X109" s="7"/>
       <c r="Y109" s="7"/>
       <c r="Z109" s="7"/>
@@ -6531,7 +6755,9 @@
       <c r="V110" s="12">
         <v>3</v>
       </c>
-      <c r="W110" s="7"/>
+      <c r="W110" s="12">
+        <v>0</v>
+      </c>
       <c r="X110" s="7"/>
       <c r="Y110" s="7"/>
       <c r="Z110" s="7"/>
@@ -6576,7 +6802,9 @@
       <c r="V111" s="12">
         <v>1</v>
       </c>
-      <c r="W111" s="7"/>
+      <c r="W111" s="12">
+        <v>0</v>
+      </c>
       <c r="X111" s="7"/>
       <c r="Y111" s="7"/>
       <c r="Z111" s="7"/>
@@ -6621,7 +6849,9 @@
       <c r="V112" s="12">
         <v>0</v>
       </c>
-      <c r="W112" s="7"/>
+      <c r="W112" s="12">
+        <v>0</v>
+      </c>
       <c r="X112" s="7"/>
       <c r="Y112" s="7"/>
       <c r="Z112" s="7"/>
@@ -6666,7 +6896,9 @@
       <c r="V113" s="12">
         <v>2</v>
       </c>
-      <c r="W113" s="7"/>
+      <c r="W113" s="12">
+        <v>3</v>
+      </c>
       <c r="X113" s="7"/>
       <c r="Y113" s="7"/>
       <c r="Z113" s="7"/>
@@ -6711,7 +6943,9 @@
       <c r="V114" s="12">
         <v>0</v>
       </c>
-      <c r="W114" s="7"/>
+      <c r="W114" s="12">
+        <v>0</v>
+      </c>
       <c r="X114" s="7"/>
       <c r="Y114" s="7"/>
       <c r="Z114" s="7"/>
@@ -6756,7 +6990,9 @@
       <c r="V115" s="12">
         <v>0</v>
       </c>
-      <c r="W115" s="7"/>
+      <c r="W115" s="12">
+        <v>0</v>
+      </c>
       <c r="X115" s="7"/>
       <c r="Y115" s="7"/>
       <c r="Z115" s="7"/>
@@ -6801,7 +7037,9 @@
       <c r="V116" s="12">
         <v>0</v>
       </c>
-      <c r="W116" s="7"/>
+      <c r="W116" s="12">
+        <v>0</v>
+      </c>
       <c r="X116" s="7"/>
       <c r="Y116" s="7"/>
       <c r="Z116" s="7"/>
@@ -6846,7 +7084,9 @@
       <c r="V117" s="12">
         <v>3</v>
       </c>
-      <c r="W117" s="7"/>
+      <c r="W117" s="12">
+        <v>3</v>
+      </c>
       <c r="X117" s="7"/>
       <c r="Y117" s="7"/>
       <c r="Z117" s="7"/>
@@ -6891,7 +7131,9 @@
       <c r="V118" s="12">
         <v>3</v>
       </c>
-      <c r="W118" s="7"/>
+      <c r="W118" s="12">
+        <v>0</v>
+      </c>
       <c r="X118" s="7"/>
       <c r="Y118" s="7"/>
       <c r="Z118" s="7"/>
@@ -6936,7 +7178,9 @@
       <c r="V119" s="12">
         <v>0</v>
       </c>
-      <c r="W119" s="7"/>
+      <c r="W119" s="12">
+        <v>0</v>
+      </c>
       <c r="X119" s="7"/>
       <c r="Y119" s="7"/>
       <c r="Z119" s="7"/>
@@ -6981,7 +7225,9 @@
       <c r="V120" s="12">
         <v>0</v>
       </c>
-      <c r="W120" s="7"/>
+      <c r="W120" s="12">
+        <v>0</v>
+      </c>
       <c r="X120" s="7"/>
       <c r="Y120" s="7"/>
       <c r="Z120" s="7"/>
@@ -7026,7 +7272,9 @@
       <c r="V121" s="12">
         <v>0</v>
       </c>
-      <c r="W121" s="7"/>
+      <c r="W121" s="12">
+        <v>0</v>
+      </c>
       <c r="X121" s="7"/>
       <c r="Y121" s="7"/>
       <c r="Z121" s="7"/>
@@ -7071,7 +7319,9 @@
       <c r="V122" s="12">
         <v>0</v>
       </c>
-      <c r="W122" s="7"/>
+      <c r="W122" s="12">
+        <v>0</v>
+      </c>
       <c r="X122" s="7"/>
       <c r="Y122" s="7"/>
       <c r="Z122" s="7"/>
@@ -7116,7 +7366,9 @@
       <c r="V123" s="12">
         <v>1</v>
       </c>
-      <c r="W123" s="7"/>
+      <c r="W123" s="12">
+        <v>0</v>
+      </c>
       <c r="X123" s="7"/>
       <c r="Y123" s="7"/>
       <c r="Z123" s="7"/>
@@ -7161,7 +7413,9 @@
       <c r="V124" s="12">
         <v>0</v>
       </c>
-      <c r="W124" s="7"/>
+      <c r="W124" s="12">
+        <v>0</v>
+      </c>
       <c r="X124" s="7"/>
       <c r="Y124" s="7"/>
       <c r="Z124" s="7"/>
@@ -7206,7 +7460,9 @@
       <c r="V125" s="12">
         <v>0</v>
       </c>
-      <c r="W125" s="7"/>
+      <c r="W125" s="12">
+        <v>0</v>
+      </c>
       <c r="X125" s="7"/>
       <c r="Y125" s="7"/>
       <c r="Z125" s="7"/>
@@ -7251,7 +7507,9 @@
       <c r="V126" s="12">
         <v>0</v>
       </c>
-      <c r="W126" s="7"/>
+      <c r="W126" s="12">
+        <v>0</v>
+      </c>
       <c r="X126" s="7"/>
       <c r="Y126" s="7"/>
       <c r="Z126" s="7"/>
@@ -7296,7 +7554,9 @@
       <c r="V127" s="12">
         <v>3</v>
       </c>
-      <c r="W127" s="7"/>
+      <c r="W127" s="12">
+        <v>3</v>
+      </c>
       <c r="X127" s="7"/>
       <c r="Y127" s="7"/>
       <c r="Z127" s="7"/>
@@ -7341,7 +7601,9 @@
       <c r="V128" s="12">
         <v>0</v>
       </c>
-      <c r="W128" s="7"/>
+      <c r="W128" s="12">
+        <v>0</v>
+      </c>
       <c r="X128" s="7"/>
       <c r="Y128" s="7"/>
       <c r="Z128" s="7"/>
@@ -7386,7 +7648,9 @@
       <c r="V129" s="12">
         <v>2</v>
       </c>
-      <c r="W129" s="7"/>
+      <c r="W129" s="12">
+        <v>3</v>
+      </c>
       <c r="X129" s="7"/>
       <c r="Y129" s="7"/>
       <c r="Z129" s="7"/>
@@ -7431,7 +7695,9 @@
       <c r="V130" s="12">
         <v>0</v>
       </c>
-      <c r="W130" s="7"/>
+      <c r="W130" s="12">
+        <v>0</v>
+      </c>
       <c r="X130" s="7"/>
       <c r="Y130" s="7"/>
       <c r="Z130" s="7"/>
@@ -7476,7 +7742,9 @@
       <c r="V131" s="12">
         <v>0</v>
       </c>
-      <c r="W131" s="7"/>
+      <c r="W131" s="12">
+        <v>0</v>
+      </c>
       <c r="X131" s="7"/>
       <c r="Y131" s="7"/>
       <c r="Z131" s="7"/>
@@ -7521,7 +7789,9 @@
       <c r="V132" s="12">
         <v>0</v>
       </c>
-      <c r="W132" s="7"/>
+      <c r="W132" s="12">
+        <v>0</v>
+      </c>
       <c r="X132" s="7"/>
       <c r="Y132" s="7"/>
       <c r="Z132" s="7"/>
@@ -7698,7 +7968,9 @@
       <c r="V136" s="13">
         <v>0</v>
       </c>
-      <c r="W136" s="4"/>
+      <c r="W136" s="13">
+        <v>2</v>
+      </c>
       <c r="X136" s="4"/>
       <c r="Y136" s="4"/>
       <c r="Z136" s="4"/>
@@ -7743,7 +8015,9 @@
       <c r="V137" s="13">
         <v>0</v>
       </c>
-      <c r="W137" s="7"/>
+      <c r="W137" s="12">
+        <v>1</v>
+      </c>
       <c r="X137" s="7"/>
       <c r="Y137" s="7"/>
       <c r="Z137" s="7"/>
@@ -7788,7 +8062,9 @@
       <c r="V138" s="13">
         <v>0</v>
       </c>
-      <c r="W138" s="7"/>
+      <c r="W138" s="12">
+        <v>0</v>
+      </c>
       <c r="X138" s="7"/>
       <c r="Y138" s="7"/>
       <c r="Z138" s="7"/>
@@ -7833,7 +8109,9 @@
       <c r="V139" s="13">
         <v>0</v>
       </c>
-      <c r="W139" s="7"/>
+      <c r="W139" s="12">
+        <v>0</v>
+      </c>
       <c r="X139" s="7"/>
       <c r="Y139" s="7"/>
       <c r="Z139" s="7"/>
@@ -7878,7 +8156,9 @@
       <c r="V140" s="13">
         <v>0</v>
       </c>
-      <c r="W140" s="7"/>
+      <c r="W140" s="12">
+        <v>0</v>
+      </c>
       <c r="X140" s="7"/>
       <c r="Y140" s="7"/>
       <c r="Z140" s="7"/>
@@ -7923,7 +8203,9 @@
       <c r="V141" s="12">
         <v>3</v>
       </c>
-      <c r="W141" s="7"/>
+      <c r="W141" s="12">
+        <v>3</v>
+      </c>
       <c r="X141" s="7"/>
       <c r="Y141" s="7"/>
       <c r="Z141" s="7"/>
@@ -7968,7 +8250,9 @@
       <c r="V142" s="12">
         <v>3</v>
       </c>
-      <c r="W142" s="7"/>
+      <c r="W142" s="12">
+        <v>0</v>
+      </c>
       <c r="X142" s="7"/>
       <c r="Y142" s="7"/>
       <c r="Z142" s="7"/>
@@ -8013,7 +8297,9 @@
       <c r="V143" s="12">
         <v>0</v>
       </c>
-      <c r="W143" s="7"/>
+      <c r="W143" s="12">
+        <v>0</v>
+      </c>
       <c r="X143" s="7"/>
       <c r="Y143" s="7"/>
       <c r="Z143" s="7"/>
@@ -8058,7 +8344,9 @@
       <c r="V144" s="12">
         <v>3</v>
       </c>
-      <c r="W144" s="7"/>
+      <c r="W144" s="12">
+        <v>3</v>
+      </c>
       <c r="X144" s="7"/>
       <c r="Y144" s="7"/>
       <c r="Z144" s="7"/>
@@ -8103,7 +8391,9 @@
       <c r="V145" s="12">
         <v>0</v>
       </c>
-      <c r="W145" s="7"/>
+      <c r="W145" s="12">
+        <v>0</v>
+      </c>
       <c r="X145" s="7"/>
       <c r="Y145" s="7"/>
       <c r="Z145" s="7"/>
@@ -8148,7 +8438,9 @@
       <c r="V146" s="12">
         <v>0</v>
       </c>
-      <c r="W146" s="7"/>
+      <c r="W146" s="12">
+        <v>0</v>
+      </c>
       <c r="X146" s="7"/>
       <c r="Y146" s="7"/>
       <c r="Z146" s="7"/>
@@ -8193,7 +8485,9 @@
       <c r="V147" s="12">
         <v>3</v>
       </c>
-      <c r="W147" s="7"/>
+      <c r="W147" s="12">
+        <v>0</v>
+      </c>
       <c r="X147" s="7"/>
       <c r="Y147" s="7"/>
       <c r="Z147" s="7"/>
@@ -8238,7 +8532,9 @@
       <c r="V148" s="12">
         <v>0</v>
       </c>
-      <c r="W148" s="7"/>
+      <c r="W148" s="12">
+        <v>0</v>
+      </c>
       <c r="X148" s="7"/>
       <c r="Y148" s="7"/>
       <c r="Z148" s="7"/>
@@ -8283,7 +8579,9 @@
       <c r="V149" s="12">
         <v>3</v>
       </c>
-      <c r="W149" s="7"/>
+      <c r="W149" s="12">
+        <v>0</v>
+      </c>
       <c r="X149" s="7"/>
       <c r="Y149" s="7"/>
       <c r="Z149" s="7"/>
@@ -8328,7 +8626,9 @@
       <c r="V150" s="12">
         <v>0</v>
       </c>
-      <c r="W150" s="7"/>
+      <c r="W150" s="12">
+        <v>3</v>
+      </c>
       <c r="X150" s="7"/>
       <c r="Y150" s="7"/>
       <c r="Z150" s="7"/>
@@ -8373,7 +8673,9 @@
       <c r="V151" s="12">
         <v>2</v>
       </c>
-      <c r="W151" s="7"/>
+      <c r="W151" s="12">
+        <v>2</v>
+      </c>
       <c r="X151" s="7"/>
       <c r="Y151" s="7"/>
       <c r="Z151" s="7"/>
@@ -8418,7 +8720,9 @@
       <c r="V152" s="12">
         <v>3</v>
       </c>
-      <c r="W152" s="7"/>
+      <c r="W152" s="12">
+        <v>3</v>
+      </c>
       <c r="X152" s="7"/>
       <c r="Y152" s="7"/>
       <c r="Z152" s="7"/>
@@ -8463,7 +8767,9 @@
       <c r="V153" s="12">
         <v>0</v>
       </c>
-      <c r="W153" s="7"/>
+      <c r="W153" s="12">
+        <v>1</v>
+      </c>
       <c r="X153" s="7"/>
       <c r="Y153" s="7"/>
       <c r="Z153" s="7"/>
@@ -8508,7 +8814,9 @@
       <c r="V154" s="12">
         <v>2</v>
       </c>
-      <c r="W154" s="7"/>
+      <c r="W154" s="12">
+        <v>0</v>
+      </c>
       <c r="X154" s="7"/>
       <c r="Y154" s="7"/>
       <c r="Z154" s="7"/>
@@ -8553,7 +8861,9 @@
       <c r="V155" s="12">
         <v>3</v>
       </c>
-      <c r="W155" s="7"/>
+      <c r="W155" s="12">
+        <v>3</v>
+      </c>
       <c r="X155" s="7"/>
       <c r="Y155" s="7"/>
       <c r="Z155" s="7"/>
@@ -8598,7 +8908,9 @@
       <c r="V156" s="12">
         <v>3</v>
       </c>
-      <c r="W156" s="7"/>
+      <c r="W156" s="12">
+        <v>3</v>
+      </c>
       <c r="X156" s="7"/>
       <c r="Y156" s="7"/>
       <c r="Z156" s="7"/>
@@ -8643,7 +8955,9 @@
       <c r="V157" s="12">
         <v>0</v>
       </c>
-      <c r="W157" s="7"/>
+      <c r="W157" s="12">
+        <v>0</v>
+      </c>
       <c r="X157" s="7"/>
       <c r="Y157" s="7"/>
       <c r="Z157" s="7"/>
@@ -8688,7 +9002,9 @@
       <c r="V158" s="12">
         <v>3</v>
       </c>
-      <c r="W158" s="7"/>
+      <c r="W158" s="12">
+        <v>3</v>
+      </c>
       <c r="X158" s="7"/>
       <c r="Y158" s="7"/>
       <c r="Z158" s="7"/>
@@ -8733,7 +9049,9 @@
       <c r="V159" s="12">
         <v>0</v>
       </c>
-      <c r="W159" s="7"/>
+      <c r="W159" s="12">
+        <v>0</v>
+      </c>
       <c r="X159" s="7"/>
       <c r="Y159" s="7"/>
       <c r="Z159" s="7"/>
@@ -8778,7 +9096,9 @@
       <c r="V160" s="12">
         <v>0</v>
       </c>
-      <c r="W160" s="7"/>
+      <c r="W160" s="12">
+        <v>0</v>
+      </c>
       <c r="X160" s="7"/>
       <c r="Y160" s="7"/>
       <c r="Z160" s="7"/>
@@ -8823,7 +9143,9 @@
       <c r="V161" s="12">
         <v>0</v>
       </c>
-      <c r="W161" s="7"/>
+      <c r="W161" s="12">
+        <v>0</v>
+      </c>
       <c r="X161" s="7"/>
       <c r="Y161" s="7"/>
       <c r="Z161" s="7"/>
@@ -8868,7 +9190,9 @@
       <c r="V162" s="12">
         <v>3</v>
       </c>
-      <c r="W162" s="7"/>
+      <c r="W162" s="12">
+        <v>0</v>
+      </c>
       <c r="X162" s="7"/>
       <c r="Y162" s="7"/>
       <c r="Z162" s="7"/>
@@ -8913,7 +9237,9 @@
       <c r="V163" s="12">
         <v>3</v>
       </c>
-      <c r="W163" s="7"/>
+      <c r="W163" s="12">
+        <v>3</v>
+      </c>
       <c r="X163" s="7"/>
       <c r="Y163" s="7"/>
       <c r="Z163" s="7"/>
@@ -8958,7 +9284,9 @@
       <c r="V164" s="12">
         <v>0</v>
       </c>
-      <c r="W164" s="7"/>
+      <c r="W164" s="12">
+        <v>0</v>
+      </c>
       <c r="X164" s="7"/>
       <c r="Y164" s="7"/>
       <c r="Z164" s="7"/>
@@ -9003,7 +9331,9 @@
       <c r="V165" s="12">
         <v>3</v>
       </c>
-      <c r="W165" s="7"/>
+      <c r="W165" s="12">
+        <v>0</v>
+      </c>
       <c r="X165" s="7"/>
       <c r="Y165" s="7"/>
       <c r="Z165" s="7"/>
@@ -9181,7 +9511,9 @@
       <c r="V169" s="13">
         <v>2</v>
       </c>
-      <c r="W169" s="4"/>
+      <c r="W169" s="13">
+        <v>3</v>
+      </c>
       <c r="X169" s="4"/>
       <c r="Y169" s="4"/>
       <c r="Z169" s="4"/>
@@ -9226,7 +9558,9 @@
       <c r="V170" s="12">
         <v>0</v>
       </c>
-      <c r="W170" s="7"/>
+      <c r="W170" s="12">
+        <v>0</v>
+      </c>
       <c r="X170" s="7"/>
       <c r="Y170" s="7"/>
       <c r="Z170" s="7"/>
@@ -9271,7 +9605,9 @@
       <c r="V171" s="12">
         <v>3</v>
       </c>
-      <c r="W171" s="7"/>
+      <c r="W171" s="12">
+        <v>0</v>
+      </c>
       <c r="X171" s="7"/>
       <c r="Y171" s="7"/>
       <c r="Z171" s="7"/>
@@ -9316,7 +9652,9 @@
       <c r="V172" s="12">
         <v>3</v>
       </c>
-      <c r="W172" s="7"/>
+      <c r="W172" s="12">
+        <v>3</v>
+      </c>
       <c r="X172" s="7"/>
       <c r="Y172" s="7"/>
       <c r="Z172" s="7"/>
@@ -9361,7 +9699,9 @@
       <c r="V173" s="12">
         <v>3</v>
       </c>
-      <c r="W173" s="7"/>
+      <c r="W173" s="12">
+        <v>3</v>
+      </c>
       <c r="X173" s="7"/>
       <c r="Y173" s="7"/>
       <c r="Z173" s="7"/>
@@ -9406,7 +9746,9 @@
       <c r="V174" s="12">
         <v>3</v>
       </c>
-      <c r="W174" s="7"/>
+      <c r="W174" s="12">
+        <v>3</v>
+      </c>
       <c r="X174" s="7"/>
       <c r="Y174" s="7"/>
       <c r="Z174" s="7"/>
@@ -9451,7 +9793,9 @@
       <c r="V175" s="12">
         <v>3</v>
       </c>
-      <c r="W175" s="7"/>
+      <c r="W175" s="12">
+        <v>3</v>
+      </c>
       <c r="X175" s="7"/>
       <c r="Y175" s="7"/>
       <c r="Z175" s="7"/>
@@ -9496,7 +9840,9 @@
       <c r="V176" s="12">
         <v>3</v>
       </c>
-      <c r="W176" s="7"/>
+      <c r="W176" s="12">
+        <v>2</v>
+      </c>
       <c r="X176" s="7"/>
       <c r="Y176" s="7"/>
       <c r="Z176" s="7"/>
@@ -9541,7 +9887,9 @@
       <c r="V177" s="12">
         <v>0</v>
       </c>
-      <c r="W177" s="7"/>
+      <c r="W177" s="12">
+        <v>2</v>
+      </c>
       <c r="X177" s="7"/>
       <c r="Y177" s="7"/>
       <c r="Z177" s="7"/>
@@ -9586,7 +9934,9 @@
       <c r="V178" s="12">
         <v>0</v>
       </c>
-      <c r="W178" s="7"/>
+      <c r="W178" s="12">
+        <v>0</v>
+      </c>
       <c r="X178" s="7"/>
       <c r="Y178" s="7"/>
       <c r="Z178" s="7"/>
@@ -9631,7 +9981,9 @@
       <c r="V179" s="12">
         <v>0</v>
       </c>
-      <c r="W179" s="7"/>
+      <c r="W179" s="12">
+        <v>0</v>
+      </c>
       <c r="X179" s="7"/>
       <c r="Y179" s="7"/>
       <c r="Z179" s="7"/>
@@ -9676,7 +10028,9 @@
       <c r="V180" s="12">
         <v>2</v>
       </c>
-      <c r="W180" s="7"/>
+      <c r="W180" s="12">
+        <v>3</v>
+      </c>
       <c r="X180" s="7"/>
       <c r="Y180" s="7"/>
       <c r="Z180" s="7"/>
@@ -9721,7 +10075,9 @@
       <c r="V181" s="12">
         <v>0</v>
       </c>
-      <c r="W181" s="7"/>
+      <c r="W181" s="12">
+        <v>2</v>
+      </c>
       <c r="X181" s="7"/>
       <c r="Y181" s="7"/>
       <c r="Z181" s="7"/>
@@ -9766,7 +10122,9 @@
       <c r="V182" s="12">
         <v>3</v>
       </c>
-      <c r="W182" s="7"/>
+      <c r="W182" s="12">
+        <v>1</v>
+      </c>
       <c r="X182" s="7"/>
       <c r="Y182" s="7"/>
       <c r="Z182" s="7"/>
@@ -9811,7 +10169,9 @@
       <c r="V183" s="12">
         <v>0</v>
       </c>
-      <c r="W183" s="7"/>
+      <c r="W183" s="12">
+        <v>0</v>
+      </c>
       <c r="X183" s="7"/>
       <c r="Y183" s="7"/>
       <c r="Z183" s="7"/>
@@ -9856,7 +10216,9 @@
       <c r="V184" s="12">
         <v>0</v>
       </c>
-      <c r="W184" s="7"/>
+      <c r="W184" s="12">
+        <v>0</v>
+      </c>
       <c r="X184" s="7"/>
       <c r="Y184" s="7"/>
       <c r="Z184" s="7"/>
@@ -9901,7 +10263,9 @@
       <c r="V185" s="12">
         <v>3</v>
       </c>
-      <c r="W185" s="7"/>
+      <c r="W185" s="12">
+        <v>0</v>
+      </c>
       <c r="X185" s="7"/>
       <c r="Y185" s="7"/>
       <c r="Z185" s="7"/>
@@ -9946,7 +10310,9 @@
       <c r="V186" s="12">
         <v>3</v>
       </c>
-      <c r="W186" s="7"/>
+      <c r="W186" s="12">
+        <v>0</v>
+      </c>
       <c r="X186" s="7"/>
       <c r="Y186" s="7"/>
       <c r="Z186" s="7"/>
@@ -9991,7 +10357,9 @@
       <c r="V187" s="12">
         <v>0</v>
       </c>
-      <c r="W187" s="7"/>
+      <c r="W187" s="12">
+        <v>0</v>
+      </c>
       <c r="X187" s="7"/>
       <c r="Y187" s="7"/>
       <c r="Z187" s="7"/>
@@ -10036,7 +10404,9 @@
       <c r="V188" s="12">
         <v>0</v>
       </c>
-      <c r="W188" s="7"/>
+      <c r="W188" s="12">
+        <v>0</v>
+      </c>
       <c r="X188" s="7"/>
       <c r="Y188" s="7"/>
       <c r="Z188" s="7"/>
@@ -10081,7 +10451,9 @@
       <c r="V189" s="12">
         <v>0</v>
       </c>
-      <c r="W189" s="7"/>
+      <c r="W189" s="12">
+        <v>0</v>
+      </c>
       <c r="X189" s="7"/>
       <c r="Y189" s="7"/>
       <c r="Z189" s="7"/>
@@ -10126,7 +10498,9 @@
       <c r="V190" s="12">
         <v>0</v>
       </c>
-      <c r="W190" s="7"/>
+      <c r="W190" s="12">
+        <v>0</v>
+      </c>
       <c r="X190" s="7"/>
       <c r="Y190" s="7"/>
       <c r="Z190" s="7"/>
@@ -10171,7 +10545,9 @@
       <c r="V191" s="12">
         <v>0</v>
       </c>
-      <c r="W191" s="7"/>
+      <c r="W191" s="12">
+        <v>0</v>
+      </c>
       <c r="X191" s="7"/>
       <c r="Y191" s="7"/>
       <c r="Z191" s="7"/>
@@ -10216,7 +10592,9 @@
       <c r="V192" s="12">
         <v>0</v>
       </c>
-      <c r="W192" s="7"/>
+      <c r="W192" s="12">
+        <v>0</v>
+      </c>
       <c r="X192" s="7"/>
       <c r="Y192" s="7"/>
       <c r="Z192" s="7"/>

--- a/Журнал.xlsx
+++ b/Журнал.xlsx
@@ -1293,26 +1293,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1325,6 +1307,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1718,70 +1718,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
     </row>
     <row r="2" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30" t="s">
+      <c r="B3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="29" t="s">
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="22"/>
-      <c r="Z3" s="22"/>
-      <c r="AA3" s="22"/>
-      <c r="AB3" s="22"/>
-      <c r="AC3" s="22"/>
-      <c r="AD3" s="22"/>
-      <c r="AE3" s="22"/>
-      <c r="AF3" s="22"/>
-      <c r="AG3" s="22"/>
-      <c r="AH3" s="22"/>
-      <c r="AI3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+      <c r="Y3" s="30"/>
+      <c r="Z3" s="30"/>
+      <c r="AA3" s="30"/>
+      <c r="AB3" s="30"/>
+      <c r="AC3" s="30"/>
+      <c r="AD3" s="30"/>
+      <c r="AE3" s="30"/>
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="31"/>
     </row>
     <row r="4" spans="1:35" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4"/>
@@ -1808,28 +1808,28 @@
       <c r="V4"/>
     </row>
     <row r="5" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="31" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="31"/>
-      <c r="N5" s="31"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
-      <c r="Q5" s="31"/>
-      <c r="R5" s="31"/>
-      <c r="S5" s="31"/>
-      <c r="T5" s="31"/>
-      <c r="U5" s="31"/>
+      <c r="B5" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
       <c r="V5" s="8"/>
       <c r="W5" s="9"/>
       <c r="X5" s="9"/>
@@ -1870,28 +1870,28 @@
       <c r="V6"/>
     </row>
     <row r="7" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
       <c r="V7" s="8"/>
       <c r="W7" s="9"/>
       <c r="X7" s="9"/>
@@ -1909,26 +1909,26 @@
     </row>
     <row r="8" spans="1:35" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="27"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="28"/>
       <c r="V8" s="10">
         <v>0</v>
       </c>
@@ -2010,7 +2010,9 @@
       <c r="W9" s="13">
         <v>0</v>
       </c>
-      <c r="X9" s="4"/>
+      <c r="X9" s="13">
+        <v>0</v>
+      </c>
       <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
@@ -2060,7 +2062,9 @@
       <c r="W10" s="12">
         <v>2</v>
       </c>
-      <c r="X10" s="7"/>
+      <c r="X10" s="12">
+        <v>3</v>
+      </c>
       <c r="Y10" s="7"/>
       <c r="Z10" s="7"/>
       <c r="AA10" s="7"/>
@@ -2110,7 +2114,9 @@
       <c r="W11" s="12">
         <v>0</v>
       </c>
-      <c r="X11" s="7"/>
+      <c r="X11" s="12">
+        <v>0</v>
+      </c>
       <c r="Y11" s="7"/>
       <c r="Z11" s="7"/>
       <c r="AA11" s="7"/>
@@ -2160,7 +2166,9 @@
       <c r="W12" s="12">
         <v>3</v>
       </c>
-      <c r="X12" s="7"/>
+      <c r="X12" s="12">
+        <v>3</v>
+      </c>
       <c r="Y12" s="7"/>
       <c r="Z12" s="7"/>
       <c r="AA12" s="7"/>
@@ -2210,7 +2218,9 @@
       <c r="W13" s="12">
         <v>0</v>
       </c>
-      <c r="X13" s="7"/>
+      <c r="X13" s="12">
+        <v>0</v>
+      </c>
       <c r="Y13" s="7"/>
       <c r="Z13" s="7"/>
       <c r="AA13" s="7"/>
@@ -2260,7 +2270,9 @@
       <c r="W14" s="12">
         <v>3</v>
       </c>
-      <c r="X14" s="7"/>
+      <c r="X14" s="12">
+        <v>0</v>
+      </c>
       <c r="Y14" s="7"/>
       <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
@@ -2310,7 +2322,9 @@
       <c r="W15" s="12">
         <v>3</v>
       </c>
-      <c r="X15" s="7"/>
+      <c r="X15" s="12">
+        <v>3</v>
+      </c>
       <c r="Y15" s="7"/>
       <c r="Z15" s="7"/>
       <c r="AA15" s="7"/>
@@ -2360,7 +2374,9 @@
       <c r="W16" s="12">
         <v>3</v>
       </c>
-      <c r="X16" s="7"/>
+      <c r="X16" s="12">
+        <v>2</v>
+      </c>
       <c r="Y16" s="7"/>
       <c r="Z16" s="7"/>
       <c r="AA16" s="7"/>
@@ -2410,7 +2426,9 @@
       <c r="W17" s="12">
         <v>0</v>
       </c>
-      <c r="X17" s="7"/>
+      <c r="X17" s="12">
+        <v>0</v>
+      </c>
       <c r="Y17" s="7"/>
       <c r="Z17" s="7"/>
       <c r="AA17" s="7"/>
@@ -2460,7 +2478,9 @@
       <c r="W18" s="12">
         <v>0</v>
       </c>
-      <c r="X18" s="7"/>
+      <c r="X18" s="12">
+        <v>2</v>
+      </c>
       <c r="Y18" s="7"/>
       <c r="Z18" s="7"/>
       <c r="AA18" s="7"/>
@@ -2510,7 +2530,9 @@
       <c r="W19" s="12">
         <v>3</v>
       </c>
-      <c r="X19" s="7"/>
+      <c r="X19" s="12">
+        <v>3</v>
+      </c>
       <c r="Y19" s="7"/>
       <c r="Z19" s="7"/>
       <c r="AA19" s="7"/>
@@ -2560,7 +2582,9 @@
       <c r="W20" s="12">
         <v>0</v>
       </c>
-      <c r="X20" s="7"/>
+      <c r="X20" s="12">
+        <v>0</v>
+      </c>
       <c r="Y20" s="7"/>
       <c r="Z20" s="7"/>
       <c r="AA20" s="7"/>
@@ -2610,7 +2634,9 @@
       <c r="W21" s="12">
         <v>3</v>
       </c>
-      <c r="X21" s="7"/>
+      <c r="X21" s="12">
+        <v>3</v>
+      </c>
       <c r="Y21" s="7"/>
       <c r="Z21" s="7"/>
       <c r="AA21" s="7"/>
@@ -2660,7 +2686,9 @@
       <c r="W22" s="12">
         <v>0</v>
       </c>
-      <c r="X22" s="7"/>
+      <c r="X22" s="12">
+        <v>0</v>
+      </c>
       <c r="Y22" s="7"/>
       <c r="Z22" s="7"/>
       <c r="AA22" s="7"/>
@@ -2710,7 +2738,9 @@
       <c r="W23" s="12">
         <v>3</v>
       </c>
-      <c r="X23" s="7"/>
+      <c r="X23" s="12">
+        <v>3</v>
+      </c>
       <c r="Y23" s="7"/>
       <c r="Z23" s="7"/>
       <c r="AA23" s="7"/>
@@ -2760,7 +2790,9 @@
       <c r="W24" s="12">
         <v>3</v>
       </c>
-      <c r="X24" s="7"/>
+      <c r="X24" s="12">
+        <v>3</v>
+      </c>
       <c r="Y24" s="7"/>
       <c r="Z24" s="7"/>
       <c r="AA24" s="7"/>
@@ -2810,7 +2842,9 @@
       <c r="W25" s="12">
         <v>0</v>
       </c>
-      <c r="X25" s="7"/>
+      <c r="X25" s="12">
+        <v>2</v>
+      </c>
       <c r="Y25" s="7"/>
       <c r="Z25" s="7"/>
       <c r="AA25" s="7"/>
@@ -2860,7 +2894,9 @@
       <c r="W26" s="12">
         <v>0</v>
       </c>
-      <c r="X26" s="7"/>
+      <c r="X26" s="12">
+        <v>0</v>
+      </c>
       <c r="Y26" s="7"/>
       <c r="Z26" s="7"/>
       <c r="AA26" s="7"/>
@@ -2910,7 +2946,9 @@
       <c r="W27" s="12">
         <v>3</v>
       </c>
-      <c r="X27" s="7"/>
+      <c r="X27" s="12">
+        <v>3</v>
+      </c>
       <c r="Y27" s="7"/>
       <c r="Z27" s="7"/>
       <c r="AA27" s="7"/>
@@ -2960,7 +2998,9 @@
       <c r="W28" s="12">
         <v>3</v>
       </c>
-      <c r="X28" s="7"/>
+      <c r="X28" s="12">
+        <v>3</v>
+      </c>
       <c r="Y28" s="7"/>
       <c r="Z28" s="7"/>
       <c r="AA28" s="7"/>
@@ -3010,7 +3050,9 @@
       <c r="W29" s="12">
         <v>0</v>
       </c>
-      <c r="X29" s="7"/>
+      <c r="X29" s="12">
+        <v>0</v>
+      </c>
       <c r="Y29" s="7"/>
       <c r="Z29" s="7"/>
       <c r="AA29" s="7"/>
@@ -3060,7 +3102,9 @@
       <c r="W30" s="12">
         <v>0</v>
       </c>
-      <c r="X30" s="7"/>
+      <c r="X30" s="12">
+        <v>0</v>
+      </c>
       <c r="Y30" s="7"/>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
@@ -3110,7 +3154,9 @@
       <c r="W31" s="12">
         <v>0</v>
       </c>
-      <c r="X31" s="7"/>
+      <c r="X31" s="12">
+        <v>0</v>
+      </c>
       <c r="Y31" s="7"/>
       <c r="Z31" s="7"/>
       <c r="AA31" s="7"/>
@@ -3160,7 +3206,9 @@
       <c r="W32" s="12">
         <v>0</v>
       </c>
-      <c r="X32" s="7"/>
+      <c r="X32" s="12">
+        <v>0</v>
+      </c>
       <c r="Y32" s="7"/>
       <c r="Z32" s="7"/>
       <c r="AA32" s="7"/>
@@ -3210,7 +3258,9 @@
       <c r="W33" s="12">
         <v>3</v>
       </c>
-      <c r="X33" s="7"/>
+      <c r="X33" s="12">
+        <v>3</v>
+      </c>
       <c r="Y33" s="7"/>
       <c r="Z33" s="7"/>
       <c r="AA33" s="7"/>
@@ -3251,28 +3301,28 @@
       <c r="V34"/>
     </row>
     <row r="35" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="24"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="24"/>
-      <c r="Q35" s="24"/>
-      <c r="R35" s="24"/>
-      <c r="S35" s="24"/>
-      <c r="T35" s="24"/>
-      <c r="U35" s="24"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="21"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="21"/>
+      <c r="R35" s="21"/>
+      <c r="S35" s="21"/>
+      <c r="T35" s="21"/>
+      <c r="U35" s="21"/>
       <c r="V35" s="8"/>
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
@@ -3391,7 +3441,9 @@
       <c r="W37" s="13">
         <v>0</v>
       </c>
-      <c r="X37" s="4"/>
+      <c r="X37" s="13">
+        <v>0</v>
+      </c>
       <c r="Y37" s="4"/>
       <c r="Z37" s="4"/>
       <c r="AA37" s="4"/>
@@ -3441,7 +3493,9 @@
       <c r="W38" s="12">
         <v>0</v>
       </c>
-      <c r="X38" s="7"/>
+      <c r="X38" s="13">
+        <v>0</v>
+      </c>
       <c r="Y38" s="7"/>
       <c r="Z38" s="7"/>
       <c r="AA38" s="7"/>
@@ -3491,7 +3545,9 @@
       <c r="W39" s="12">
         <v>0</v>
       </c>
-      <c r="X39" s="7"/>
+      <c r="X39" s="13">
+        <v>0</v>
+      </c>
       <c r="Y39" s="7"/>
       <c r="Z39" s="7"/>
       <c r="AA39" s="7"/>
@@ -3541,7 +3597,9 @@
       <c r="W40" s="12">
         <v>0</v>
       </c>
-      <c r="X40" s="7"/>
+      <c r="X40" s="13">
+        <v>0</v>
+      </c>
       <c r="Y40" s="7"/>
       <c r="Z40" s="7"/>
       <c r="AA40" s="7"/>
@@ -3591,7 +3649,9 @@
       <c r="W41" s="12">
         <v>0</v>
       </c>
-      <c r="X41" s="7"/>
+      <c r="X41" s="13">
+        <v>0</v>
+      </c>
       <c r="Y41" s="7"/>
       <c r="Z41" s="7"/>
       <c r="AA41" s="7"/>
@@ -3641,7 +3701,9 @@
       <c r="W42" s="12">
         <v>0</v>
       </c>
-      <c r="X42" s="7"/>
+      <c r="X42" s="13">
+        <v>0</v>
+      </c>
       <c r="Y42" s="7"/>
       <c r="Z42" s="7"/>
       <c r="AA42" s="7"/>
@@ -3691,7 +3753,9 @@
       <c r="W43" s="12">
         <v>0</v>
       </c>
-      <c r="X43" s="7"/>
+      <c r="X43" s="13">
+        <v>0</v>
+      </c>
       <c r="Y43" s="7"/>
       <c r="Z43" s="7"/>
       <c r="AA43" s="7"/>
@@ -3741,7 +3805,9 @@
       <c r="W44" s="12">
         <v>0</v>
       </c>
-      <c r="X44" s="7"/>
+      <c r="X44" s="13">
+        <v>0</v>
+      </c>
       <c r="Y44" s="7"/>
       <c r="Z44" s="7"/>
       <c r="AA44" s="7"/>
@@ -3791,7 +3857,9 @@
       <c r="W45" s="12">
         <v>0</v>
       </c>
-      <c r="X45" s="7"/>
+      <c r="X45" s="13">
+        <v>0</v>
+      </c>
       <c r="Y45" s="7"/>
       <c r="Z45" s="7"/>
       <c r="AA45" s="7"/>
@@ -3841,7 +3909,9 @@
       <c r="W46" s="12">
         <v>0</v>
       </c>
-      <c r="X46" s="7"/>
+      <c r="X46" s="13">
+        <v>0</v>
+      </c>
       <c r="Y46" s="7"/>
       <c r="Z46" s="7"/>
       <c r="AA46" s="7"/>
@@ -3891,7 +3961,9 @@
       <c r="W47" s="12">
         <v>0</v>
       </c>
-      <c r="X47" s="7"/>
+      <c r="X47" s="13">
+        <v>0</v>
+      </c>
       <c r="Y47" s="7"/>
       <c r="Z47" s="7"/>
       <c r="AA47" s="7"/>
@@ -3941,7 +4013,9 @@
       <c r="W48" s="12">
         <v>0</v>
       </c>
-      <c r="X48" s="7"/>
+      <c r="X48" s="13">
+        <v>0</v>
+      </c>
       <c r="Y48" s="7"/>
       <c r="Z48" s="7"/>
       <c r="AA48" s="7"/>
@@ -3991,7 +4065,9 @@
       <c r="W49" s="12">
         <v>3</v>
       </c>
-      <c r="X49" s="7"/>
+      <c r="X49" s="13">
+        <v>0</v>
+      </c>
       <c r="Y49" s="7"/>
       <c r="Z49" s="7"/>
       <c r="AA49" s="7"/>
@@ -4041,7 +4117,9 @@
       <c r="W50" s="12">
         <v>0</v>
       </c>
-      <c r="X50" s="7"/>
+      <c r="X50" s="13">
+        <v>0</v>
+      </c>
       <c r="Y50" s="7"/>
       <c r="Z50" s="7"/>
       <c r="AA50" s="7"/>
@@ -4091,7 +4169,9 @@
       <c r="W51" s="12">
         <v>0</v>
       </c>
-      <c r="X51" s="7"/>
+      <c r="X51" s="13">
+        <v>0</v>
+      </c>
       <c r="Y51" s="7"/>
       <c r="Z51" s="7"/>
       <c r="AA51" s="7"/>
@@ -4141,7 +4221,9 @@
       <c r="W52" s="12">
         <v>0</v>
       </c>
-      <c r="X52" s="7"/>
+      <c r="X52" s="13">
+        <v>0</v>
+      </c>
       <c r="Y52" s="7"/>
       <c r="Z52" s="7"/>
       <c r="AA52" s="7"/>
@@ -4191,7 +4273,9 @@
       <c r="W53" s="12">
         <v>1</v>
       </c>
-      <c r="X53" s="7"/>
+      <c r="X53" s="13">
+        <v>0</v>
+      </c>
       <c r="Y53" s="7"/>
       <c r="Z53" s="7"/>
       <c r="AA53" s="7"/>
@@ -4241,7 +4325,9 @@
       <c r="W54" s="12">
         <v>0</v>
       </c>
-      <c r="X54" s="7"/>
+      <c r="X54" s="13">
+        <v>0</v>
+      </c>
       <c r="Y54" s="7"/>
       <c r="Z54" s="7"/>
       <c r="AA54" s="7"/>
@@ -4291,7 +4377,9 @@
       <c r="W55" s="12">
         <v>0</v>
       </c>
-      <c r="X55" s="7"/>
+      <c r="X55" s="13">
+        <v>0</v>
+      </c>
       <c r="Y55" s="7"/>
       <c r="Z55" s="7"/>
       <c r="AA55" s="7"/>
@@ -4341,7 +4429,9 @@
       <c r="W56" s="12">
         <v>0</v>
       </c>
-      <c r="X56" s="7"/>
+      <c r="X56" s="13">
+        <v>0</v>
+      </c>
       <c r="Y56" s="7"/>
       <c r="Z56" s="7"/>
       <c r="AA56" s="7"/>
@@ -4391,7 +4481,9 @@
       <c r="W57" s="12">
         <v>0</v>
       </c>
-      <c r="X57" s="7"/>
+      <c r="X57" s="13">
+        <v>0</v>
+      </c>
       <c r="Y57" s="7"/>
       <c r="Z57" s="7"/>
       <c r="AA57" s="7"/>
@@ -4441,7 +4533,9 @@
       <c r="W58" s="12">
         <v>0</v>
       </c>
-      <c r="X58" s="7"/>
+      <c r="X58" s="13">
+        <v>0</v>
+      </c>
       <c r="Y58" s="7"/>
       <c r="Z58" s="7"/>
       <c r="AA58" s="7"/>
@@ -4491,7 +4585,9 @@
       <c r="W59" s="12">
         <v>0</v>
       </c>
-      <c r="X59" s="7"/>
+      <c r="X59" s="13">
+        <v>0</v>
+      </c>
       <c r="Y59" s="7"/>
       <c r="Z59" s="7"/>
       <c r="AA59" s="7"/>
@@ -4541,7 +4637,9 @@
       <c r="W60" s="12">
         <v>0</v>
       </c>
-      <c r="X60" s="7"/>
+      <c r="X60" s="13">
+        <v>0</v>
+      </c>
       <c r="Y60" s="7"/>
       <c r="Z60" s="7"/>
       <c r="AA60" s="7"/>
@@ -4591,7 +4689,9 @@
       <c r="W61" s="12">
         <v>0</v>
       </c>
-      <c r="X61" s="7"/>
+      <c r="X61" s="12">
+        <v>0</v>
+      </c>
       <c r="Y61" s="7"/>
       <c r="Z61" s="7"/>
       <c r="AA61" s="7"/>
@@ -4641,7 +4741,9 @@
       <c r="W62" s="12">
         <v>3</v>
       </c>
-      <c r="X62" s="7"/>
+      <c r="X62" s="12">
+        <v>3</v>
+      </c>
       <c r="Y62" s="7"/>
       <c r="Z62" s="7"/>
       <c r="AA62" s="7"/>
@@ -4691,7 +4793,9 @@
       <c r="W63" s="12">
         <v>0</v>
       </c>
-      <c r="X63" s="7"/>
+      <c r="X63" s="12">
+        <v>0</v>
+      </c>
       <c r="Y63" s="7"/>
       <c r="Z63" s="7"/>
       <c r="AA63" s="7"/>
@@ -4741,7 +4845,9 @@
       <c r="W64" s="12">
         <v>0</v>
       </c>
-      <c r="X64" s="7"/>
+      <c r="X64" s="12">
+        <v>0</v>
+      </c>
       <c r="Y64" s="7"/>
       <c r="Z64" s="7"/>
       <c r="AA64" s="7"/>
@@ -4791,7 +4897,9 @@
       <c r="W65" s="12">
         <v>0</v>
       </c>
-      <c r="X65" s="7"/>
+      <c r="X65" s="12">
+        <v>0</v>
+      </c>
       <c r="Y65" s="7"/>
       <c r="Z65" s="7"/>
       <c r="AA65" s="7"/>
@@ -4841,7 +4949,9 @@
       <c r="W66" s="12">
         <v>0</v>
       </c>
-      <c r="X66" s="7"/>
+      <c r="X66" s="12">
+        <v>0</v>
+      </c>
       <c r="Y66" s="7"/>
       <c r="Z66" s="7"/>
       <c r="AA66" s="7"/>
@@ -4883,28 +4993,28 @@
     </row>
     <row r="68" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
-      <c r="B68" s="24" t="s">
+      <c r="B68" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="C68" s="24"/>
-      <c r="D68" s="24"/>
-      <c r="E68" s="24"/>
-      <c r="F68" s="24"/>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="24"/>
-      <c r="J68" s="24"/>
-      <c r="K68" s="24"/>
-      <c r="L68" s="24"/>
-      <c r="M68" s="24"/>
-      <c r="N68" s="24"/>
-      <c r="O68" s="24"/>
-      <c r="P68" s="24"/>
-      <c r="Q68" s="24"/>
-      <c r="R68" s="24"/>
-      <c r="S68" s="24"/>
-      <c r="T68" s="24"/>
-      <c r="U68" s="24"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="21"/>
+      <c r="P68" s="21"/>
+      <c r="Q68" s="21"/>
+      <c r="R68" s="21"/>
+      <c r="S68" s="21"/>
+      <c r="T68" s="21"/>
+      <c r="U68" s="21"/>
       <c r="V68" s="8"/>
       <c r="W68" s="9"/>
       <c r="X68" s="9"/>
@@ -5024,7 +5134,9 @@
       <c r="W70" s="13">
         <v>0</v>
       </c>
-      <c r="X70" s="4"/>
+      <c r="X70" s="13">
+        <v>0</v>
+      </c>
       <c r="Y70" s="4"/>
       <c r="Z70" s="4"/>
       <c r="AA70" s="4"/>
@@ -5074,7 +5186,9 @@
       <c r="W71" s="12">
         <v>3</v>
       </c>
-      <c r="X71" s="7"/>
+      <c r="X71" s="12">
+        <v>0</v>
+      </c>
       <c r="Y71" s="7"/>
       <c r="Z71" s="7"/>
       <c r="AA71" s="7"/>
@@ -5124,7 +5238,9 @@
       <c r="W72" s="12">
         <v>3</v>
       </c>
-      <c r="X72" s="7"/>
+      <c r="X72" s="12">
+        <v>3</v>
+      </c>
       <c r="Y72" s="7"/>
       <c r="Z72" s="7"/>
       <c r="AA72" s="7"/>
@@ -5174,7 +5290,9 @@
       <c r="W73" s="12">
         <v>0</v>
       </c>
-      <c r="X73" s="7"/>
+      <c r="X73" s="12">
+        <v>0</v>
+      </c>
       <c r="Y73" s="7"/>
       <c r="Z73" s="7"/>
       <c r="AA73" s="7"/>
@@ -5224,7 +5342,9 @@
       <c r="W74" s="12">
         <v>0</v>
       </c>
-      <c r="X74" s="7"/>
+      <c r="X74" s="12">
+        <v>0</v>
+      </c>
       <c r="Y74" s="7"/>
       <c r="Z74" s="7"/>
       <c r="AA74" s="7"/>
@@ -5274,7 +5394,9 @@
       <c r="W75" s="12">
         <v>0</v>
       </c>
-      <c r="X75" s="7"/>
+      <c r="X75" s="12">
+        <v>0</v>
+      </c>
       <c r="Y75" s="7"/>
       <c r="Z75" s="7"/>
       <c r="AA75" s="7"/>
@@ -5324,7 +5446,9 @@
       <c r="W76" s="12">
         <v>0</v>
       </c>
-      <c r="X76" s="7"/>
+      <c r="X76" s="12">
+        <v>0</v>
+      </c>
       <c r="Y76" s="7"/>
       <c r="Z76" s="7"/>
       <c r="AA76" s="7"/>
@@ -5374,7 +5498,9 @@
       <c r="W77" s="12">
         <v>0</v>
       </c>
-      <c r="X77" s="7"/>
+      <c r="X77" s="12">
+        <v>0</v>
+      </c>
       <c r="Y77" s="7"/>
       <c r="Z77" s="7"/>
       <c r="AA77" s="7"/>
@@ -5424,7 +5550,9 @@
       <c r="W78" s="12">
         <v>0</v>
       </c>
-      <c r="X78" s="7"/>
+      <c r="X78" s="12">
+        <v>0</v>
+      </c>
       <c r="Y78" s="7"/>
       <c r="Z78" s="7"/>
       <c r="AA78" s="7"/>
@@ -5474,7 +5602,9 @@
       <c r="W79" s="12">
         <v>0</v>
       </c>
-      <c r="X79" s="7"/>
+      <c r="X79" s="12">
+        <v>0</v>
+      </c>
       <c r="Y79" s="7"/>
       <c r="Z79" s="7"/>
       <c r="AA79" s="7"/>
@@ -5524,7 +5654,9 @@
       <c r="W80" s="12">
         <v>0</v>
       </c>
-      <c r="X80" s="7"/>
+      <c r="X80" s="12">
+        <v>0</v>
+      </c>
       <c r="Y80" s="7"/>
       <c r="Z80" s="7"/>
       <c r="AA80" s="7"/>
@@ -5574,7 +5706,9 @@
       <c r="W81" s="12">
         <v>0</v>
       </c>
-      <c r="X81" s="7"/>
+      <c r="X81" s="12">
+        <v>0</v>
+      </c>
       <c r="Y81" s="7"/>
       <c r="Z81" s="7"/>
       <c r="AA81" s="7"/>
@@ -5624,7 +5758,9 @@
       <c r="W82" s="12">
         <v>0</v>
       </c>
-      <c r="X82" s="7"/>
+      <c r="X82" s="12">
+        <v>0</v>
+      </c>
       <c r="Y82" s="7"/>
       <c r="Z82" s="7"/>
       <c r="AA82" s="7"/>
@@ -5674,7 +5810,9 @@
       <c r="W83" s="12">
         <v>0</v>
       </c>
-      <c r="X83" s="7"/>
+      <c r="X83" s="12">
+        <v>0</v>
+      </c>
       <c r="Y83" s="7"/>
       <c r="Z83" s="7"/>
       <c r="AA83" s="7"/>
@@ -5724,7 +5862,9 @@
       <c r="W84" s="12">
         <v>0</v>
       </c>
-      <c r="X84" s="7"/>
+      <c r="X84" s="12">
+        <v>0</v>
+      </c>
       <c r="Y84" s="7"/>
       <c r="Z84" s="7"/>
       <c r="AA84" s="7"/>
@@ -5774,7 +5914,9 @@
       <c r="W85" s="12">
         <v>0</v>
       </c>
-      <c r="X85" s="7"/>
+      <c r="X85" s="12">
+        <v>0</v>
+      </c>
       <c r="Y85" s="7"/>
       <c r="Z85" s="7"/>
       <c r="AA85" s="7"/>
@@ -5824,7 +5966,9 @@
       <c r="W86" s="12">
         <v>0</v>
       </c>
-      <c r="X86" s="7"/>
+      <c r="X86" s="12">
+        <v>0</v>
+      </c>
       <c r="Y86" s="7"/>
       <c r="Z86" s="7"/>
       <c r="AA86" s="7"/>
@@ -5874,7 +6018,9 @@
       <c r="W87" s="12">
         <v>0</v>
       </c>
-      <c r="X87" s="7"/>
+      <c r="X87" s="12">
+        <v>0</v>
+      </c>
       <c r="Y87" s="7"/>
       <c r="Z87" s="7"/>
       <c r="AA87" s="7"/>
@@ -5924,7 +6070,9 @@
       <c r="W88" s="12">
         <v>0</v>
       </c>
-      <c r="X88" s="7"/>
+      <c r="X88" s="12">
+        <v>0</v>
+      </c>
       <c r="Y88" s="7"/>
       <c r="Z88" s="7"/>
       <c r="AA88" s="7"/>
@@ -5974,7 +6122,9 @@
       <c r="W89" s="12">
         <v>0</v>
       </c>
-      <c r="X89" s="7"/>
+      <c r="X89" s="12">
+        <v>0</v>
+      </c>
       <c r="Y89" s="7"/>
       <c r="Z89" s="7"/>
       <c r="AA89" s="7"/>
@@ -6024,7 +6174,9 @@
       <c r="W90" s="12">
         <v>0</v>
       </c>
-      <c r="X90" s="7"/>
+      <c r="X90" s="12">
+        <v>0</v>
+      </c>
       <c r="Y90" s="7"/>
       <c r="Z90" s="7"/>
       <c r="AA90" s="7"/>
@@ -6074,7 +6226,9 @@
       <c r="W91" s="12">
         <v>0</v>
       </c>
-      <c r="X91" s="7"/>
+      <c r="X91" s="12">
+        <v>0</v>
+      </c>
       <c r="Y91" s="7"/>
       <c r="Z91" s="7"/>
       <c r="AA91" s="7"/>
@@ -6124,7 +6278,9 @@
       <c r="W92" s="12">
         <v>0</v>
       </c>
-      <c r="X92" s="7"/>
+      <c r="X92" s="12">
+        <v>0</v>
+      </c>
       <c r="Y92" s="7"/>
       <c r="Z92" s="7"/>
       <c r="AA92" s="7"/>
@@ -6174,7 +6330,9 @@
       <c r="W93" s="12">
         <v>0</v>
       </c>
-      <c r="X93" s="7"/>
+      <c r="X93" s="12">
+        <v>0</v>
+      </c>
       <c r="Y93" s="7"/>
       <c r="Z93" s="7"/>
       <c r="AA93" s="7"/>
@@ -6224,7 +6382,9 @@
       <c r="W94" s="12">
         <v>0</v>
       </c>
-      <c r="X94" s="7"/>
+      <c r="X94" s="12">
+        <v>0</v>
+      </c>
       <c r="Y94" s="7"/>
       <c r="Z94" s="7"/>
       <c r="AA94" s="7"/>
@@ -6274,7 +6434,9 @@
       <c r="W95" s="12">
         <v>0</v>
       </c>
-      <c r="X95" s="7"/>
+      <c r="X95" s="12">
+        <v>0</v>
+      </c>
       <c r="Y95" s="7"/>
       <c r="Z95" s="7"/>
       <c r="AA95" s="7"/>
@@ -6324,7 +6486,9 @@
       <c r="W96" s="12">
         <v>0</v>
       </c>
-      <c r="X96" s="7"/>
+      <c r="X96" s="12">
+        <v>0</v>
+      </c>
       <c r="Y96" s="7"/>
       <c r="Z96" s="7"/>
       <c r="AA96" s="7"/>
@@ -6374,7 +6538,9 @@
       <c r="W97" s="12">
         <v>0</v>
       </c>
-      <c r="X97" s="7"/>
+      <c r="X97" s="12">
+        <v>0</v>
+      </c>
       <c r="Y97" s="7"/>
       <c r="Z97" s="7"/>
       <c r="AA97" s="7"/>
@@ -6424,7 +6590,9 @@
       <c r="W98" s="12">
         <v>0</v>
       </c>
-      <c r="X98" s="7"/>
+      <c r="X98" s="12">
+        <v>0</v>
+      </c>
       <c r="Y98" s="7"/>
       <c r="Z98" s="7"/>
       <c r="AA98" s="7"/>
@@ -6474,7 +6642,9 @@
       <c r="W99" s="12">
         <v>0</v>
       </c>
-      <c r="X99" s="7"/>
+      <c r="X99" s="12">
+        <v>0</v>
+      </c>
       <c r="Y99" s="7"/>
       <c r="Z99" s="7"/>
       <c r="AA99" s="7"/>
@@ -6515,28 +6685,28 @@
       <c r="V100"/>
     </row>
     <row r="101" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B101" s="24" t="s">
+      <c r="B101" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="C101" s="24"/>
-      <c r="D101" s="24"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="24"/>
-      <c r="H101" s="24"/>
-      <c r="I101" s="24"/>
-      <c r="J101" s="24"/>
-      <c r="K101" s="24"/>
-      <c r="L101" s="24"/>
-      <c r="M101" s="24"/>
-      <c r="N101" s="24"/>
-      <c r="O101" s="24"/>
-      <c r="P101" s="24"/>
-      <c r="Q101" s="24"/>
-      <c r="R101" s="24"/>
-      <c r="S101" s="24"/>
-      <c r="T101" s="24"/>
-      <c r="U101" s="24"/>
+      <c r="C101" s="21"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="21"/>
+      <c r="F101" s="21"/>
+      <c r="G101" s="21"/>
+      <c r="H101" s="21"/>
+      <c r="I101" s="21"/>
+      <c r="J101" s="21"/>
+      <c r="K101" s="21"/>
+      <c r="L101" s="21"/>
+      <c r="M101" s="21"/>
+      <c r="N101" s="21"/>
+      <c r="O101" s="21"/>
+      <c r="P101" s="21"/>
+      <c r="Q101" s="21"/>
+      <c r="R101" s="21"/>
+      <c r="S101" s="21"/>
+      <c r="T101" s="21"/>
+      <c r="U101" s="21"/>
       <c r="V101" s="8"/>
       <c r="W101" s="9"/>
       <c r="X101" s="9"/>
@@ -6656,7 +6826,9 @@
       <c r="W103" s="13">
         <v>0</v>
       </c>
-      <c r="X103" s="4"/>
+      <c r="X103" s="13">
+        <v>0</v>
+      </c>
       <c r="Y103" s="4"/>
       <c r="Z103" s="4"/>
       <c r="AA103" s="4"/>
@@ -6706,7 +6878,9 @@
       <c r="W104" s="12">
         <v>0</v>
       </c>
-      <c r="X104" s="7"/>
+      <c r="X104" s="13">
+        <v>0</v>
+      </c>
       <c r="Y104" s="7"/>
       <c r="Z104" s="7"/>
       <c r="AA104" s="7"/>
@@ -6756,7 +6930,9 @@
       <c r="W105" s="12">
         <v>0</v>
       </c>
-      <c r="X105" s="7"/>
+      <c r="X105" s="13">
+        <v>0</v>
+      </c>
       <c r="Y105" s="7"/>
       <c r="Z105" s="7"/>
       <c r="AA105" s="7"/>
@@ -6806,7 +6982,9 @@
       <c r="W106" s="12">
         <v>0</v>
       </c>
-      <c r="X106" s="7"/>
+      <c r="X106" s="13">
+        <v>0</v>
+      </c>
       <c r="Y106" s="7"/>
       <c r="Z106" s="7"/>
       <c r="AA106" s="7"/>
@@ -6856,7 +7034,9 @@
       <c r="W107" s="12">
         <v>0</v>
       </c>
-      <c r="X107" s="7"/>
+      <c r="X107" s="13">
+        <v>0</v>
+      </c>
       <c r="Y107" s="7"/>
       <c r="Z107" s="7"/>
       <c r="AA107" s="7"/>
@@ -6906,7 +7086,9 @@
       <c r="W108" s="12">
         <v>3</v>
       </c>
-      <c r="X108" s="7"/>
+      <c r="X108" s="13">
+        <v>0</v>
+      </c>
       <c r="Y108" s="7"/>
       <c r="Z108" s="7"/>
       <c r="AA108" s="7"/>
@@ -6956,7 +7138,9 @@
       <c r="W109" s="12">
         <v>0</v>
       </c>
-      <c r="X109" s="7"/>
+      <c r="X109" s="13">
+        <v>0</v>
+      </c>
       <c r="Y109" s="7"/>
       <c r="Z109" s="7"/>
       <c r="AA109" s="7"/>
@@ -7006,7 +7190,9 @@
       <c r="W110" s="12">
         <v>0</v>
       </c>
-      <c r="X110" s="7"/>
+      <c r="X110" s="13">
+        <v>0</v>
+      </c>
       <c r="Y110" s="7"/>
       <c r="Z110" s="7"/>
       <c r="AA110" s="7"/>
@@ -7056,7 +7242,9 @@
       <c r="W111" s="12">
         <v>0</v>
       </c>
-      <c r="X111" s="7"/>
+      <c r="X111" s="13">
+        <v>0</v>
+      </c>
       <c r="Y111" s="7"/>
       <c r="Z111" s="7"/>
       <c r="AA111" s="7"/>
@@ -7106,7 +7294,9 @@
       <c r="W112" s="12">
         <v>0</v>
       </c>
-      <c r="X112" s="7"/>
+      <c r="X112" s="13">
+        <v>0</v>
+      </c>
       <c r="Y112" s="7"/>
       <c r="Z112" s="7"/>
       <c r="AA112" s="7"/>
@@ -7156,7 +7346,9 @@
       <c r="W113" s="12">
         <v>3</v>
       </c>
-      <c r="X113" s="7"/>
+      <c r="X113" s="12">
+        <v>2</v>
+      </c>
       <c r="Y113" s="7"/>
       <c r="Z113" s="7"/>
       <c r="AA113" s="7"/>
@@ -7206,7 +7398,9 @@
       <c r="W114" s="12">
         <v>0</v>
       </c>
-      <c r="X114" s="7"/>
+      <c r="X114" s="12">
+        <v>0</v>
+      </c>
       <c r="Y114" s="7"/>
       <c r="Z114" s="7"/>
       <c r="AA114" s="7"/>
@@ -7256,7 +7450,9 @@
       <c r="W115" s="12">
         <v>0</v>
       </c>
-      <c r="X115" s="7"/>
+      <c r="X115" s="12">
+        <v>0</v>
+      </c>
       <c r="Y115" s="7"/>
       <c r="Z115" s="7"/>
       <c r="AA115" s="7"/>
@@ -7306,7 +7502,9 @@
       <c r="W116" s="12">
         <v>0</v>
       </c>
-      <c r="X116" s="7"/>
+      <c r="X116" s="12">
+        <v>0</v>
+      </c>
       <c r="Y116" s="7"/>
       <c r="Z116" s="7"/>
       <c r="AA116" s="7"/>
@@ -7356,7 +7554,9 @@
       <c r="W117" s="12">
         <v>3</v>
       </c>
-      <c r="X117" s="7"/>
+      <c r="X117" s="12">
+        <v>2</v>
+      </c>
       <c r="Y117" s="7"/>
       <c r="Z117" s="7"/>
       <c r="AA117" s="7"/>
@@ -7406,7 +7606,9 @@
       <c r="W118" s="12">
         <v>0</v>
       </c>
-      <c r="X118" s="7"/>
+      <c r="X118" s="12">
+        <v>0</v>
+      </c>
       <c r="Y118" s="7"/>
       <c r="Z118" s="7"/>
       <c r="AA118" s="7"/>
@@ -7456,7 +7658,9 @@
       <c r="W119" s="12">
         <v>0</v>
       </c>
-      <c r="X119" s="7"/>
+      <c r="X119" s="12">
+        <v>0</v>
+      </c>
       <c r="Y119" s="7"/>
       <c r="Z119" s="7"/>
       <c r="AA119" s="7"/>
@@ -7506,7 +7710,9 @@
       <c r="W120" s="12">
         <v>0</v>
       </c>
-      <c r="X120" s="7"/>
+      <c r="X120" s="12">
+        <v>0</v>
+      </c>
       <c r="Y120" s="7"/>
       <c r="Z120" s="7"/>
       <c r="AA120" s="7"/>
@@ -7556,7 +7762,9 @@
       <c r="W121" s="12">
         <v>0</v>
       </c>
-      <c r="X121" s="7"/>
+      <c r="X121" s="12">
+        <v>0</v>
+      </c>
       <c r="Y121" s="7"/>
       <c r="Z121" s="7"/>
       <c r="AA121" s="7"/>
@@ -7606,7 +7814,9 @@
       <c r="W122" s="12">
         <v>0</v>
       </c>
-      <c r="X122" s="7"/>
+      <c r="X122" s="12">
+        <v>0</v>
+      </c>
       <c r="Y122" s="7"/>
       <c r="Z122" s="7"/>
       <c r="AA122" s="7"/>
@@ -7656,7 +7866,9 @@
       <c r="W123" s="12">
         <v>0</v>
       </c>
-      <c r="X123" s="7"/>
+      <c r="X123" s="12">
+        <v>0</v>
+      </c>
       <c r="Y123" s="7"/>
       <c r="Z123" s="7"/>
       <c r="AA123" s="7"/>
@@ -7706,7 +7918,9 @@
       <c r="W124" s="12">
         <v>0</v>
       </c>
-      <c r="X124" s="7"/>
+      <c r="X124" s="12">
+        <v>0</v>
+      </c>
       <c r="Y124" s="7"/>
       <c r="Z124" s="7"/>
       <c r="AA124" s="7"/>
@@ -7756,7 +7970,9 @@
       <c r="W125" s="12">
         <v>0</v>
       </c>
-      <c r="X125" s="7"/>
+      <c r="X125" s="12">
+        <v>0</v>
+      </c>
       <c r="Y125" s="7"/>
       <c r="Z125" s="7"/>
       <c r="AA125" s="7"/>
@@ -7806,7 +8022,9 @@
       <c r="W126" s="12">
         <v>0</v>
       </c>
-      <c r="X126" s="7"/>
+      <c r="X126" s="12">
+        <v>0</v>
+      </c>
       <c r="Y126" s="7"/>
       <c r="Z126" s="7"/>
       <c r="AA126" s="7"/>
@@ -7856,7 +8074,9 @@
       <c r="W127" s="12">
         <v>3</v>
       </c>
-      <c r="X127" s="7"/>
+      <c r="X127" s="12">
+        <v>0</v>
+      </c>
       <c r="Y127" s="7"/>
       <c r="Z127" s="7"/>
       <c r="AA127" s="7"/>
@@ -7906,7 +8126,9 @@
       <c r="W128" s="12">
         <v>0</v>
       </c>
-      <c r="X128" s="7"/>
+      <c r="X128" s="12">
+        <v>0</v>
+      </c>
       <c r="Y128" s="7"/>
       <c r="Z128" s="7"/>
       <c r="AA128" s="7"/>
@@ -7956,7 +8178,9 @@
       <c r="W129" s="12">
         <v>3</v>
       </c>
-      <c r="X129" s="7"/>
+      <c r="X129" s="12">
+        <v>2</v>
+      </c>
       <c r="Y129" s="7"/>
       <c r="Z129" s="7"/>
       <c r="AA129" s="7"/>
@@ -8006,7 +8230,9 @@
       <c r="W130" s="12">
         <v>0</v>
       </c>
-      <c r="X130" s="7"/>
+      <c r="X130" s="12">
+        <v>0</v>
+      </c>
       <c r="Y130" s="7"/>
       <c r="Z130" s="7"/>
       <c r="AA130" s="7"/>
@@ -8056,7 +8282,9 @@
       <c r="W131" s="12">
         <v>0</v>
       </c>
-      <c r="X131" s="7"/>
+      <c r="X131" s="12">
+        <v>0</v>
+      </c>
       <c r="Y131" s="7"/>
       <c r="Z131" s="7"/>
       <c r="AA131" s="7"/>
@@ -8106,7 +8334,9 @@
       <c r="W132" s="12">
         <v>0</v>
       </c>
-      <c r="X132" s="7"/>
+      <c r="X132" s="12">
+        <v>0</v>
+      </c>
       <c r="Y132" s="7"/>
       <c r="Z132" s="7"/>
       <c r="AA132" s="7"/>
@@ -8147,28 +8377,28 @@
       <c r="V133"/>
     </row>
     <row r="134" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B134" s="24" t="s">
+      <c r="B134" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="C134" s="24"/>
-      <c r="D134" s="24"/>
-      <c r="E134" s="24"/>
-      <c r="F134" s="24"/>
-      <c r="G134" s="24"/>
-      <c r="H134" s="24"/>
-      <c r="I134" s="24"/>
-      <c r="J134" s="24"/>
-      <c r="K134" s="24"/>
-      <c r="L134" s="24"/>
-      <c r="M134" s="24"/>
-      <c r="N134" s="24"/>
-      <c r="O134" s="24"/>
-      <c r="P134" s="24"/>
-      <c r="Q134" s="24"/>
-      <c r="R134" s="24"/>
-      <c r="S134" s="24"/>
-      <c r="T134" s="24"/>
-      <c r="U134" s="24"/>
+      <c r="C134" s="21"/>
+      <c r="D134" s="21"/>
+      <c r="E134" s="21"/>
+      <c r="F134" s="21"/>
+      <c r="G134" s="21"/>
+      <c r="H134" s="21"/>
+      <c r="I134" s="21"/>
+      <c r="J134" s="21"/>
+      <c r="K134" s="21"/>
+      <c r="L134" s="21"/>
+      <c r="M134" s="21"/>
+      <c r="N134" s="21"/>
+      <c r="O134" s="21"/>
+      <c r="P134" s="21"/>
+      <c r="Q134" s="21"/>
+      <c r="R134" s="21"/>
+      <c r="S134" s="21"/>
+      <c r="T134" s="21"/>
+      <c r="U134" s="21"/>
       <c r="V134" s="8"/>
       <c r="W134" s="9"/>
       <c r="X134" s="9"/>
@@ -8187,26 +8417,26 @@
     </row>
     <row r="135" spans="1:36" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135"/>
-      <c r="B135" s="25"/>
-      <c r="C135" s="26"/>
-      <c r="D135" s="26"/>
-      <c r="E135" s="26"/>
-      <c r="F135" s="26"/>
-      <c r="G135" s="26"/>
-      <c r="H135" s="26"/>
-      <c r="I135" s="26"/>
-      <c r="J135" s="26"/>
-      <c r="K135" s="26"/>
-      <c r="L135" s="26"/>
-      <c r="M135" s="26"/>
-      <c r="N135" s="26"/>
-      <c r="O135" s="26"/>
-      <c r="P135" s="26"/>
-      <c r="Q135" s="26"/>
-      <c r="R135" s="26"/>
-      <c r="S135" s="26"/>
-      <c r="T135" s="26"/>
-      <c r="U135" s="27"/>
+      <c r="B135" s="26"/>
+      <c r="C135" s="27"/>
+      <c r="D135" s="27"/>
+      <c r="E135" s="27"/>
+      <c r="F135" s="27"/>
+      <c r="G135" s="27"/>
+      <c r="H135" s="27"/>
+      <c r="I135" s="27"/>
+      <c r="J135" s="27"/>
+      <c r="K135" s="27"/>
+      <c r="L135" s="27"/>
+      <c r="M135" s="27"/>
+      <c r="N135" s="27"/>
+      <c r="O135" s="27"/>
+      <c r="P135" s="27"/>
+      <c r="Q135" s="27"/>
+      <c r="R135" s="27"/>
+      <c r="S135" s="27"/>
+      <c r="T135" s="27"/>
+      <c r="U135" s="28"/>
       <c r="V135" s="10">
         <v>0</v>
       </c>
@@ -8288,7 +8518,9 @@
       <c r="W136" s="13">
         <v>2</v>
       </c>
-      <c r="X136" s="4"/>
+      <c r="X136" s="13">
+        <v>3</v>
+      </c>
       <c r="Y136" s="4"/>
       <c r="Z136" s="4"/>
       <c r="AA136" s="4"/>
@@ -8338,7 +8570,9 @@
       <c r="W137" s="12">
         <v>1</v>
       </c>
-      <c r="X137" s="7"/>
+      <c r="X137" s="12">
+        <v>0</v>
+      </c>
       <c r="Y137" s="7"/>
       <c r="Z137" s="7"/>
       <c r="AA137" s="7"/>
@@ -8388,7 +8622,9 @@
       <c r="W138" s="12">
         <v>0</v>
       </c>
-      <c r="X138" s="7"/>
+      <c r="X138" s="12">
+        <v>0</v>
+      </c>
       <c r="Y138" s="7"/>
       <c r="Z138" s="7"/>
       <c r="AA138" s="7"/>
@@ -8438,7 +8674,9 @@
       <c r="W139" s="12">
         <v>0</v>
       </c>
-      <c r="X139" s="7"/>
+      <c r="X139" s="12">
+        <v>0</v>
+      </c>
       <c r="Y139" s="7"/>
       <c r="Z139" s="7"/>
       <c r="AA139" s="7"/>
@@ -8488,7 +8726,9 @@
       <c r="W140" s="12">
         <v>0</v>
       </c>
-      <c r="X140" s="7"/>
+      <c r="X140" s="12">
+        <v>0</v>
+      </c>
       <c r="Y140" s="7"/>
       <c r="Z140" s="7"/>
       <c r="AA140" s="7"/>
@@ -8538,7 +8778,9 @@
       <c r="W141" s="12">
         <v>3</v>
       </c>
-      <c r="X141" s="7"/>
+      <c r="X141" s="12">
+        <v>3</v>
+      </c>
       <c r="Y141" s="7"/>
       <c r="Z141" s="7"/>
       <c r="AA141" s="7"/>
@@ -8588,7 +8830,9 @@
       <c r="W142" s="12">
         <v>0</v>
       </c>
-      <c r="X142" s="7"/>
+      <c r="X142" s="12">
+        <v>1</v>
+      </c>
       <c r="Y142" s="7"/>
       <c r="Z142" s="7"/>
       <c r="AA142" s="7"/>
@@ -8638,7 +8882,9 @@
       <c r="W143" s="12">
         <v>0</v>
       </c>
-      <c r="X143" s="7"/>
+      <c r="X143" s="12">
+        <v>3</v>
+      </c>
       <c r="Y143" s="7"/>
       <c r="Z143" s="7"/>
       <c r="AA143" s="7"/>
@@ -8688,7 +8934,9 @@
       <c r="W144" s="12">
         <v>3</v>
       </c>
-      <c r="X144" s="7"/>
+      <c r="X144" s="12">
+        <v>3</v>
+      </c>
       <c r="Y144" s="7"/>
       <c r="Z144" s="7"/>
       <c r="AA144" s="7"/>
@@ -8738,7 +8986,9 @@
       <c r="W145" s="12">
         <v>0</v>
       </c>
-      <c r="X145" s="7"/>
+      <c r="X145" s="12">
+        <v>0</v>
+      </c>
       <c r="Y145" s="7"/>
       <c r="Z145" s="7"/>
       <c r="AA145" s="7"/>
@@ -8788,7 +9038,9 @@
       <c r="W146" s="12">
         <v>0</v>
       </c>
-      <c r="X146" s="7"/>
+      <c r="X146" s="12">
+        <v>0</v>
+      </c>
       <c r="Y146" s="7"/>
       <c r="Z146" s="7"/>
       <c r="AA146" s="7"/>
@@ -8838,7 +9090,9 @@
       <c r="W147" s="12">
         <v>0</v>
       </c>
-      <c r="X147" s="7"/>
+      <c r="X147" s="12">
+        <v>3</v>
+      </c>
       <c r="Y147" s="7"/>
       <c r="Z147" s="7"/>
       <c r="AA147" s="7"/>
@@ -8888,7 +9142,9 @@
       <c r="W148" s="12">
         <v>0</v>
       </c>
-      <c r="X148" s="7"/>
+      <c r="X148" s="12">
+        <v>0</v>
+      </c>
       <c r="Y148" s="7"/>
       <c r="Z148" s="7"/>
       <c r="AA148" s="7"/>
@@ -8938,7 +9194,9 @@
       <c r="W149" s="12">
         <v>0</v>
       </c>
-      <c r="X149" s="7"/>
+      <c r="X149" s="12">
+        <v>3</v>
+      </c>
       <c r="Y149" s="7"/>
       <c r="Z149" s="7"/>
       <c r="AA149" s="7"/>
@@ -8988,7 +9246,9 @@
       <c r="W150" s="12">
         <v>3</v>
       </c>
-      <c r="X150" s="7"/>
+      <c r="X150" s="12">
+        <v>0</v>
+      </c>
       <c r="Y150" s="7"/>
       <c r="Z150" s="7"/>
       <c r="AA150" s="7"/>
@@ -9038,7 +9298,9 @@
       <c r="W151" s="12">
         <v>2</v>
       </c>
-      <c r="X151" s="7"/>
+      <c r="X151" s="12">
+        <v>3</v>
+      </c>
       <c r="Y151" s="7"/>
       <c r="Z151" s="7"/>
       <c r="AA151" s="7"/>
@@ -9088,7 +9350,9 @@
       <c r="W152" s="12">
         <v>3</v>
       </c>
-      <c r="X152" s="7"/>
+      <c r="X152" s="12">
+        <v>2</v>
+      </c>
       <c r="Y152" s="7"/>
       <c r="Z152" s="7"/>
       <c r="AA152" s="7"/>
@@ -9138,7 +9402,9 @@
       <c r="W153" s="12">
         <v>1</v>
       </c>
-      <c r="X153" s="7"/>
+      <c r="X153" s="12">
+        <v>0</v>
+      </c>
       <c r="Y153" s="7"/>
       <c r="Z153" s="7"/>
       <c r="AA153" s="7"/>
@@ -9188,7 +9454,9 @@
       <c r="W154" s="12">
         <v>0</v>
       </c>
-      <c r="X154" s="7"/>
+      <c r="X154" s="12">
+        <v>3</v>
+      </c>
       <c r="Y154" s="7"/>
       <c r="Z154" s="7"/>
       <c r="AA154" s="7"/>
@@ -9238,7 +9506,9 @@
       <c r="W155" s="12">
         <v>3</v>
       </c>
-      <c r="X155" s="7"/>
+      <c r="X155" s="12">
+        <v>3</v>
+      </c>
       <c r="Y155" s="7"/>
       <c r="Z155" s="7"/>
       <c r="AA155" s="7"/>
@@ -9288,7 +9558,9 @@
       <c r="W156" s="12">
         <v>3</v>
       </c>
-      <c r="X156" s="7"/>
+      <c r="X156" s="12">
+        <v>3</v>
+      </c>
       <c r="Y156" s="7"/>
       <c r="Z156" s="7"/>
       <c r="AA156" s="7"/>
@@ -9338,7 +9610,9 @@
       <c r="W157" s="12">
         <v>0</v>
       </c>
-      <c r="X157" s="7"/>
+      <c r="X157" s="12">
+        <v>0</v>
+      </c>
       <c r="Y157" s="7"/>
       <c r="Z157" s="7"/>
       <c r="AA157" s="7"/>
@@ -9388,7 +9662,9 @@
       <c r="W158" s="12">
         <v>3</v>
       </c>
-      <c r="X158" s="7"/>
+      <c r="X158" s="12">
+        <v>3</v>
+      </c>
       <c r="Y158" s="7"/>
       <c r="Z158" s="7"/>
       <c r="AA158" s="7"/>
@@ -9438,7 +9714,9 @@
       <c r="W159" s="12">
         <v>0</v>
       </c>
-      <c r="X159" s="7"/>
+      <c r="X159" s="12">
+        <v>0</v>
+      </c>
       <c r="Y159" s="7"/>
       <c r="Z159" s="7"/>
       <c r="AA159" s="7"/>
@@ -9488,7 +9766,9 @@
       <c r="W160" s="12">
         <v>0</v>
       </c>
-      <c r="X160" s="7"/>
+      <c r="X160" s="12">
+        <v>0</v>
+      </c>
       <c r="Y160" s="7"/>
       <c r="Z160" s="7"/>
       <c r="AA160" s="7"/>
@@ -9538,7 +9818,9 @@
       <c r="W161" s="12">
         <v>0</v>
       </c>
-      <c r="X161" s="7"/>
+      <c r="X161" s="12">
+        <v>0</v>
+      </c>
       <c r="Y161" s="7"/>
       <c r="Z161" s="7"/>
       <c r="AA161" s="7"/>
@@ -9588,7 +9870,9 @@
       <c r="W162" s="12">
         <v>0</v>
       </c>
-      <c r="X162" s="7"/>
+      <c r="X162" s="12">
+        <v>3</v>
+      </c>
       <c r="Y162" s="7"/>
       <c r="Z162" s="7"/>
       <c r="AA162" s="7"/>
@@ -9638,7 +9922,9 @@
       <c r="W163" s="12">
         <v>3</v>
       </c>
-      <c r="X163" s="7"/>
+      <c r="X163" s="12">
+        <v>3</v>
+      </c>
       <c r="Y163" s="7"/>
       <c r="Z163" s="7"/>
       <c r="AA163" s="7"/>
@@ -9688,7 +9974,9 @@
       <c r="W164" s="12">
         <v>0</v>
       </c>
-      <c r="X164" s="7"/>
+      <c r="X164" s="12">
+        <v>0</v>
+      </c>
       <c r="Y164" s="7"/>
       <c r="Z164" s="7"/>
       <c r="AA164" s="7"/>
@@ -9738,7 +10026,9 @@
       <c r="W165" s="12">
         <v>0</v>
       </c>
-      <c r="X165" s="7"/>
+      <c r="X165" s="12">
+        <v>3</v>
+      </c>
       <c r="Y165" s="7"/>
       <c r="Z165" s="7"/>
       <c r="AA165" s="7"/>
@@ -9779,28 +10069,28 @@
       <c r="V166"/>
     </row>
     <row r="167" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B167" s="24" t="s">
+      <c r="B167" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="C167" s="24"/>
-      <c r="D167" s="24"/>
-      <c r="E167" s="24"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="24"/>
-      <c r="H167" s="24"/>
-      <c r="I167" s="24"/>
-      <c r="J167" s="24"/>
-      <c r="K167" s="24"/>
-      <c r="L167" s="24"/>
-      <c r="M167" s="24"/>
-      <c r="N167" s="24"/>
-      <c r="O167" s="24"/>
-      <c r="P167" s="24"/>
-      <c r="Q167" s="24"/>
-      <c r="R167" s="24"/>
-      <c r="S167" s="24"/>
-      <c r="T167" s="24"/>
-      <c r="U167" s="24"/>
+      <c r="C167" s="21"/>
+      <c r="D167" s="21"/>
+      <c r="E167" s="21"/>
+      <c r="F167" s="21"/>
+      <c r="G167" s="21"/>
+      <c r="H167" s="21"/>
+      <c r="I167" s="21"/>
+      <c r="J167" s="21"/>
+      <c r="K167" s="21"/>
+      <c r="L167" s="21"/>
+      <c r="M167" s="21"/>
+      <c r="N167" s="21"/>
+      <c r="O167" s="21"/>
+      <c r="P167" s="21"/>
+      <c r="Q167" s="21"/>
+      <c r="R167" s="21"/>
+      <c r="S167" s="21"/>
+      <c r="T167" s="21"/>
+      <c r="U167" s="21"/>
       <c r="V167" s="8"/>
       <c r="W167" s="9"/>
       <c r="X167" s="9"/>
@@ -9819,26 +10109,26 @@
     </row>
     <row r="168" spans="1:36" ht="19.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168"/>
-      <c r="B168" s="25"/>
-      <c r="C168" s="26"/>
-      <c r="D168" s="26"/>
-      <c r="E168" s="26"/>
-      <c r="F168" s="26"/>
-      <c r="G168" s="26"/>
-      <c r="H168" s="26"/>
-      <c r="I168" s="26"/>
-      <c r="J168" s="26"/>
-      <c r="K168" s="26"/>
-      <c r="L168" s="26"/>
-      <c r="M168" s="26"/>
-      <c r="N168" s="26"/>
-      <c r="O168" s="26"/>
-      <c r="P168" s="26"/>
-      <c r="Q168" s="26"/>
-      <c r="R168" s="26"/>
-      <c r="S168" s="26"/>
-      <c r="T168" s="26"/>
-      <c r="U168" s="27"/>
+      <c r="B168" s="26"/>
+      <c r="C168" s="27"/>
+      <c r="D168" s="27"/>
+      <c r="E168" s="27"/>
+      <c r="F168" s="27"/>
+      <c r="G168" s="27"/>
+      <c r="H168" s="27"/>
+      <c r="I168" s="27"/>
+      <c r="J168" s="27"/>
+      <c r="K168" s="27"/>
+      <c r="L168" s="27"/>
+      <c r="M168" s="27"/>
+      <c r="N168" s="27"/>
+      <c r="O168" s="27"/>
+      <c r="P168" s="27"/>
+      <c r="Q168" s="27"/>
+      <c r="R168" s="27"/>
+      <c r="S168" s="27"/>
+      <c r="T168" s="27"/>
+      <c r="U168" s="28"/>
       <c r="V168" s="10">
         <v>0</v>
       </c>
@@ -9921,7 +10211,9 @@
       <c r="W169" s="13">
         <v>3</v>
       </c>
-      <c r="X169" s="4"/>
+      <c r="X169" s="13">
+        <v>0</v>
+      </c>
       <c r="Y169" s="4"/>
       <c r="Z169" s="4"/>
       <c r="AA169" s="4"/>
@@ -9971,7 +10263,9 @@
       <c r="W170" s="12">
         <v>0</v>
       </c>
-      <c r="X170" s="7"/>
+      <c r="X170" s="12">
+        <v>0</v>
+      </c>
       <c r="Y170" s="7"/>
       <c r="Z170" s="7"/>
       <c r="AA170" s="7"/>
@@ -10021,7 +10315,9 @@
       <c r="W171" s="12">
         <v>0</v>
       </c>
-      <c r="X171" s="7"/>
+      <c r="X171" s="12">
+        <v>3</v>
+      </c>
       <c r="Y171" s="7"/>
       <c r="Z171" s="7"/>
       <c r="AA171" s="7"/>
@@ -10071,7 +10367,9 @@
       <c r="W172" s="12">
         <v>3</v>
       </c>
-      <c r="X172" s="7"/>
+      <c r="X172" s="12">
+        <v>3</v>
+      </c>
       <c r="Y172" s="7"/>
       <c r="Z172" s="7"/>
       <c r="AA172" s="7"/>
@@ -10121,7 +10419,9 @@
       <c r="W173" s="12">
         <v>3</v>
       </c>
-      <c r="X173" s="7"/>
+      <c r="X173" s="12">
+        <v>3</v>
+      </c>
       <c r="Y173" s="7"/>
       <c r="Z173" s="7"/>
       <c r="AA173" s="7"/>
@@ -10171,7 +10471,9 @@
       <c r="W174" s="12">
         <v>3</v>
       </c>
-      <c r="X174" s="7"/>
+      <c r="X174" s="12">
+        <v>3</v>
+      </c>
       <c r="Y174" s="7"/>
       <c r="Z174" s="7"/>
       <c r="AA174" s="7"/>
@@ -10221,7 +10523,9 @@
       <c r="W175" s="12">
         <v>3</v>
       </c>
-      <c r="X175" s="7"/>
+      <c r="X175" s="12">
+        <v>3</v>
+      </c>
       <c r="Y175" s="7"/>
       <c r="Z175" s="7"/>
       <c r="AA175" s="7"/>
@@ -10271,7 +10575,9 @@
       <c r="W176" s="12">
         <v>2</v>
       </c>
-      <c r="X176" s="7"/>
+      <c r="X176" s="12">
+        <v>2</v>
+      </c>
       <c r="Y176" s="7"/>
       <c r="Z176" s="7"/>
       <c r="AA176" s="7"/>
@@ -10321,7 +10627,9 @@
       <c r="W177" s="12">
         <v>2</v>
       </c>
-      <c r="X177" s="7"/>
+      <c r="X177" s="12">
+        <v>0</v>
+      </c>
       <c r="Y177" s="7"/>
       <c r="Z177" s="7"/>
       <c r="AA177" s="7"/>
@@ -10371,7 +10679,9 @@
       <c r="W178" s="12">
         <v>0</v>
       </c>
-      <c r="X178" s="7"/>
+      <c r="X178" s="12">
+        <v>0</v>
+      </c>
       <c r="Y178" s="7"/>
       <c r="Z178" s="7"/>
       <c r="AA178" s="7"/>
@@ -10421,7 +10731,9 @@
       <c r="W179" s="12">
         <v>0</v>
       </c>
-      <c r="X179" s="7"/>
+      <c r="X179" s="12">
+        <v>0</v>
+      </c>
       <c r="Y179" s="7"/>
       <c r="Z179" s="7"/>
       <c r="AA179" s="7"/>
@@ -10471,7 +10783,9 @@
       <c r="W180" s="12">
         <v>3</v>
       </c>
-      <c r="X180" s="7"/>
+      <c r="X180" s="12">
+        <v>3</v>
+      </c>
       <c r="Y180" s="7"/>
       <c r="Z180" s="7"/>
       <c r="AA180" s="7"/>
@@ -10521,7 +10835,9 @@
       <c r="W181" s="12">
         <v>2</v>
       </c>
-      <c r="X181" s="7"/>
+      <c r="X181" s="12">
+        <v>3</v>
+      </c>
       <c r="Y181" s="7"/>
       <c r="Z181" s="7"/>
       <c r="AA181" s="7"/>
@@ -10571,7 +10887,9 @@
       <c r="W182" s="12">
         <v>1</v>
       </c>
-      <c r="X182" s="7"/>
+      <c r="X182" s="12">
+        <v>2</v>
+      </c>
       <c r="Y182" s="7"/>
       <c r="Z182" s="7"/>
       <c r="AA182" s="7"/>
@@ -10621,7 +10939,9 @@
       <c r="W183" s="12">
         <v>0</v>
       </c>
-      <c r="X183" s="7"/>
+      <c r="X183" s="12">
+        <v>0</v>
+      </c>
       <c r="Y183" s="7"/>
       <c r="Z183" s="7"/>
       <c r="AA183" s="7"/>
@@ -10671,7 +10991,9 @@
       <c r="W184" s="12">
         <v>0</v>
       </c>
-      <c r="X184" s="7"/>
+      <c r="X184" s="12">
+        <v>0</v>
+      </c>
       <c r="Y184" s="7"/>
       <c r="Z184" s="7"/>
       <c r="AA184" s="7"/>
@@ -10721,7 +11043,9 @@
       <c r="W185" s="12">
         <v>3</v>
       </c>
-      <c r="X185" s="7"/>
+      <c r="X185" s="12">
+        <v>3</v>
+      </c>
       <c r="Y185" s="7"/>
       <c r="Z185" s="7"/>
       <c r="AA185" s="7"/>
@@ -10771,7 +11095,9 @@
       <c r="W186" s="12">
         <v>0</v>
       </c>
-      <c r="X186" s="7"/>
+      <c r="X186" s="12">
+        <v>0</v>
+      </c>
       <c r="Y186" s="7"/>
       <c r="Z186" s="7"/>
       <c r="AA186" s="7"/>
@@ -10821,7 +11147,9 @@
       <c r="W187" s="12">
         <v>0</v>
       </c>
-      <c r="X187" s="7"/>
+      <c r="X187" s="12">
+        <v>0</v>
+      </c>
       <c r="Y187" s="7"/>
       <c r="Z187" s="7"/>
       <c r="AA187" s="7"/>
@@ -10866,12 +11194,14 @@
       <c r="T188" s="20"/>
       <c r="U188" s="20"/>
       <c r="V188" s="12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W188" s="12">
-        <v>0</v>
-      </c>
-      <c r="X188" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="X188" s="12">
+        <v>3</v>
+      </c>
       <c r="Y188" s="7"/>
       <c r="Z188" s="7"/>
       <c r="AA188" s="7"/>
@@ -10881,7 +11211,7 @@
       <c r="AE188" s="6"/>
       <c r="AF188" s="17">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG188" s="7"/>
       <c r="AH188" s="7"/>
@@ -10921,7 +11251,9 @@
       <c r="W189" s="12">
         <v>0</v>
       </c>
-      <c r="X189" s="7"/>
+      <c r="X189" s="12">
+        <v>0</v>
+      </c>
       <c r="Y189" s="7"/>
       <c r="Z189" s="7"/>
       <c r="AA189" s="7"/>
@@ -10971,7 +11303,9 @@
       <c r="W190" s="12">
         <v>0</v>
       </c>
-      <c r="X190" s="7"/>
+      <c r="X190" s="12">
+        <v>0</v>
+      </c>
       <c r="Y190" s="7"/>
       <c r="Z190" s="7"/>
       <c r="AA190" s="7"/>
@@ -11021,7 +11355,9 @@
       <c r="W191" s="12">
         <v>0</v>
       </c>
-      <c r="X191" s="7"/>
+      <c r="X191" s="12">
+        <v>1</v>
+      </c>
       <c r="Y191" s="7"/>
       <c r="Z191" s="7"/>
       <c r="AA191" s="7"/>
@@ -11071,7 +11407,9 @@
       <c r="W192" s="12">
         <v>0</v>
       </c>
-      <c r="X192" s="7"/>
+      <c r="X192" s="12">
+        <v>0</v>
+      </c>
       <c r="Y192" s="7"/>
       <c r="Z192" s="7"/>
       <c r="AA192" s="7"/>
@@ -11120,7 +11458,9 @@
       <c r="W193" s="12">
         <v>3</v>
       </c>
-      <c r="X193" s="7"/>
+      <c r="X193" s="12">
+        <v>3</v>
+      </c>
       <c r="Y193" s="7"/>
       <c r="Z193" s="7"/>
       <c r="AA193" s="7"/>
@@ -11169,7 +11509,9 @@
       <c r="W194" s="12">
         <v>3</v>
       </c>
-      <c r="X194" s="7"/>
+      <c r="X194" s="12">
+        <v>3</v>
+      </c>
       <c r="Y194" s="7"/>
       <c r="Z194" s="7"/>
       <c r="AA194" s="7"/>
@@ -11187,510 +11529,6 @@
     </row>
   </sheetData>
   <mergeCells count="528">
-    <mergeCell ref="B194:C194"/>
-    <mergeCell ref="D194:N194"/>
-    <mergeCell ref="O194:U194"/>
-    <mergeCell ref="B7:U7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:N9"/>
-    <mergeCell ref="O9:U9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:N10"/>
-    <mergeCell ref="O10:U10"/>
-    <mergeCell ref="B1:U1"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:N3"/>
-    <mergeCell ref="O3:U3"/>
-    <mergeCell ref="B5:U5"/>
-    <mergeCell ref="B8:U8"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:N13"/>
-    <mergeCell ref="O13:U13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:N14"/>
-    <mergeCell ref="O14:U14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:N11"/>
-    <mergeCell ref="O11:U11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:N12"/>
-    <mergeCell ref="O12:U12"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:N17"/>
-    <mergeCell ref="O17:U17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:N18"/>
-    <mergeCell ref="O18:U18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:N15"/>
-    <mergeCell ref="O15:U15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:N16"/>
-    <mergeCell ref="O16:U16"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:N21"/>
-    <mergeCell ref="O21:U21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:N22"/>
-    <mergeCell ref="O22:U22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:N19"/>
-    <mergeCell ref="O19:U19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:N20"/>
-    <mergeCell ref="O20:U20"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:N25"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:N26"/>
-    <mergeCell ref="O26:U26"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:N23"/>
-    <mergeCell ref="O23:U23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:N24"/>
-    <mergeCell ref="O24:U24"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:N29"/>
-    <mergeCell ref="O29:U29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:N30"/>
-    <mergeCell ref="O30:U30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:N27"/>
-    <mergeCell ref="O27:U27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:N28"/>
-    <mergeCell ref="O28:U28"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:N33"/>
-    <mergeCell ref="O33:U33"/>
-    <mergeCell ref="B35:U35"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:N37"/>
-    <mergeCell ref="O37:U37"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:N31"/>
-    <mergeCell ref="O31:U31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:N32"/>
-    <mergeCell ref="O32:U32"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:N40"/>
-    <mergeCell ref="O40:U40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:N41"/>
-    <mergeCell ref="O41:U41"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:N38"/>
-    <mergeCell ref="O38:U38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:N39"/>
-    <mergeCell ref="O39:U39"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:N44"/>
-    <mergeCell ref="O44:U44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:N45"/>
-    <mergeCell ref="O45:U45"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:N42"/>
-    <mergeCell ref="O42:U42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:N43"/>
-    <mergeCell ref="O43:U43"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:N48"/>
-    <mergeCell ref="O48:U48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:N49"/>
-    <mergeCell ref="O49:U49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:N46"/>
-    <mergeCell ref="O46:U46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:N47"/>
-    <mergeCell ref="O47:U47"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:N52"/>
-    <mergeCell ref="O52:U52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:N53"/>
-    <mergeCell ref="O53:U53"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:N50"/>
-    <mergeCell ref="O50:U50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:N51"/>
-    <mergeCell ref="O51:U51"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:N56"/>
-    <mergeCell ref="O56:U56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:N57"/>
-    <mergeCell ref="O57:U57"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:N54"/>
-    <mergeCell ref="O54:U54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:N55"/>
-    <mergeCell ref="O55:U55"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:N60"/>
-    <mergeCell ref="O60:U60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="D61:N61"/>
-    <mergeCell ref="O61:U61"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:N58"/>
-    <mergeCell ref="O58:U58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:N59"/>
-    <mergeCell ref="O59:U59"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="D64:N64"/>
-    <mergeCell ref="O64:U64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:N65"/>
-    <mergeCell ref="O65:U65"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:N62"/>
-    <mergeCell ref="O62:U62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D63:N63"/>
-    <mergeCell ref="O63:U63"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="D71:N71"/>
-    <mergeCell ref="O71:U71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="D72:N72"/>
-    <mergeCell ref="O72:U72"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="D66:N66"/>
-    <mergeCell ref="O66:U66"/>
-    <mergeCell ref="B68:U68"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="D70:N70"/>
-    <mergeCell ref="O70:U70"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="D75:N75"/>
-    <mergeCell ref="O75:U75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="D76:N76"/>
-    <mergeCell ref="O76:U76"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="D73:N73"/>
-    <mergeCell ref="O73:U73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="D74:N74"/>
-    <mergeCell ref="O74:U74"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="D79:N79"/>
-    <mergeCell ref="O79:U79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="D80:N80"/>
-    <mergeCell ref="O80:U80"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="D77:N77"/>
-    <mergeCell ref="O77:U77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="D78:N78"/>
-    <mergeCell ref="O78:U78"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="D83:N83"/>
-    <mergeCell ref="O83:U83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="D84:N84"/>
-    <mergeCell ref="O84:U84"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="D81:N81"/>
-    <mergeCell ref="O81:U81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:N82"/>
-    <mergeCell ref="O82:U82"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="D87:N87"/>
-    <mergeCell ref="O87:U87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="D88:N88"/>
-    <mergeCell ref="O88:U88"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="D85:N85"/>
-    <mergeCell ref="O85:U85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="D86:N86"/>
-    <mergeCell ref="O86:U86"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="D91:N91"/>
-    <mergeCell ref="O91:U91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="D92:N92"/>
-    <mergeCell ref="O92:U92"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="D89:N89"/>
-    <mergeCell ref="O89:U89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="D90:N90"/>
-    <mergeCell ref="O90:U90"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="D95:N95"/>
-    <mergeCell ref="O95:U95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="D96:N96"/>
-    <mergeCell ref="O96:U96"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="D93:N93"/>
-    <mergeCell ref="O93:U93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="D94:N94"/>
-    <mergeCell ref="O94:U94"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:N99"/>
-    <mergeCell ref="O99:U99"/>
-    <mergeCell ref="B101:U101"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="D103:N103"/>
-    <mergeCell ref="O103:U103"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="D97:N97"/>
-    <mergeCell ref="O97:U97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="D98:N98"/>
-    <mergeCell ref="O98:U98"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="D106:N106"/>
-    <mergeCell ref="O106:U106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="D107:N107"/>
-    <mergeCell ref="O107:U107"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="D104:N104"/>
-    <mergeCell ref="O104:U104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="D105:N105"/>
-    <mergeCell ref="O105:U105"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="D110:N110"/>
-    <mergeCell ref="O110:U110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="D111:N111"/>
-    <mergeCell ref="O111:U111"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="D108:N108"/>
-    <mergeCell ref="O108:U108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="D109:N109"/>
-    <mergeCell ref="O109:U109"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="D114:N114"/>
-    <mergeCell ref="O114:U114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="D115:N115"/>
-    <mergeCell ref="O115:U115"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="D112:N112"/>
-    <mergeCell ref="O112:U112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="D113:N113"/>
-    <mergeCell ref="O113:U113"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="D118:N118"/>
-    <mergeCell ref="O118:U118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="D119:N119"/>
-    <mergeCell ref="O119:U119"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="D116:N116"/>
-    <mergeCell ref="O116:U116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="D117:N117"/>
-    <mergeCell ref="O117:U117"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="D122:N122"/>
-    <mergeCell ref="O122:U122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="D123:N123"/>
-    <mergeCell ref="O123:U123"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="D120:N120"/>
-    <mergeCell ref="O120:U120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="D121:N121"/>
-    <mergeCell ref="O121:U121"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="D126:N126"/>
-    <mergeCell ref="O126:U126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="D127:N127"/>
-    <mergeCell ref="O127:U127"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="D124:N124"/>
-    <mergeCell ref="O124:U124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="D125:N125"/>
-    <mergeCell ref="O125:U125"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="D130:N130"/>
-    <mergeCell ref="O130:U130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="D131:N131"/>
-    <mergeCell ref="O131:U131"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="D128:N128"/>
-    <mergeCell ref="O128:U128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="D129:N129"/>
-    <mergeCell ref="O129:U129"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="D137:N137"/>
-    <mergeCell ref="O137:U137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="D138:N138"/>
-    <mergeCell ref="O138:U138"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="D132:N132"/>
-    <mergeCell ref="O132:U132"/>
-    <mergeCell ref="B134:U134"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="D136:N136"/>
-    <mergeCell ref="O136:U136"/>
-    <mergeCell ref="B135:U135"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="D141:N141"/>
-    <mergeCell ref="O141:U141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="D142:N142"/>
-    <mergeCell ref="O142:U142"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="D139:N139"/>
-    <mergeCell ref="O139:U139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="D140:N140"/>
-    <mergeCell ref="O140:U140"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="D145:N145"/>
-    <mergeCell ref="O145:U145"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="D146:N146"/>
-    <mergeCell ref="O146:U146"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="D143:N143"/>
-    <mergeCell ref="O143:U143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="D144:N144"/>
-    <mergeCell ref="O144:U144"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="D149:N149"/>
-    <mergeCell ref="O149:U149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="D150:N150"/>
-    <mergeCell ref="O150:U150"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="D147:N147"/>
-    <mergeCell ref="O147:U147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="D148:N148"/>
-    <mergeCell ref="O148:U148"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="D153:N153"/>
-    <mergeCell ref="O153:U153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="D154:N154"/>
-    <mergeCell ref="O154:U154"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="D151:N151"/>
-    <mergeCell ref="O151:U151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="D152:N152"/>
-    <mergeCell ref="O152:U152"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="D157:N157"/>
-    <mergeCell ref="O157:U157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="D158:N158"/>
-    <mergeCell ref="O158:U158"/>
-    <mergeCell ref="B155:C155"/>
-    <mergeCell ref="D155:N155"/>
-    <mergeCell ref="O155:U155"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="D156:N156"/>
-    <mergeCell ref="O156:U156"/>
-    <mergeCell ref="B161:C161"/>
-    <mergeCell ref="D161:N161"/>
-    <mergeCell ref="O161:U161"/>
-    <mergeCell ref="B162:C162"/>
-    <mergeCell ref="D162:N162"/>
-    <mergeCell ref="O162:U162"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="D159:N159"/>
-    <mergeCell ref="O159:U159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="D160:N160"/>
-    <mergeCell ref="O160:U160"/>
-    <mergeCell ref="B165:C165"/>
-    <mergeCell ref="D165:N165"/>
-    <mergeCell ref="O165:U165"/>
-    <mergeCell ref="B167:U167"/>
-    <mergeCell ref="B169:C169"/>
-    <mergeCell ref="D169:N169"/>
-    <mergeCell ref="O169:U169"/>
-    <mergeCell ref="B163:C163"/>
-    <mergeCell ref="D163:N163"/>
-    <mergeCell ref="O163:U163"/>
-    <mergeCell ref="B164:C164"/>
-    <mergeCell ref="D164:N164"/>
-    <mergeCell ref="O164:U164"/>
-    <mergeCell ref="B168:U168"/>
-    <mergeCell ref="B172:C172"/>
-    <mergeCell ref="D172:N172"/>
-    <mergeCell ref="O172:U172"/>
-    <mergeCell ref="B173:C173"/>
-    <mergeCell ref="D173:N173"/>
-    <mergeCell ref="O173:U173"/>
-    <mergeCell ref="B170:C170"/>
-    <mergeCell ref="D170:N170"/>
-    <mergeCell ref="O170:U170"/>
-    <mergeCell ref="B171:C171"/>
-    <mergeCell ref="D171:N171"/>
-    <mergeCell ref="O171:U171"/>
-    <mergeCell ref="B176:C176"/>
-    <mergeCell ref="D176:N176"/>
-    <mergeCell ref="O176:U176"/>
-    <mergeCell ref="B177:C177"/>
-    <mergeCell ref="D177:N177"/>
-    <mergeCell ref="O177:U177"/>
-    <mergeCell ref="B174:C174"/>
-    <mergeCell ref="D174:N174"/>
-    <mergeCell ref="O174:U174"/>
-    <mergeCell ref="B175:C175"/>
-    <mergeCell ref="D175:N175"/>
-    <mergeCell ref="O175:U175"/>
-    <mergeCell ref="B180:C180"/>
-    <mergeCell ref="D180:N180"/>
-    <mergeCell ref="O180:U180"/>
-    <mergeCell ref="B181:C181"/>
-    <mergeCell ref="D181:N181"/>
-    <mergeCell ref="O181:U181"/>
-    <mergeCell ref="B178:C178"/>
-    <mergeCell ref="D178:N178"/>
-    <mergeCell ref="O178:U178"/>
-    <mergeCell ref="B179:C179"/>
-    <mergeCell ref="D179:N179"/>
-    <mergeCell ref="O179:U179"/>
-    <mergeCell ref="O187:U187"/>
-    <mergeCell ref="B184:C184"/>
-    <mergeCell ref="D184:N184"/>
-    <mergeCell ref="O184:U184"/>
-    <mergeCell ref="B185:C185"/>
-    <mergeCell ref="D185:N185"/>
-    <mergeCell ref="O185:U185"/>
-    <mergeCell ref="B182:C182"/>
-    <mergeCell ref="D182:N182"/>
-    <mergeCell ref="O182:U182"/>
-    <mergeCell ref="B183:C183"/>
-    <mergeCell ref="D183:N183"/>
-    <mergeCell ref="O183:U183"/>
     <mergeCell ref="B193:C193"/>
     <mergeCell ref="D193:N193"/>
     <mergeCell ref="O193:U193"/>
@@ -11715,6 +11553,510 @@
     <mergeCell ref="O186:U186"/>
     <mergeCell ref="B187:C187"/>
     <mergeCell ref="D187:N187"/>
+    <mergeCell ref="O187:U187"/>
+    <mergeCell ref="B184:C184"/>
+    <mergeCell ref="D184:N184"/>
+    <mergeCell ref="O184:U184"/>
+    <mergeCell ref="B185:C185"/>
+    <mergeCell ref="D185:N185"/>
+    <mergeCell ref="O185:U185"/>
+    <mergeCell ref="B182:C182"/>
+    <mergeCell ref="D182:N182"/>
+    <mergeCell ref="O182:U182"/>
+    <mergeCell ref="B183:C183"/>
+    <mergeCell ref="D183:N183"/>
+    <mergeCell ref="O183:U183"/>
+    <mergeCell ref="B180:C180"/>
+    <mergeCell ref="D180:N180"/>
+    <mergeCell ref="O180:U180"/>
+    <mergeCell ref="B181:C181"/>
+    <mergeCell ref="D181:N181"/>
+    <mergeCell ref="O181:U181"/>
+    <mergeCell ref="B178:C178"/>
+    <mergeCell ref="D178:N178"/>
+    <mergeCell ref="O178:U178"/>
+    <mergeCell ref="B179:C179"/>
+    <mergeCell ref="D179:N179"/>
+    <mergeCell ref="O179:U179"/>
+    <mergeCell ref="B176:C176"/>
+    <mergeCell ref="D176:N176"/>
+    <mergeCell ref="O176:U176"/>
+    <mergeCell ref="B177:C177"/>
+    <mergeCell ref="D177:N177"/>
+    <mergeCell ref="O177:U177"/>
+    <mergeCell ref="B174:C174"/>
+    <mergeCell ref="D174:N174"/>
+    <mergeCell ref="O174:U174"/>
+    <mergeCell ref="B175:C175"/>
+    <mergeCell ref="D175:N175"/>
+    <mergeCell ref="O175:U175"/>
+    <mergeCell ref="B172:C172"/>
+    <mergeCell ref="D172:N172"/>
+    <mergeCell ref="O172:U172"/>
+    <mergeCell ref="B173:C173"/>
+    <mergeCell ref="D173:N173"/>
+    <mergeCell ref="O173:U173"/>
+    <mergeCell ref="B170:C170"/>
+    <mergeCell ref="D170:N170"/>
+    <mergeCell ref="O170:U170"/>
+    <mergeCell ref="B171:C171"/>
+    <mergeCell ref="D171:N171"/>
+    <mergeCell ref="O171:U171"/>
+    <mergeCell ref="B165:C165"/>
+    <mergeCell ref="D165:N165"/>
+    <mergeCell ref="O165:U165"/>
+    <mergeCell ref="B167:U167"/>
+    <mergeCell ref="B169:C169"/>
+    <mergeCell ref="D169:N169"/>
+    <mergeCell ref="O169:U169"/>
+    <mergeCell ref="B163:C163"/>
+    <mergeCell ref="D163:N163"/>
+    <mergeCell ref="O163:U163"/>
+    <mergeCell ref="B164:C164"/>
+    <mergeCell ref="D164:N164"/>
+    <mergeCell ref="O164:U164"/>
+    <mergeCell ref="B168:U168"/>
+    <mergeCell ref="B161:C161"/>
+    <mergeCell ref="D161:N161"/>
+    <mergeCell ref="O161:U161"/>
+    <mergeCell ref="B162:C162"/>
+    <mergeCell ref="D162:N162"/>
+    <mergeCell ref="O162:U162"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="D159:N159"/>
+    <mergeCell ref="O159:U159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="D160:N160"/>
+    <mergeCell ref="O160:U160"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="D157:N157"/>
+    <mergeCell ref="O157:U157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="D158:N158"/>
+    <mergeCell ref="O158:U158"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="D155:N155"/>
+    <mergeCell ref="O155:U155"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="D156:N156"/>
+    <mergeCell ref="O156:U156"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="D153:N153"/>
+    <mergeCell ref="O153:U153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="D154:N154"/>
+    <mergeCell ref="O154:U154"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="D151:N151"/>
+    <mergeCell ref="O151:U151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="D152:N152"/>
+    <mergeCell ref="O152:U152"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="D149:N149"/>
+    <mergeCell ref="O149:U149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="D150:N150"/>
+    <mergeCell ref="O150:U150"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="D147:N147"/>
+    <mergeCell ref="O147:U147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="D148:N148"/>
+    <mergeCell ref="O148:U148"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="D145:N145"/>
+    <mergeCell ref="O145:U145"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="D146:N146"/>
+    <mergeCell ref="O146:U146"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="D143:N143"/>
+    <mergeCell ref="O143:U143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="D144:N144"/>
+    <mergeCell ref="O144:U144"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="D141:N141"/>
+    <mergeCell ref="O141:U141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="D142:N142"/>
+    <mergeCell ref="O142:U142"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="D139:N139"/>
+    <mergeCell ref="O139:U139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="D140:N140"/>
+    <mergeCell ref="O140:U140"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="D137:N137"/>
+    <mergeCell ref="O137:U137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="D138:N138"/>
+    <mergeCell ref="O138:U138"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="D132:N132"/>
+    <mergeCell ref="O132:U132"/>
+    <mergeCell ref="B134:U134"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="D136:N136"/>
+    <mergeCell ref="O136:U136"/>
+    <mergeCell ref="B135:U135"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="D130:N130"/>
+    <mergeCell ref="O130:U130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="D131:N131"/>
+    <mergeCell ref="O131:U131"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="D128:N128"/>
+    <mergeCell ref="O128:U128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="D129:N129"/>
+    <mergeCell ref="O129:U129"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="D126:N126"/>
+    <mergeCell ref="O126:U126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="D127:N127"/>
+    <mergeCell ref="O127:U127"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="D124:N124"/>
+    <mergeCell ref="O124:U124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="D125:N125"/>
+    <mergeCell ref="O125:U125"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="D122:N122"/>
+    <mergeCell ref="O122:U122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="D123:N123"/>
+    <mergeCell ref="O123:U123"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="D120:N120"/>
+    <mergeCell ref="O120:U120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="D121:N121"/>
+    <mergeCell ref="O121:U121"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="D118:N118"/>
+    <mergeCell ref="O118:U118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="D119:N119"/>
+    <mergeCell ref="O119:U119"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="D116:N116"/>
+    <mergeCell ref="O116:U116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="D117:N117"/>
+    <mergeCell ref="O117:U117"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="D114:N114"/>
+    <mergeCell ref="O114:U114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="D115:N115"/>
+    <mergeCell ref="O115:U115"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="D112:N112"/>
+    <mergeCell ref="O112:U112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="D113:N113"/>
+    <mergeCell ref="O113:U113"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="D110:N110"/>
+    <mergeCell ref="O110:U110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="D111:N111"/>
+    <mergeCell ref="O111:U111"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="D108:N108"/>
+    <mergeCell ref="O108:U108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="D109:N109"/>
+    <mergeCell ref="O109:U109"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="D106:N106"/>
+    <mergeCell ref="O106:U106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="D107:N107"/>
+    <mergeCell ref="O107:U107"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="D104:N104"/>
+    <mergeCell ref="O104:U104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="D105:N105"/>
+    <mergeCell ref="O105:U105"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:N99"/>
+    <mergeCell ref="O99:U99"/>
+    <mergeCell ref="B101:U101"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="D103:N103"/>
+    <mergeCell ref="O103:U103"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="D97:N97"/>
+    <mergeCell ref="O97:U97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="D98:N98"/>
+    <mergeCell ref="O98:U98"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="D95:N95"/>
+    <mergeCell ref="O95:U95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="D96:N96"/>
+    <mergeCell ref="O96:U96"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="D93:N93"/>
+    <mergeCell ref="O93:U93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="D94:N94"/>
+    <mergeCell ref="O94:U94"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="D91:N91"/>
+    <mergeCell ref="O91:U91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="D92:N92"/>
+    <mergeCell ref="O92:U92"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="D89:N89"/>
+    <mergeCell ref="O89:U89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="D90:N90"/>
+    <mergeCell ref="O90:U90"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="D87:N87"/>
+    <mergeCell ref="O87:U87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="D88:N88"/>
+    <mergeCell ref="O88:U88"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="D85:N85"/>
+    <mergeCell ref="O85:U85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="D86:N86"/>
+    <mergeCell ref="O86:U86"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="D83:N83"/>
+    <mergeCell ref="O83:U83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="D84:N84"/>
+    <mergeCell ref="O84:U84"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="D81:N81"/>
+    <mergeCell ref="O81:U81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:N82"/>
+    <mergeCell ref="O82:U82"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="D79:N79"/>
+    <mergeCell ref="O79:U79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="D80:N80"/>
+    <mergeCell ref="O80:U80"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="D77:N77"/>
+    <mergeCell ref="O77:U77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="D78:N78"/>
+    <mergeCell ref="O78:U78"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="D75:N75"/>
+    <mergeCell ref="O75:U75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="D76:N76"/>
+    <mergeCell ref="O76:U76"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="D73:N73"/>
+    <mergeCell ref="O73:U73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="D74:N74"/>
+    <mergeCell ref="O74:U74"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="D71:N71"/>
+    <mergeCell ref="O71:U71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="D72:N72"/>
+    <mergeCell ref="O72:U72"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="D66:N66"/>
+    <mergeCell ref="O66:U66"/>
+    <mergeCell ref="B68:U68"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="D70:N70"/>
+    <mergeCell ref="O70:U70"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:N64"/>
+    <mergeCell ref="O64:U64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:N65"/>
+    <mergeCell ref="O65:U65"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:N62"/>
+    <mergeCell ref="O62:U62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D63:N63"/>
+    <mergeCell ref="O63:U63"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:N60"/>
+    <mergeCell ref="O60:U60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:N61"/>
+    <mergeCell ref="O61:U61"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:N58"/>
+    <mergeCell ref="O58:U58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:N59"/>
+    <mergeCell ref="O59:U59"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:N56"/>
+    <mergeCell ref="O56:U56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:N57"/>
+    <mergeCell ref="O57:U57"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:N54"/>
+    <mergeCell ref="O54:U54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:N55"/>
+    <mergeCell ref="O55:U55"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:N52"/>
+    <mergeCell ref="O52:U52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:N53"/>
+    <mergeCell ref="O53:U53"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:N50"/>
+    <mergeCell ref="O50:U50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:N51"/>
+    <mergeCell ref="O51:U51"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:N48"/>
+    <mergeCell ref="O48:U48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:N49"/>
+    <mergeCell ref="O49:U49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:N46"/>
+    <mergeCell ref="O46:U46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:N47"/>
+    <mergeCell ref="O47:U47"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:N44"/>
+    <mergeCell ref="O44:U44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:N45"/>
+    <mergeCell ref="O45:U45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:N42"/>
+    <mergeCell ref="O42:U42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:N43"/>
+    <mergeCell ref="O43:U43"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:N40"/>
+    <mergeCell ref="O40:U40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:N41"/>
+    <mergeCell ref="O41:U41"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:N38"/>
+    <mergeCell ref="O38:U38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:N39"/>
+    <mergeCell ref="O39:U39"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:N33"/>
+    <mergeCell ref="O33:U33"/>
+    <mergeCell ref="B35:U35"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:N37"/>
+    <mergeCell ref="O37:U37"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:N31"/>
+    <mergeCell ref="O31:U31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:N32"/>
+    <mergeCell ref="O32:U32"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:N29"/>
+    <mergeCell ref="O29:U29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:N30"/>
+    <mergeCell ref="O30:U30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:N27"/>
+    <mergeCell ref="O27:U27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:N28"/>
+    <mergeCell ref="O28:U28"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:N25"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:N26"/>
+    <mergeCell ref="O26:U26"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:N23"/>
+    <mergeCell ref="O23:U23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:N24"/>
+    <mergeCell ref="O24:U24"/>
+    <mergeCell ref="O16:U16"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:N21"/>
+    <mergeCell ref="O21:U21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:N22"/>
+    <mergeCell ref="O22:U22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:N19"/>
+    <mergeCell ref="O19:U19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:N20"/>
+    <mergeCell ref="O20:U20"/>
+    <mergeCell ref="B1:U1"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:N3"/>
+    <mergeCell ref="O3:U3"/>
+    <mergeCell ref="B5:U5"/>
+    <mergeCell ref="B8:U8"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:N13"/>
+    <mergeCell ref="O13:U13"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:N11"/>
+    <mergeCell ref="O11:U11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:N12"/>
+    <mergeCell ref="O12:U12"/>
+    <mergeCell ref="B194:C194"/>
+    <mergeCell ref="D194:N194"/>
+    <mergeCell ref="O194:U194"/>
+    <mergeCell ref="B7:U7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:N9"/>
+    <mergeCell ref="O9:U9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:N10"/>
+    <mergeCell ref="O10:U10"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:N14"/>
+    <mergeCell ref="O14:U14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:N17"/>
+    <mergeCell ref="O17:U17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:N18"/>
+    <mergeCell ref="O18:U18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:N15"/>
+    <mergeCell ref="O15:U15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:N16"/>
   </mergeCells>
   <pageMargins left="0.39370078740157477" right="0.39370078740157477" top="0.39370078740157477" bottom="0.39370078740157477" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>

--- a/Журнал.xlsx
+++ b/Журнал.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1-семестр" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="145621" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1293,8 +1293,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1307,24 +1325,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1718,70 +1718,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
     </row>
     <row r="2" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="24" t="s">
+      <c r="B3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="23" t="s">
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="T3" s="23"/>
-      <c r="U3" s="23"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="30"/>
-      <c r="AF3" s="30"/>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="31"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
+      <c r="Y3" s="22"/>
+      <c r="Z3" s="22"/>
+      <c r="AA3" s="22"/>
+      <c r="AB3" s="22"/>
+      <c r="AC3" s="22"/>
+      <c r="AD3" s="22"/>
+      <c r="AE3" s="22"/>
+      <c r="AF3" s="22"/>
+      <c r="AG3" s="22"/>
+      <c r="AH3" s="22"/>
+      <c r="AI3" s="23"/>
     </row>
     <row r="4" spans="1:35" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4"/>
@@ -1808,28 +1808,28 @@
       <c r="V4"/>
     </row>
     <row r="5" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
+      <c r="B5" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="31"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="31"/>
+      <c r="U5" s="31"/>
       <c r="V5" s="8"/>
       <c r="W5" s="9"/>
       <c r="X5" s="9"/>
@@ -1870,28 +1870,28 @@
       <c r="V6"/>
     </row>
     <row r="7" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
-      <c r="T7" s="21"/>
-      <c r="U7" s="21"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="24"/>
       <c r="V7" s="8"/>
       <c r="W7" s="9"/>
       <c r="X7" s="9"/>
@@ -1909,26 +1909,26 @@
     </row>
     <row r="8" spans="1:35" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="27"/>
-      <c r="R8" s="27"/>
-      <c r="S8" s="27"/>
-      <c r="T8" s="27"/>
-      <c r="U8" s="28"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="27"/>
       <c r="V8" s="10">
         <v>0</v>
       </c>
@@ -3301,28 +3301,28 @@
       <c r="V34"/>
     </row>
     <row r="35" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
-      <c r="M35" s="21"/>
-      <c r="N35" s="21"/>
-      <c r="O35" s="21"/>
-      <c r="P35" s="21"/>
-      <c r="Q35" s="21"/>
-      <c r="R35" s="21"/>
-      <c r="S35" s="21"/>
-      <c r="T35" s="21"/>
-      <c r="U35" s="21"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="24"/>
+      <c r="Q35" s="24"/>
+      <c r="R35" s="24"/>
+      <c r="S35" s="24"/>
+      <c r="T35" s="24"/>
+      <c r="U35" s="24"/>
       <c r="V35" s="8"/>
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
@@ -4993,28 +4993,28 @@
     </row>
     <row r="68" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
-      <c r="B68" s="21" t="s">
+      <c r="B68" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="21"/>
-      <c r="L68" s="21"/>
-      <c r="M68" s="21"/>
-      <c r="N68" s="21"/>
-      <c r="O68" s="21"/>
-      <c r="P68" s="21"/>
-      <c r="Q68" s="21"/>
-      <c r="R68" s="21"/>
-      <c r="S68" s="21"/>
-      <c r="T68" s="21"/>
-      <c r="U68" s="21"/>
+      <c r="C68" s="24"/>
+      <c r="D68" s="24"/>
+      <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="24"/>
+      <c r="J68" s="24"/>
+      <c r="K68" s="24"/>
+      <c r="L68" s="24"/>
+      <c r="M68" s="24"/>
+      <c r="N68" s="24"/>
+      <c r="O68" s="24"/>
+      <c r="P68" s="24"/>
+      <c r="Q68" s="24"/>
+      <c r="R68" s="24"/>
+      <c r="S68" s="24"/>
+      <c r="T68" s="24"/>
+      <c r="U68" s="24"/>
       <c r="V68" s="8"/>
       <c r="W68" s="9"/>
       <c r="X68" s="9"/>
@@ -6685,28 +6685,28 @@
       <c r="V100"/>
     </row>
     <row r="101" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B101" s="21" t="s">
+      <c r="B101" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="C101" s="21"/>
-      <c r="D101" s="21"/>
-      <c r="E101" s="21"/>
-      <c r="F101" s="21"/>
-      <c r="G101" s="21"/>
-      <c r="H101" s="21"/>
-      <c r="I101" s="21"/>
-      <c r="J101" s="21"/>
-      <c r="K101" s="21"/>
-      <c r="L101" s="21"/>
-      <c r="M101" s="21"/>
-      <c r="N101" s="21"/>
-      <c r="O101" s="21"/>
-      <c r="P101" s="21"/>
-      <c r="Q101" s="21"/>
-      <c r="R101" s="21"/>
-      <c r="S101" s="21"/>
-      <c r="T101" s="21"/>
-      <c r="U101" s="21"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+      <c r="I101" s="24"/>
+      <c r="J101" s="24"/>
+      <c r="K101" s="24"/>
+      <c r="L101" s="24"/>
+      <c r="M101" s="24"/>
+      <c r="N101" s="24"/>
+      <c r="O101" s="24"/>
+      <c r="P101" s="24"/>
+      <c r="Q101" s="24"/>
+      <c r="R101" s="24"/>
+      <c r="S101" s="24"/>
+      <c r="T101" s="24"/>
+      <c r="U101" s="24"/>
       <c r="V101" s="8"/>
       <c r="W101" s="9"/>
       <c r="X101" s="9"/>
@@ -8377,28 +8377,28 @@
       <c r="V133"/>
     </row>
     <row r="134" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B134" s="21" t="s">
+      <c r="B134" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="C134" s="21"/>
-      <c r="D134" s="21"/>
-      <c r="E134" s="21"/>
-      <c r="F134" s="21"/>
-      <c r="G134" s="21"/>
-      <c r="H134" s="21"/>
-      <c r="I134" s="21"/>
-      <c r="J134" s="21"/>
-      <c r="K134" s="21"/>
-      <c r="L134" s="21"/>
-      <c r="M134" s="21"/>
-      <c r="N134" s="21"/>
-      <c r="O134" s="21"/>
-      <c r="P134" s="21"/>
-      <c r="Q134" s="21"/>
-      <c r="R134" s="21"/>
-      <c r="S134" s="21"/>
-      <c r="T134" s="21"/>
-      <c r="U134" s="21"/>
+      <c r="C134" s="24"/>
+      <c r="D134" s="24"/>
+      <c r="E134" s="24"/>
+      <c r="F134" s="24"/>
+      <c r="G134" s="24"/>
+      <c r="H134" s="24"/>
+      <c r="I134" s="24"/>
+      <c r="J134" s="24"/>
+      <c r="K134" s="24"/>
+      <c r="L134" s="24"/>
+      <c r="M134" s="24"/>
+      <c r="N134" s="24"/>
+      <c r="O134" s="24"/>
+      <c r="P134" s="24"/>
+      <c r="Q134" s="24"/>
+      <c r="R134" s="24"/>
+      <c r="S134" s="24"/>
+      <c r="T134" s="24"/>
+      <c r="U134" s="24"/>
       <c r="V134" s="8"/>
       <c r="W134" s="9"/>
       <c r="X134" s="9"/>
@@ -8417,26 +8417,26 @@
     </row>
     <row r="135" spans="1:36" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135"/>
-      <c r="B135" s="26"/>
-      <c r="C135" s="27"/>
-      <c r="D135" s="27"/>
-      <c r="E135" s="27"/>
-      <c r="F135" s="27"/>
-      <c r="G135" s="27"/>
-      <c r="H135" s="27"/>
-      <c r="I135" s="27"/>
-      <c r="J135" s="27"/>
-      <c r="K135" s="27"/>
-      <c r="L135" s="27"/>
-      <c r="M135" s="27"/>
-      <c r="N135" s="27"/>
-      <c r="O135" s="27"/>
-      <c r="P135" s="27"/>
-      <c r="Q135" s="27"/>
-      <c r="R135" s="27"/>
-      <c r="S135" s="27"/>
-      <c r="T135" s="27"/>
-      <c r="U135" s="28"/>
+      <c r="B135" s="25"/>
+      <c r="C135" s="26"/>
+      <c r="D135" s="26"/>
+      <c r="E135" s="26"/>
+      <c r="F135" s="26"/>
+      <c r="G135" s="26"/>
+      <c r="H135" s="26"/>
+      <c r="I135" s="26"/>
+      <c r="J135" s="26"/>
+      <c r="K135" s="26"/>
+      <c r="L135" s="26"/>
+      <c r="M135" s="26"/>
+      <c r="N135" s="26"/>
+      <c r="O135" s="26"/>
+      <c r="P135" s="26"/>
+      <c r="Q135" s="26"/>
+      <c r="R135" s="26"/>
+      <c r="S135" s="26"/>
+      <c r="T135" s="26"/>
+      <c r="U135" s="27"/>
       <c r="V135" s="10">
         <v>0</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>3</v>
       </c>
       <c r="W147" s="12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X147" s="12">
         <v>3</v>
@@ -9102,7 +9102,7 @@
       <c r="AE147" s="6"/>
       <c r="AF147" s="17">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG147" s="7"/>
       <c r="AH147" s="7"/>
@@ -10069,28 +10069,28 @@
       <c r="V166"/>
     </row>
     <row r="167" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B167" s="21" t="s">
+      <c r="B167" s="24" t="s">
         <v>299</v>
       </c>
-      <c r="C167" s="21"/>
-      <c r="D167" s="21"/>
-      <c r="E167" s="21"/>
-      <c r="F167" s="21"/>
-      <c r="G167" s="21"/>
-      <c r="H167" s="21"/>
-      <c r="I167" s="21"/>
-      <c r="J167" s="21"/>
-      <c r="K167" s="21"/>
-      <c r="L167" s="21"/>
-      <c r="M167" s="21"/>
-      <c r="N167" s="21"/>
-      <c r="O167" s="21"/>
-      <c r="P167" s="21"/>
-      <c r="Q167" s="21"/>
-      <c r="R167" s="21"/>
-      <c r="S167" s="21"/>
-      <c r="T167" s="21"/>
-      <c r="U167" s="21"/>
+      <c r="C167" s="24"/>
+      <c r="D167" s="24"/>
+      <c r="E167" s="24"/>
+      <c r="F167" s="24"/>
+      <c r="G167" s="24"/>
+      <c r="H167" s="24"/>
+      <c r="I167" s="24"/>
+      <c r="J167" s="24"/>
+      <c r="K167" s="24"/>
+      <c r="L167" s="24"/>
+      <c r="M167" s="24"/>
+      <c r="N167" s="24"/>
+      <c r="O167" s="24"/>
+      <c r="P167" s="24"/>
+      <c r="Q167" s="24"/>
+      <c r="R167" s="24"/>
+      <c r="S167" s="24"/>
+      <c r="T167" s="24"/>
+      <c r="U167" s="24"/>
       <c r="V167" s="8"/>
       <c r="W167" s="9"/>
       <c r="X167" s="9"/>
@@ -10109,26 +10109,26 @@
     </row>
     <row r="168" spans="1:36" ht="19.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168"/>
-      <c r="B168" s="26"/>
-      <c r="C168" s="27"/>
-      <c r="D168" s="27"/>
-      <c r="E168" s="27"/>
-      <c r="F168" s="27"/>
-      <c r="G168" s="27"/>
-      <c r="H168" s="27"/>
-      <c r="I168" s="27"/>
-      <c r="J168" s="27"/>
-      <c r="K168" s="27"/>
-      <c r="L168" s="27"/>
-      <c r="M168" s="27"/>
-      <c r="N168" s="27"/>
-      <c r="O168" s="27"/>
-      <c r="P168" s="27"/>
-      <c r="Q168" s="27"/>
-      <c r="R168" s="27"/>
-      <c r="S168" s="27"/>
-      <c r="T168" s="27"/>
-      <c r="U168" s="28"/>
+      <c r="B168" s="25"/>
+      <c r="C168" s="26"/>
+      <c r="D168" s="26"/>
+      <c r="E168" s="26"/>
+      <c r="F168" s="26"/>
+      <c r="G168" s="26"/>
+      <c r="H168" s="26"/>
+      <c r="I168" s="26"/>
+      <c r="J168" s="26"/>
+      <c r="K168" s="26"/>
+      <c r="L168" s="26"/>
+      <c r="M168" s="26"/>
+      <c r="N168" s="26"/>
+      <c r="O168" s="26"/>
+      <c r="P168" s="26"/>
+      <c r="Q168" s="26"/>
+      <c r="R168" s="26"/>
+      <c r="S168" s="26"/>
+      <c r="T168" s="26"/>
+      <c r="U168" s="27"/>
       <c r="V168" s="10">
         <v>0</v>
       </c>
@@ -11529,6 +11529,510 @@
     </row>
   </sheetData>
   <mergeCells count="528">
+    <mergeCell ref="B194:C194"/>
+    <mergeCell ref="D194:N194"/>
+    <mergeCell ref="O194:U194"/>
+    <mergeCell ref="B7:U7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:N9"/>
+    <mergeCell ref="O9:U9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:N10"/>
+    <mergeCell ref="O10:U10"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:N14"/>
+    <mergeCell ref="O14:U14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:N17"/>
+    <mergeCell ref="O17:U17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:N18"/>
+    <mergeCell ref="O18:U18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:N15"/>
+    <mergeCell ref="O15:U15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:N16"/>
+    <mergeCell ref="B1:U1"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:N3"/>
+    <mergeCell ref="O3:U3"/>
+    <mergeCell ref="B5:U5"/>
+    <mergeCell ref="B8:U8"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:N13"/>
+    <mergeCell ref="O13:U13"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:N11"/>
+    <mergeCell ref="O11:U11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:N12"/>
+    <mergeCell ref="O12:U12"/>
+    <mergeCell ref="O16:U16"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:N21"/>
+    <mergeCell ref="O21:U21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:N22"/>
+    <mergeCell ref="O22:U22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:N19"/>
+    <mergeCell ref="O19:U19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:N20"/>
+    <mergeCell ref="O20:U20"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:N25"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:N26"/>
+    <mergeCell ref="O26:U26"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:N23"/>
+    <mergeCell ref="O23:U23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:N24"/>
+    <mergeCell ref="O24:U24"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:N29"/>
+    <mergeCell ref="O29:U29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:N30"/>
+    <mergeCell ref="O30:U30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:N27"/>
+    <mergeCell ref="O27:U27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:N28"/>
+    <mergeCell ref="O28:U28"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:N33"/>
+    <mergeCell ref="O33:U33"/>
+    <mergeCell ref="B35:U35"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:N37"/>
+    <mergeCell ref="O37:U37"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:N31"/>
+    <mergeCell ref="O31:U31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:N32"/>
+    <mergeCell ref="O32:U32"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:N40"/>
+    <mergeCell ref="O40:U40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:N41"/>
+    <mergeCell ref="O41:U41"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:N38"/>
+    <mergeCell ref="O38:U38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:N39"/>
+    <mergeCell ref="O39:U39"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:N44"/>
+    <mergeCell ref="O44:U44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:N45"/>
+    <mergeCell ref="O45:U45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:N42"/>
+    <mergeCell ref="O42:U42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:N43"/>
+    <mergeCell ref="O43:U43"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:N48"/>
+    <mergeCell ref="O48:U48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:N49"/>
+    <mergeCell ref="O49:U49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:N46"/>
+    <mergeCell ref="O46:U46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:N47"/>
+    <mergeCell ref="O47:U47"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:N52"/>
+    <mergeCell ref="O52:U52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:N53"/>
+    <mergeCell ref="O53:U53"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:N50"/>
+    <mergeCell ref="O50:U50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:N51"/>
+    <mergeCell ref="O51:U51"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:N56"/>
+    <mergeCell ref="O56:U56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:N57"/>
+    <mergeCell ref="O57:U57"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:N54"/>
+    <mergeCell ref="O54:U54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:N55"/>
+    <mergeCell ref="O55:U55"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:N60"/>
+    <mergeCell ref="O60:U60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:N61"/>
+    <mergeCell ref="O61:U61"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:N58"/>
+    <mergeCell ref="O58:U58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:N59"/>
+    <mergeCell ref="O59:U59"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:N64"/>
+    <mergeCell ref="O64:U64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:N65"/>
+    <mergeCell ref="O65:U65"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:N62"/>
+    <mergeCell ref="O62:U62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D63:N63"/>
+    <mergeCell ref="O63:U63"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="D71:N71"/>
+    <mergeCell ref="O71:U71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="D72:N72"/>
+    <mergeCell ref="O72:U72"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="D66:N66"/>
+    <mergeCell ref="O66:U66"/>
+    <mergeCell ref="B68:U68"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="D70:N70"/>
+    <mergeCell ref="O70:U70"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="D75:N75"/>
+    <mergeCell ref="O75:U75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="D76:N76"/>
+    <mergeCell ref="O76:U76"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="D73:N73"/>
+    <mergeCell ref="O73:U73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="D74:N74"/>
+    <mergeCell ref="O74:U74"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="D79:N79"/>
+    <mergeCell ref="O79:U79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="D80:N80"/>
+    <mergeCell ref="O80:U80"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="D77:N77"/>
+    <mergeCell ref="O77:U77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="D78:N78"/>
+    <mergeCell ref="O78:U78"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="D83:N83"/>
+    <mergeCell ref="O83:U83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="D84:N84"/>
+    <mergeCell ref="O84:U84"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="D81:N81"/>
+    <mergeCell ref="O81:U81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:N82"/>
+    <mergeCell ref="O82:U82"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="D87:N87"/>
+    <mergeCell ref="O87:U87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="D88:N88"/>
+    <mergeCell ref="O88:U88"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="D85:N85"/>
+    <mergeCell ref="O85:U85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="D86:N86"/>
+    <mergeCell ref="O86:U86"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="D91:N91"/>
+    <mergeCell ref="O91:U91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="D92:N92"/>
+    <mergeCell ref="O92:U92"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="D89:N89"/>
+    <mergeCell ref="O89:U89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="D90:N90"/>
+    <mergeCell ref="O90:U90"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="D95:N95"/>
+    <mergeCell ref="O95:U95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="D96:N96"/>
+    <mergeCell ref="O96:U96"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="D93:N93"/>
+    <mergeCell ref="O93:U93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="D94:N94"/>
+    <mergeCell ref="O94:U94"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:N99"/>
+    <mergeCell ref="O99:U99"/>
+    <mergeCell ref="B101:U101"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="D103:N103"/>
+    <mergeCell ref="O103:U103"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="D97:N97"/>
+    <mergeCell ref="O97:U97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="D98:N98"/>
+    <mergeCell ref="O98:U98"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="D106:N106"/>
+    <mergeCell ref="O106:U106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="D107:N107"/>
+    <mergeCell ref="O107:U107"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="D104:N104"/>
+    <mergeCell ref="O104:U104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="D105:N105"/>
+    <mergeCell ref="O105:U105"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="D110:N110"/>
+    <mergeCell ref="O110:U110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="D111:N111"/>
+    <mergeCell ref="O111:U111"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="D108:N108"/>
+    <mergeCell ref="O108:U108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="D109:N109"/>
+    <mergeCell ref="O109:U109"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="D114:N114"/>
+    <mergeCell ref="O114:U114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="D115:N115"/>
+    <mergeCell ref="O115:U115"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="D112:N112"/>
+    <mergeCell ref="O112:U112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="D113:N113"/>
+    <mergeCell ref="O113:U113"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="D118:N118"/>
+    <mergeCell ref="O118:U118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="D119:N119"/>
+    <mergeCell ref="O119:U119"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="D116:N116"/>
+    <mergeCell ref="O116:U116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="D117:N117"/>
+    <mergeCell ref="O117:U117"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="D122:N122"/>
+    <mergeCell ref="O122:U122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="D123:N123"/>
+    <mergeCell ref="O123:U123"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="D120:N120"/>
+    <mergeCell ref="O120:U120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="D121:N121"/>
+    <mergeCell ref="O121:U121"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="D126:N126"/>
+    <mergeCell ref="O126:U126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="D127:N127"/>
+    <mergeCell ref="O127:U127"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="D124:N124"/>
+    <mergeCell ref="O124:U124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="D125:N125"/>
+    <mergeCell ref="O125:U125"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="D130:N130"/>
+    <mergeCell ref="O130:U130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="D131:N131"/>
+    <mergeCell ref="O131:U131"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="D128:N128"/>
+    <mergeCell ref="O128:U128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="D129:N129"/>
+    <mergeCell ref="O129:U129"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="D137:N137"/>
+    <mergeCell ref="O137:U137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="D138:N138"/>
+    <mergeCell ref="O138:U138"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="D132:N132"/>
+    <mergeCell ref="O132:U132"/>
+    <mergeCell ref="B134:U134"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="D136:N136"/>
+    <mergeCell ref="O136:U136"/>
+    <mergeCell ref="B135:U135"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="D141:N141"/>
+    <mergeCell ref="O141:U141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="D142:N142"/>
+    <mergeCell ref="O142:U142"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="D139:N139"/>
+    <mergeCell ref="O139:U139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="D140:N140"/>
+    <mergeCell ref="O140:U140"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="D145:N145"/>
+    <mergeCell ref="O145:U145"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="D146:N146"/>
+    <mergeCell ref="O146:U146"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="D143:N143"/>
+    <mergeCell ref="O143:U143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="D144:N144"/>
+    <mergeCell ref="O144:U144"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="D149:N149"/>
+    <mergeCell ref="O149:U149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="D150:N150"/>
+    <mergeCell ref="O150:U150"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="D147:N147"/>
+    <mergeCell ref="O147:U147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="D148:N148"/>
+    <mergeCell ref="O148:U148"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="D153:N153"/>
+    <mergeCell ref="O153:U153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="D154:N154"/>
+    <mergeCell ref="O154:U154"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="D151:N151"/>
+    <mergeCell ref="O151:U151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="D152:N152"/>
+    <mergeCell ref="O152:U152"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="D157:N157"/>
+    <mergeCell ref="O157:U157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="D158:N158"/>
+    <mergeCell ref="O158:U158"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="D155:N155"/>
+    <mergeCell ref="O155:U155"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="D156:N156"/>
+    <mergeCell ref="O156:U156"/>
+    <mergeCell ref="B161:C161"/>
+    <mergeCell ref="D161:N161"/>
+    <mergeCell ref="O161:U161"/>
+    <mergeCell ref="B162:C162"/>
+    <mergeCell ref="D162:N162"/>
+    <mergeCell ref="O162:U162"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="D159:N159"/>
+    <mergeCell ref="O159:U159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="D160:N160"/>
+    <mergeCell ref="O160:U160"/>
+    <mergeCell ref="B165:C165"/>
+    <mergeCell ref="D165:N165"/>
+    <mergeCell ref="O165:U165"/>
+    <mergeCell ref="B167:U167"/>
+    <mergeCell ref="B169:C169"/>
+    <mergeCell ref="D169:N169"/>
+    <mergeCell ref="O169:U169"/>
+    <mergeCell ref="B163:C163"/>
+    <mergeCell ref="D163:N163"/>
+    <mergeCell ref="O163:U163"/>
+    <mergeCell ref="B164:C164"/>
+    <mergeCell ref="D164:N164"/>
+    <mergeCell ref="O164:U164"/>
+    <mergeCell ref="B168:U168"/>
+    <mergeCell ref="B172:C172"/>
+    <mergeCell ref="D172:N172"/>
+    <mergeCell ref="O172:U172"/>
+    <mergeCell ref="B173:C173"/>
+    <mergeCell ref="D173:N173"/>
+    <mergeCell ref="O173:U173"/>
+    <mergeCell ref="B170:C170"/>
+    <mergeCell ref="D170:N170"/>
+    <mergeCell ref="O170:U170"/>
+    <mergeCell ref="B171:C171"/>
+    <mergeCell ref="D171:N171"/>
+    <mergeCell ref="O171:U171"/>
+    <mergeCell ref="B176:C176"/>
+    <mergeCell ref="D176:N176"/>
+    <mergeCell ref="O176:U176"/>
+    <mergeCell ref="B177:C177"/>
+    <mergeCell ref="D177:N177"/>
+    <mergeCell ref="O177:U177"/>
+    <mergeCell ref="B174:C174"/>
+    <mergeCell ref="D174:N174"/>
+    <mergeCell ref="O174:U174"/>
+    <mergeCell ref="B175:C175"/>
+    <mergeCell ref="D175:N175"/>
+    <mergeCell ref="O175:U175"/>
+    <mergeCell ref="B180:C180"/>
+    <mergeCell ref="D180:N180"/>
+    <mergeCell ref="O180:U180"/>
+    <mergeCell ref="B181:C181"/>
+    <mergeCell ref="D181:N181"/>
+    <mergeCell ref="O181:U181"/>
+    <mergeCell ref="B178:C178"/>
+    <mergeCell ref="D178:N178"/>
+    <mergeCell ref="O178:U178"/>
+    <mergeCell ref="B179:C179"/>
+    <mergeCell ref="D179:N179"/>
+    <mergeCell ref="O179:U179"/>
+    <mergeCell ref="O187:U187"/>
+    <mergeCell ref="B184:C184"/>
+    <mergeCell ref="D184:N184"/>
+    <mergeCell ref="O184:U184"/>
+    <mergeCell ref="B185:C185"/>
+    <mergeCell ref="D185:N185"/>
+    <mergeCell ref="O185:U185"/>
+    <mergeCell ref="B182:C182"/>
+    <mergeCell ref="D182:N182"/>
+    <mergeCell ref="O182:U182"/>
+    <mergeCell ref="B183:C183"/>
+    <mergeCell ref="D183:N183"/>
+    <mergeCell ref="O183:U183"/>
     <mergeCell ref="B193:C193"/>
     <mergeCell ref="D193:N193"/>
     <mergeCell ref="O193:U193"/>
@@ -11553,510 +12057,6 @@
     <mergeCell ref="O186:U186"/>
     <mergeCell ref="B187:C187"/>
     <mergeCell ref="D187:N187"/>
-    <mergeCell ref="O187:U187"/>
-    <mergeCell ref="B184:C184"/>
-    <mergeCell ref="D184:N184"/>
-    <mergeCell ref="O184:U184"/>
-    <mergeCell ref="B185:C185"/>
-    <mergeCell ref="D185:N185"/>
-    <mergeCell ref="O185:U185"/>
-    <mergeCell ref="B182:C182"/>
-    <mergeCell ref="D182:N182"/>
-    <mergeCell ref="O182:U182"/>
-    <mergeCell ref="B183:C183"/>
-    <mergeCell ref="D183:N183"/>
-    <mergeCell ref="O183:U183"/>
-    <mergeCell ref="B180:C180"/>
-    <mergeCell ref="D180:N180"/>
-    <mergeCell ref="O180:U180"/>
-    <mergeCell ref="B181:C181"/>
-    <mergeCell ref="D181:N181"/>
-    <mergeCell ref="O181:U181"/>
-    <mergeCell ref="B178:C178"/>
-    <mergeCell ref="D178:N178"/>
-    <mergeCell ref="O178:U178"/>
-    <mergeCell ref="B179:C179"/>
-    <mergeCell ref="D179:N179"/>
-    <mergeCell ref="O179:U179"/>
-    <mergeCell ref="B176:C176"/>
-    <mergeCell ref="D176:N176"/>
-    <mergeCell ref="O176:U176"/>
-    <mergeCell ref="B177:C177"/>
-    <mergeCell ref="D177:N177"/>
-    <mergeCell ref="O177:U177"/>
-    <mergeCell ref="B174:C174"/>
-    <mergeCell ref="D174:N174"/>
-    <mergeCell ref="O174:U174"/>
-    <mergeCell ref="B175:C175"/>
-    <mergeCell ref="D175:N175"/>
-    <mergeCell ref="O175:U175"/>
-    <mergeCell ref="B172:C172"/>
-    <mergeCell ref="D172:N172"/>
-    <mergeCell ref="O172:U172"/>
-    <mergeCell ref="B173:C173"/>
-    <mergeCell ref="D173:N173"/>
-    <mergeCell ref="O173:U173"/>
-    <mergeCell ref="B170:C170"/>
-    <mergeCell ref="D170:N170"/>
-    <mergeCell ref="O170:U170"/>
-    <mergeCell ref="B171:C171"/>
-    <mergeCell ref="D171:N171"/>
-    <mergeCell ref="O171:U171"/>
-    <mergeCell ref="B165:C165"/>
-    <mergeCell ref="D165:N165"/>
-    <mergeCell ref="O165:U165"/>
-    <mergeCell ref="B167:U167"/>
-    <mergeCell ref="B169:C169"/>
-    <mergeCell ref="D169:N169"/>
-    <mergeCell ref="O169:U169"/>
-    <mergeCell ref="B163:C163"/>
-    <mergeCell ref="D163:N163"/>
-    <mergeCell ref="O163:U163"/>
-    <mergeCell ref="B164:C164"/>
-    <mergeCell ref="D164:N164"/>
-    <mergeCell ref="O164:U164"/>
-    <mergeCell ref="B168:U168"/>
-    <mergeCell ref="B161:C161"/>
-    <mergeCell ref="D161:N161"/>
-    <mergeCell ref="O161:U161"/>
-    <mergeCell ref="B162:C162"/>
-    <mergeCell ref="D162:N162"/>
-    <mergeCell ref="O162:U162"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="D159:N159"/>
-    <mergeCell ref="O159:U159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="D160:N160"/>
-    <mergeCell ref="O160:U160"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="D157:N157"/>
-    <mergeCell ref="O157:U157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="D158:N158"/>
-    <mergeCell ref="O158:U158"/>
-    <mergeCell ref="B155:C155"/>
-    <mergeCell ref="D155:N155"/>
-    <mergeCell ref="O155:U155"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="D156:N156"/>
-    <mergeCell ref="O156:U156"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="D153:N153"/>
-    <mergeCell ref="O153:U153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="D154:N154"/>
-    <mergeCell ref="O154:U154"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="D151:N151"/>
-    <mergeCell ref="O151:U151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="D152:N152"/>
-    <mergeCell ref="O152:U152"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="D149:N149"/>
-    <mergeCell ref="O149:U149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="D150:N150"/>
-    <mergeCell ref="O150:U150"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="D147:N147"/>
-    <mergeCell ref="O147:U147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="D148:N148"/>
-    <mergeCell ref="O148:U148"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="D145:N145"/>
-    <mergeCell ref="O145:U145"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="D146:N146"/>
-    <mergeCell ref="O146:U146"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="D143:N143"/>
-    <mergeCell ref="O143:U143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="D144:N144"/>
-    <mergeCell ref="O144:U144"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="D141:N141"/>
-    <mergeCell ref="O141:U141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="D142:N142"/>
-    <mergeCell ref="O142:U142"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="D139:N139"/>
-    <mergeCell ref="O139:U139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="D140:N140"/>
-    <mergeCell ref="O140:U140"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="D137:N137"/>
-    <mergeCell ref="O137:U137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="D138:N138"/>
-    <mergeCell ref="O138:U138"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="D132:N132"/>
-    <mergeCell ref="O132:U132"/>
-    <mergeCell ref="B134:U134"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="D136:N136"/>
-    <mergeCell ref="O136:U136"/>
-    <mergeCell ref="B135:U135"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="D130:N130"/>
-    <mergeCell ref="O130:U130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="D131:N131"/>
-    <mergeCell ref="O131:U131"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="D128:N128"/>
-    <mergeCell ref="O128:U128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="D129:N129"/>
-    <mergeCell ref="O129:U129"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="D126:N126"/>
-    <mergeCell ref="O126:U126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="D127:N127"/>
-    <mergeCell ref="O127:U127"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="D124:N124"/>
-    <mergeCell ref="O124:U124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="D125:N125"/>
-    <mergeCell ref="O125:U125"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="D122:N122"/>
-    <mergeCell ref="O122:U122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="D123:N123"/>
-    <mergeCell ref="O123:U123"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="D120:N120"/>
-    <mergeCell ref="O120:U120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="D121:N121"/>
-    <mergeCell ref="O121:U121"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="D118:N118"/>
-    <mergeCell ref="O118:U118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="D119:N119"/>
-    <mergeCell ref="O119:U119"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="D116:N116"/>
-    <mergeCell ref="O116:U116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="D117:N117"/>
-    <mergeCell ref="O117:U117"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="D114:N114"/>
-    <mergeCell ref="O114:U114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="D115:N115"/>
-    <mergeCell ref="O115:U115"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="D112:N112"/>
-    <mergeCell ref="O112:U112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="D113:N113"/>
-    <mergeCell ref="O113:U113"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="D110:N110"/>
-    <mergeCell ref="O110:U110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="D111:N111"/>
-    <mergeCell ref="O111:U111"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="D108:N108"/>
-    <mergeCell ref="O108:U108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="D109:N109"/>
-    <mergeCell ref="O109:U109"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="D106:N106"/>
-    <mergeCell ref="O106:U106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="D107:N107"/>
-    <mergeCell ref="O107:U107"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="D104:N104"/>
-    <mergeCell ref="O104:U104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="D105:N105"/>
-    <mergeCell ref="O105:U105"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:N99"/>
-    <mergeCell ref="O99:U99"/>
-    <mergeCell ref="B101:U101"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="D103:N103"/>
-    <mergeCell ref="O103:U103"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="D97:N97"/>
-    <mergeCell ref="O97:U97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="D98:N98"/>
-    <mergeCell ref="O98:U98"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="D95:N95"/>
-    <mergeCell ref="O95:U95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="D96:N96"/>
-    <mergeCell ref="O96:U96"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="D93:N93"/>
-    <mergeCell ref="O93:U93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="D94:N94"/>
-    <mergeCell ref="O94:U94"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="D91:N91"/>
-    <mergeCell ref="O91:U91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="D92:N92"/>
-    <mergeCell ref="O92:U92"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="D89:N89"/>
-    <mergeCell ref="O89:U89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="D90:N90"/>
-    <mergeCell ref="O90:U90"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="D87:N87"/>
-    <mergeCell ref="O87:U87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="D88:N88"/>
-    <mergeCell ref="O88:U88"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="D85:N85"/>
-    <mergeCell ref="O85:U85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="D86:N86"/>
-    <mergeCell ref="O86:U86"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="D83:N83"/>
-    <mergeCell ref="O83:U83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="D84:N84"/>
-    <mergeCell ref="O84:U84"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="D81:N81"/>
-    <mergeCell ref="O81:U81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:N82"/>
-    <mergeCell ref="O82:U82"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="D79:N79"/>
-    <mergeCell ref="O79:U79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="D80:N80"/>
-    <mergeCell ref="O80:U80"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="D77:N77"/>
-    <mergeCell ref="O77:U77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="D78:N78"/>
-    <mergeCell ref="O78:U78"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="D75:N75"/>
-    <mergeCell ref="O75:U75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="D76:N76"/>
-    <mergeCell ref="O76:U76"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="D73:N73"/>
-    <mergeCell ref="O73:U73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="D74:N74"/>
-    <mergeCell ref="O74:U74"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="D71:N71"/>
-    <mergeCell ref="O71:U71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="D72:N72"/>
-    <mergeCell ref="O72:U72"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="D66:N66"/>
-    <mergeCell ref="O66:U66"/>
-    <mergeCell ref="B68:U68"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="D70:N70"/>
-    <mergeCell ref="O70:U70"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="D64:N64"/>
-    <mergeCell ref="O64:U64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:N65"/>
-    <mergeCell ref="O65:U65"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:N62"/>
-    <mergeCell ref="O62:U62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D63:N63"/>
-    <mergeCell ref="O63:U63"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:N60"/>
-    <mergeCell ref="O60:U60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="D61:N61"/>
-    <mergeCell ref="O61:U61"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:N58"/>
-    <mergeCell ref="O58:U58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:N59"/>
-    <mergeCell ref="O59:U59"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:N56"/>
-    <mergeCell ref="O56:U56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:N57"/>
-    <mergeCell ref="O57:U57"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:N54"/>
-    <mergeCell ref="O54:U54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:N55"/>
-    <mergeCell ref="O55:U55"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:N52"/>
-    <mergeCell ref="O52:U52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:N53"/>
-    <mergeCell ref="O53:U53"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:N50"/>
-    <mergeCell ref="O50:U50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:N51"/>
-    <mergeCell ref="O51:U51"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:N48"/>
-    <mergeCell ref="O48:U48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:N49"/>
-    <mergeCell ref="O49:U49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:N46"/>
-    <mergeCell ref="O46:U46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:N47"/>
-    <mergeCell ref="O47:U47"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:N44"/>
-    <mergeCell ref="O44:U44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:N45"/>
-    <mergeCell ref="O45:U45"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:N42"/>
-    <mergeCell ref="O42:U42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:N43"/>
-    <mergeCell ref="O43:U43"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:N40"/>
-    <mergeCell ref="O40:U40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:N41"/>
-    <mergeCell ref="O41:U41"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:N38"/>
-    <mergeCell ref="O38:U38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:N39"/>
-    <mergeCell ref="O39:U39"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:N33"/>
-    <mergeCell ref="O33:U33"/>
-    <mergeCell ref="B35:U35"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:N37"/>
-    <mergeCell ref="O37:U37"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:N31"/>
-    <mergeCell ref="O31:U31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:N32"/>
-    <mergeCell ref="O32:U32"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:N29"/>
-    <mergeCell ref="O29:U29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:N30"/>
-    <mergeCell ref="O30:U30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:N27"/>
-    <mergeCell ref="O27:U27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:N28"/>
-    <mergeCell ref="O28:U28"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:N25"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:N26"/>
-    <mergeCell ref="O26:U26"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:N23"/>
-    <mergeCell ref="O23:U23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:N24"/>
-    <mergeCell ref="O24:U24"/>
-    <mergeCell ref="O16:U16"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:N21"/>
-    <mergeCell ref="O21:U21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:N22"/>
-    <mergeCell ref="O22:U22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:N19"/>
-    <mergeCell ref="O19:U19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:N20"/>
-    <mergeCell ref="O20:U20"/>
-    <mergeCell ref="B1:U1"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:N3"/>
-    <mergeCell ref="O3:U3"/>
-    <mergeCell ref="B5:U5"/>
-    <mergeCell ref="B8:U8"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:N13"/>
-    <mergeCell ref="O13:U13"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:N11"/>
-    <mergeCell ref="O11:U11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:N12"/>
-    <mergeCell ref="O12:U12"/>
-    <mergeCell ref="B194:C194"/>
-    <mergeCell ref="D194:N194"/>
-    <mergeCell ref="O194:U194"/>
-    <mergeCell ref="B7:U7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:N9"/>
-    <mergeCell ref="O9:U9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:N10"/>
-    <mergeCell ref="O10:U10"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:N14"/>
-    <mergeCell ref="O14:U14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:N17"/>
-    <mergeCell ref="O17:U17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:N18"/>
-    <mergeCell ref="O18:U18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:N15"/>
-    <mergeCell ref="O15:U15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:N16"/>
   </mergeCells>
   <pageMargins left="0.39370078740157477" right="0.39370078740157477" top="0.39370078740157477" bottom="0.39370078740157477" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>

--- a/Журнал.xlsx
+++ b/Журнал.xlsx
@@ -1293,26 +1293,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1325,6 +1307,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1718,70 +1718,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
     </row>
     <row r="2" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30" t="s">
+      <c r="B3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="29" t="s">
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="22"/>
-      <c r="Z3" s="22"/>
-      <c r="AA3" s="22"/>
-      <c r="AB3" s="22"/>
-      <c r="AC3" s="22"/>
-      <c r="AD3" s="22"/>
-      <c r="AE3" s="22"/>
-      <c r="AF3" s="22"/>
-      <c r="AG3" s="22"/>
-      <c r="AH3" s="22"/>
-      <c r="AI3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+      <c r="Y3" s="30"/>
+      <c r="Z3" s="30"/>
+      <c r="AA3" s="30"/>
+      <c r="AB3" s="30"/>
+      <c r="AC3" s="30"/>
+      <c r="AD3" s="30"/>
+      <c r="AE3" s="30"/>
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="31"/>
     </row>
     <row r="4" spans="1:35" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4"/>
@@ -1808,28 +1808,28 @@
       <c r="V4"/>
     </row>
     <row r="5" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="31" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="31"/>
-      <c r="N5" s="31"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
-      <c r="Q5" s="31"/>
-      <c r="R5" s="31"/>
-      <c r="S5" s="31"/>
-      <c r="T5" s="31"/>
-      <c r="U5" s="31"/>
+      <c r="B5" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
       <c r="V5" s="8"/>
       <c r="W5" s="9"/>
       <c r="X5" s="9"/>
@@ -1870,28 +1870,28 @@
       <c r="V6"/>
     </row>
     <row r="7" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
       <c r="V7" s="8"/>
       <c r="W7" s="9"/>
       <c r="X7" s="9"/>
@@ -1909,26 +1909,26 @@
     </row>
     <row r="8" spans="1:35" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="27"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="28"/>
       <c r="V8" s="10">
         <v>0</v>
       </c>
@@ -3301,28 +3301,28 @@
       <c r="V34"/>
     </row>
     <row r="35" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="24"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="24"/>
-      <c r="Q35" s="24"/>
-      <c r="R35" s="24"/>
-      <c r="S35" s="24"/>
-      <c r="T35" s="24"/>
-      <c r="U35" s="24"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="21"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="21"/>
+      <c r="R35" s="21"/>
+      <c r="S35" s="21"/>
+      <c r="T35" s="21"/>
+      <c r="U35" s="21"/>
       <c r="V35" s="8"/>
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
@@ -4993,28 +4993,28 @@
     </row>
     <row r="68" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
-      <c r="B68" s="24" t="s">
+      <c r="B68" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="C68" s="24"/>
-      <c r="D68" s="24"/>
-      <c r="E68" s="24"/>
-      <c r="F68" s="24"/>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="24"/>
-      <c r="J68" s="24"/>
-      <c r="K68" s="24"/>
-      <c r="L68" s="24"/>
-      <c r="M68" s="24"/>
-      <c r="N68" s="24"/>
-      <c r="O68" s="24"/>
-      <c r="P68" s="24"/>
-      <c r="Q68" s="24"/>
-      <c r="R68" s="24"/>
-      <c r="S68" s="24"/>
-      <c r="T68" s="24"/>
-      <c r="U68" s="24"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="21"/>
+      <c r="P68" s="21"/>
+      <c r="Q68" s="21"/>
+      <c r="R68" s="21"/>
+      <c r="S68" s="21"/>
+      <c r="T68" s="21"/>
+      <c r="U68" s="21"/>
       <c r="V68" s="8"/>
       <c r="W68" s="9"/>
       <c r="X68" s="9"/>
@@ -6685,28 +6685,28 @@
       <c r="V100"/>
     </row>
     <row r="101" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B101" s="24" t="s">
+      <c r="B101" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="C101" s="24"/>
-      <c r="D101" s="24"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="24"/>
-      <c r="H101" s="24"/>
-      <c r="I101" s="24"/>
-      <c r="J101" s="24"/>
-      <c r="K101" s="24"/>
-      <c r="L101" s="24"/>
-      <c r="M101" s="24"/>
-      <c r="N101" s="24"/>
-      <c r="O101" s="24"/>
-      <c r="P101" s="24"/>
-      <c r="Q101" s="24"/>
-      <c r="R101" s="24"/>
-      <c r="S101" s="24"/>
-      <c r="T101" s="24"/>
-      <c r="U101" s="24"/>
+      <c r="C101" s="21"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="21"/>
+      <c r="F101" s="21"/>
+      <c r="G101" s="21"/>
+      <c r="H101" s="21"/>
+      <c r="I101" s="21"/>
+      <c r="J101" s="21"/>
+      <c r="K101" s="21"/>
+      <c r="L101" s="21"/>
+      <c r="M101" s="21"/>
+      <c r="N101" s="21"/>
+      <c r="O101" s="21"/>
+      <c r="P101" s="21"/>
+      <c r="Q101" s="21"/>
+      <c r="R101" s="21"/>
+      <c r="S101" s="21"/>
+      <c r="T101" s="21"/>
+      <c r="U101" s="21"/>
       <c r="V101" s="8"/>
       <c r="W101" s="9"/>
       <c r="X101" s="9"/>
@@ -8377,28 +8377,28 @@
       <c r="V133"/>
     </row>
     <row r="134" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B134" s="24" t="s">
+      <c r="B134" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="C134" s="24"/>
-      <c r="D134" s="24"/>
-      <c r="E134" s="24"/>
-      <c r="F134" s="24"/>
-      <c r="G134" s="24"/>
-      <c r="H134" s="24"/>
-      <c r="I134" s="24"/>
-      <c r="J134" s="24"/>
-      <c r="K134" s="24"/>
-      <c r="L134" s="24"/>
-      <c r="M134" s="24"/>
-      <c r="N134" s="24"/>
-      <c r="O134" s="24"/>
-      <c r="P134" s="24"/>
-      <c r="Q134" s="24"/>
-      <c r="R134" s="24"/>
-      <c r="S134" s="24"/>
-      <c r="T134" s="24"/>
-      <c r="U134" s="24"/>
+      <c r="C134" s="21"/>
+      <c r="D134" s="21"/>
+      <c r="E134" s="21"/>
+      <c r="F134" s="21"/>
+      <c r="G134" s="21"/>
+      <c r="H134" s="21"/>
+      <c r="I134" s="21"/>
+      <c r="J134" s="21"/>
+      <c r="K134" s="21"/>
+      <c r="L134" s="21"/>
+      <c r="M134" s="21"/>
+      <c r="N134" s="21"/>
+      <c r="O134" s="21"/>
+      <c r="P134" s="21"/>
+      <c r="Q134" s="21"/>
+      <c r="R134" s="21"/>
+      <c r="S134" s="21"/>
+      <c r="T134" s="21"/>
+      <c r="U134" s="21"/>
       <c r="V134" s="8"/>
       <c r="W134" s="9"/>
       <c r="X134" s="9"/>
@@ -8417,26 +8417,26 @@
     </row>
     <row r="135" spans="1:36" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135"/>
-      <c r="B135" s="25"/>
-      <c r="C135" s="26"/>
-      <c r="D135" s="26"/>
-      <c r="E135" s="26"/>
-      <c r="F135" s="26"/>
-      <c r="G135" s="26"/>
-      <c r="H135" s="26"/>
-      <c r="I135" s="26"/>
-      <c r="J135" s="26"/>
-      <c r="K135" s="26"/>
-      <c r="L135" s="26"/>
-      <c r="M135" s="26"/>
-      <c r="N135" s="26"/>
-      <c r="O135" s="26"/>
-      <c r="P135" s="26"/>
-      <c r="Q135" s="26"/>
-      <c r="R135" s="26"/>
-      <c r="S135" s="26"/>
-      <c r="T135" s="26"/>
-      <c r="U135" s="27"/>
+      <c r="B135" s="26"/>
+      <c r="C135" s="27"/>
+      <c r="D135" s="27"/>
+      <c r="E135" s="27"/>
+      <c r="F135" s="27"/>
+      <c r="G135" s="27"/>
+      <c r="H135" s="27"/>
+      <c r="I135" s="27"/>
+      <c r="J135" s="27"/>
+      <c r="K135" s="27"/>
+      <c r="L135" s="27"/>
+      <c r="M135" s="27"/>
+      <c r="N135" s="27"/>
+      <c r="O135" s="27"/>
+      <c r="P135" s="27"/>
+      <c r="Q135" s="27"/>
+      <c r="R135" s="27"/>
+      <c r="S135" s="27"/>
+      <c r="T135" s="27"/>
+      <c r="U135" s="28"/>
       <c r="V135" s="10">
         <v>0</v>
       </c>
@@ -9192,7 +9192,7 @@
         <v>3</v>
       </c>
       <c r="W149" s="12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X149" s="12">
         <v>3</v>
@@ -9206,7 +9206,7 @@
       <c r="AE149" s="6"/>
       <c r="AF149" s="17">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG149" s="7"/>
       <c r="AH149" s="7"/>
@@ -10069,28 +10069,28 @@
       <c r="V166"/>
     </row>
     <row r="167" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B167" s="24" t="s">
+      <c r="B167" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="C167" s="24"/>
-      <c r="D167" s="24"/>
-      <c r="E167" s="24"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="24"/>
-      <c r="H167" s="24"/>
-      <c r="I167" s="24"/>
-      <c r="J167" s="24"/>
-      <c r="K167" s="24"/>
-      <c r="L167" s="24"/>
-      <c r="M167" s="24"/>
-      <c r="N167" s="24"/>
-      <c r="O167" s="24"/>
-      <c r="P167" s="24"/>
-      <c r="Q167" s="24"/>
-      <c r="R167" s="24"/>
-      <c r="S167" s="24"/>
-      <c r="T167" s="24"/>
-      <c r="U167" s="24"/>
+      <c r="C167" s="21"/>
+      <c r="D167" s="21"/>
+      <c r="E167" s="21"/>
+      <c r="F167" s="21"/>
+      <c r="G167" s="21"/>
+      <c r="H167" s="21"/>
+      <c r="I167" s="21"/>
+      <c r="J167" s="21"/>
+      <c r="K167" s="21"/>
+      <c r="L167" s="21"/>
+      <c r="M167" s="21"/>
+      <c r="N167" s="21"/>
+      <c r="O167" s="21"/>
+      <c r="P167" s="21"/>
+      <c r="Q167" s="21"/>
+      <c r="R167" s="21"/>
+      <c r="S167" s="21"/>
+      <c r="T167" s="21"/>
+      <c r="U167" s="21"/>
       <c r="V167" s="8"/>
       <c r="W167" s="9"/>
       <c r="X167" s="9"/>
@@ -10109,26 +10109,26 @@
     </row>
     <row r="168" spans="1:36" ht="19.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168"/>
-      <c r="B168" s="25"/>
-      <c r="C168" s="26"/>
-      <c r="D168" s="26"/>
-      <c r="E168" s="26"/>
-      <c r="F168" s="26"/>
-      <c r="G168" s="26"/>
-      <c r="H168" s="26"/>
-      <c r="I168" s="26"/>
-      <c r="J168" s="26"/>
-      <c r="K168" s="26"/>
-      <c r="L168" s="26"/>
-      <c r="M168" s="26"/>
-      <c r="N168" s="26"/>
-      <c r="O168" s="26"/>
-      <c r="P168" s="26"/>
-      <c r="Q168" s="26"/>
-      <c r="R168" s="26"/>
-      <c r="S168" s="26"/>
-      <c r="T168" s="26"/>
-      <c r="U168" s="27"/>
+      <c r="B168" s="26"/>
+      <c r="C168" s="27"/>
+      <c r="D168" s="27"/>
+      <c r="E168" s="27"/>
+      <c r="F168" s="27"/>
+      <c r="G168" s="27"/>
+      <c r="H168" s="27"/>
+      <c r="I168" s="27"/>
+      <c r="J168" s="27"/>
+      <c r="K168" s="27"/>
+      <c r="L168" s="27"/>
+      <c r="M168" s="27"/>
+      <c r="N168" s="27"/>
+      <c r="O168" s="27"/>
+      <c r="P168" s="27"/>
+      <c r="Q168" s="27"/>
+      <c r="R168" s="27"/>
+      <c r="S168" s="27"/>
+      <c r="T168" s="27"/>
+      <c r="U168" s="28"/>
       <c r="V168" s="10">
         <v>0</v>
       </c>
@@ -11529,6 +11529,510 @@
     </row>
   </sheetData>
   <mergeCells count="528">
+    <mergeCell ref="B193:C193"/>
+    <mergeCell ref="D193:N193"/>
+    <mergeCell ref="O193:U193"/>
+    <mergeCell ref="B192:C192"/>
+    <mergeCell ref="D192:N192"/>
+    <mergeCell ref="O192:U192"/>
+    <mergeCell ref="V3:AI3"/>
+    <mergeCell ref="B190:C190"/>
+    <mergeCell ref="D190:N190"/>
+    <mergeCell ref="O190:U190"/>
+    <mergeCell ref="B191:C191"/>
+    <mergeCell ref="D191:N191"/>
+    <mergeCell ref="O191:U191"/>
+    <mergeCell ref="B188:C188"/>
+    <mergeCell ref="D188:N188"/>
+    <mergeCell ref="O188:U188"/>
+    <mergeCell ref="B189:C189"/>
+    <mergeCell ref="D189:N189"/>
+    <mergeCell ref="O189:U189"/>
+    <mergeCell ref="B186:C186"/>
+    <mergeCell ref="D186:N186"/>
+    <mergeCell ref="O186:U186"/>
+    <mergeCell ref="B187:C187"/>
+    <mergeCell ref="D187:N187"/>
+    <mergeCell ref="O187:U187"/>
+    <mergeCell ref="B184:C184"/>
+    <mergeCell ref="D184:N184"/>
+    <mergeCell ref="O184:U184"/>
+    <mergeCell ref="B185:C185"/>
+    <mergeCell ref="D185:N185"/>
+    <mergeCell ref="O185:U185"/>
+    <mergeCell ref="B182:C182"/>
+    <mergeCell ref="D182:N182"/>
+    <mergeCell ref="O182:U182"/>
+    <mergeCell ref="B183:C183"/>
+    <mergeCell ref="D183:N183"/>
+    <mergeCell ref="O183:U183"/>
+    <mergeCell ref="B180:C180"/>
+    <mergeCell ref="D180:N180"/>
+    <mergeCell ref="O180:U180"/>
+    <mergeCell ref="B181:C181"/>
+    <mergeCell ref="D181:N181"/>
+    <mergeCell ref="O181:U181"/>
+    <mergeCell ref="B178:C178"/>
+    <mergeCell ref="D178:N178"/>
+    <mergeCell ref="O178:U178"/>
+    <mergeCell ref="B179:C179"/>
+    <mergeCell ref="D179:N179"/>
+    <mergeCell ref="O179:U179"/>
+    <mergeCell ref="B176:C176"/>
+    <mergeCell ref="D176:N176"/>
+    <mergeCell ref="O176:U176"/>
+    <mergeCell ref="B177:C177"/>
+    <mergeCell ref="D177:N177"/>
+    <mergeCell ref="O177:U177"/>
+    <mergeCell ref="B174:C174"/>
+    <mergeCell ref="D174:N174"/>
+    <mergeCell ref="O174:U174"/>
+    <mergeCell ref="B175:C175"/>
+    <mergeCell ref="D175:N175"/>
+    <mergeCell ref="O175:U175"/>
+    <mergeCell ref="B172:C172"/>
+    <mergeCell ref="D172:N172"/>
+    <mergeCell ref="O172:U172"/>
+    <mergeCell ref="B173:C173"/>
+    <mergeCell ref="D173:N173"/>
+    <mergeCell ref="O173:U173"/>
+    <mergeCell ref="B170:C170"/>
+    <mergeCell ref="D170:N170"/>
+    <mergeCell ref="O170:U170"/>
+    <mergeCell ref="B171:C171"/>
+    <mergeCell ref="D171:N171"/>
+    <mergeCell ref="O171:U171"/>
+    <mergeCell ref="B165:C165"/>
+    <mergeCell ref="D165:N165"/>
+    <mergeCell ref="O165:U165"/>
+    <mergeCell ref="B167:U167"/>
+    <mergeCell ref="B169:C169"/>
+    <mergeCell ref="D169:N169"/>
+    <mergeCell ref="O169:U169"/>
+    <mergeCell ref="B163:C163"/>
+    <mergeCell ref="D163:N163"/>
+    <mergeCell ref="O163:U163"/>
+    <mergeCell ref="B164:C164"/>
+    <mergeCell ref="D164:N164"/>
+    <mergeCell ref="O164:U164"/>
+    <mergeCell ref="B168:U168"/>
+    <mergeCell ref="B161:C161"/>
+    <mergeCell ref="D161:N161"/>
+    <mergeCell ref="O161:U161"/>
+    <mergeCell ref="B162:C162"/>
+    <mergeCell ref="D162:N162"/>
+    <mergeCell ref="O162:U162"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="D159:N159"/>
+    <mergeCell ref="O159:U159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="D160:N160"/>
+    <mergeCell ref="O160:U160"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="D157:N157"/>
+    <mergeCell ref="O157:U157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="D158:N158"/>
+    <mergeCell ref="O158:U158"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="D155:N155"/>
+    <mergeCell ref="O155:U155"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="D156:N156"/>
+    <mergeCell ref="O156:U156"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="D153:N153"/>
+    <mergeCell ref="O153:U153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="D154:N154"/>
+    <mergeCell ref="O154:U154"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="D151:N151"/>
+    <mergeCell ref="O151:U151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="D152:N152"/>
+    <mergeCell ref="O152:U152"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="D149:N149"/>
+    <mergeCell ref="O149:U149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="D150:N150"/>
+    <mergeCell ref="O150:U150"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="D147:N147"/>
+    <mergeCell ref="O147:U147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="D148:N148"/>
+    <mergeCell ref="O148:U148"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="D145:N145"/>
+    <mergeCell ref="O145:U145"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="D146:N146"/>
+    <mergeCell ref="O146:U146"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="D143:N143"/>
+    <mergeCell ref="O143:U143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="D144:N144"/>
+    <mergeCell ref="O144:U144"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="D141:N141"/>
+    <mergeCell ref="O141:U141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="D142:N142"/>
+    <mergeCell ref="O142:U142"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="D139:N139"/>
+    <mergeCell ref="O139:U139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="D140:N140"/>
+    <mergeCell ref="O140:U140"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="D137:N137"/>
+    <mergeCell ref="O137:U137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="D138:N138"/>
+    <mergeCell ref="O138:U138"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="D132:N132"/>
+    <mergeCell ref="O132:U132"/>
+    <mergeCell ref="B134:U134"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="D136:N136"/>
+    <mergeCell ref="O136:U136"/>
+    <mergeCell ref="B135:U135"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="D130:N130"/>
+    <mergeCell ref="O130:U130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="D131:N131"/>
+    <mergeCell ref="O131:U131"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="D128:N128"/>
+    <mergeCell ref="O128:U128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="D129:N129"/>
+    <mergeCell ref="O129:U129"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="D126:N126"/>
+    <mergeCell ref="O126:U126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="D127:N127"/>
+    <mergeCell ref="O127:U127"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="D124:N124"/>
+    <mergeCell ref="O124:U124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="D125:N125"/>
+    <mergeCell ref="O125:U125"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="D122:N122"/>
+    <mergeCell ref="O122:U122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="D123:N123"/>
+    <mergeCell ref="O123:U123"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="D120:N120"/>
+    <mergeCell ref="O120:U120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="D121:N121"/>
+    <mergeCell ref="O121:U121"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="D118:N118"/>
+    <mergeCell ref="O118:U118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="D119:N119"/>
+    <mergeCell ref="O119:U119"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="D116:N116"/>
+    <mergeCell ref="O116:U116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="D117:N117"/>
+    <mergeCell ref="O117:U117"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="D114:N114"/>
+    <mergeCell ref="O114:U114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="D115:N115"/>
+    <mergeCell ref="O115:U115"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="D112:N112"/>
+    <mergeCell ref="O112:U112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="D113:N113"/>
+    <mergeCell ref="O113:U113"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="D110:N110"/>
+    <mergeCell ref="O110:U110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="D111:N111"/>
+    <mergeCell ref="O111:U111"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="D108:N108"/>
+    <mergeCell ref="O108:U108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="D109:N109"/>
+    <mergeCell ref="O109:U109"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="D106:N106"/>
+    <mergeCell ref="O106:U106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="D107:N107"/>
+    <mergeCell ref="O107:U107"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="D104:N104"/>
+    <mergeCell ref="O104:U104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="D105:N105"/>
+    <mergeCell ref="O105:U105"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:N99"/>
+    <mergeCell ref="O99:U99"/>
+    <mergeCell ref="B101:U101"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="D103:N103"/>
+    <mergeCell ref="O103:U103"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="D97:N97"/>
+    <mergeCell ref="O97:U97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="D98:N98"/>
+    <mergeCell ref="O98:U98"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="D95:N95"/>
+    <mergeCell ref="O95:U95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="D96:N96"/>
+    <mergeCell ref="O96:U96"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="D93:N93"/>
+    <mergeCell ref="O93:U93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="D94:N94"/>
+    <mergeCell ref="O94:U94"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="D91:N91"/>
+    <mergeCell ref="O91:U91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="D92:N92"/>
+    <mergeCell ref="O92:U92"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="D89:N89"/>
+    <mergeCell ref="O89:U89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="D90:N90"/>
+    <mergeCell ref="O90:U90"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="D87:N87"/>
+    <mergeCell ref="O87:U87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="D88:N88"/>
+    <mergeCell ref="O88:U88"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="D85:N85"/>
+    <mergeCell ref="O85:U85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="D86:N86"/>
+    <mergeCell ref="O86:U86"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="D83:N83"/>
+    <mergeCell ref="O83:U83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="D84:N84"/>
+    <mergeCell ref="O84:U84"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="D81:N81"/>
+    <mergeCell ref="O81:U81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:N82"/>
+    <mergeCell ref="O82:U82"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="D79:N79"/>
+    <mergeCell ref="O79:U79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="D80:N80"/>
+    <mergeCell ref="O80:U80"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="D77:N77"/>
+    <mergeCell ref="O77:U77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="D78:N78"/>
+    <mergeCell ref="O78:U78"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="D75:N75"/>
+    <mergeCell ref="O75:U75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="D76:N76"/>
+    <mergeCell ref="O76:U76"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="D73:N73"/>
+    <mergeCell ref="O73:U73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="D74:N74"/>
+    <mergeCell ref="O74:U74"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="D71:N71"/>
+    <mergeCell ref="O71:U71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="D72:N72"/>
+    <mergeCell ref="O72:U72"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="D66:N66"/>
+    <mergeCell ref="O66:U66"/>
+    <mergeCell ref="B68:U68"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="D70:N70"/>
+    <mergeCell ref="O70:U70"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:N64"/>
+    <mergeCell ref="O64:U64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:N65"/>
+    <mergeCell ref="O65:U65"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:N62"/>
+    <mergeCell ref="O62:U62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D63:N63"/>
+    <mergeCell ref="O63:U63"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:N60"/>
+    <mergeCell ref="O60:U60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:N61"/>
+    <mergeCell ref="O61:U61"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:N58"/>
+    <mergeCell ref="O58:U58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:N59"/>
+    <mergeCell ref="O59:U59"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:N56"/>
+    <mergeCell ref="O56:U56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:N57"/>
+    <mergeCell ref="O57:U57"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:N54"/>
+    <mergeCell ref="O54:U54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:N55"/>
+    <mergeCell ref="O55:U55"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:N52"/>
+    <mergeCell ref="O52:U52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:N53"/>
+    <mergeCell ref="O53:U53"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:N50"/>
+    <mergeCell ref="O50:U50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:N51"/>
+    <mergeCell ref="O51:U51"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:N48"/>
+    <mergeCell ref="O48:U48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:N49"/>
+    <mergeCell ref="O49:U49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:N46"/>
+    <mergeCell ref="O46:U46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:N47"/>
+    <mergeCell ref="O47:U47"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:N44"/>
+    <mergeCell ref="O44:U44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:N45"/>
+    <mergeCell ref="O45:U45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:N42"/>
+    <mergeCell ref="O42:U42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:N43"/>
+    <mergeCell ref="O43:U43"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:N40"/>
+    <mergeCell ref="O40:U40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:N41"/>
+    <mergeCell ref="O41:U41"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:N38"/>
+    <mergeCell ref="O38:U38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:N39"/>
+    <mergeCell ref="O39:U39"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:N33"/>
+    <mergeCell ref="O33:U33"/>
+    <mergeCell ref="B35:U35"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:N37"/>
+    <mergeCell ref="O37:U37"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:N31"/>
+    <mergeCell ref="O31:U31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:N32"/>
+    <mergeCell ref="O32:U32"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:N29"/>
+    <mergeCell ref="O29:U29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:N30"/>
+    <mergeCell ref="O30:U30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:N27"/>
+    <mergeCell ref="O27:U27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:N28"/>
+    <mergeCell ref="O28:U28"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:N25"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:N26"/>
+    <mergeCell ref="O26:U26"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:N23"/>
+    <mergeCell ref="O23:U23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:N24"/>
+    <mergeCell ref="O24:U24"/>
+    <mergeCell ref="O16:U16"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:N21"/>
+    <mergeCell ref="O21:U21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:N22"/>
+    <mergeCell ref="O22:U22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:N19"/>
+    <mergeCell ref="O19:U19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:N20"/>
+    <mergeCell ref="O20:U20"/>
+    <mergeCell ref="B1:U1"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:N3"/>
+    <mergeCell ref="O3:U3"/>
+    <mergeCell ref="B5:U5"/>
+    <mergeCell ref="B8:U8"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:N13"/>
+    <mergeCell ref="O13:U13"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:N11"/>
+    <mergeCell ref="O11:U11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:N12"/>
+    <mergeCell ref="O12:U12"/>
     <mergeCell ref="B194:C194"/>
     <mergeCell ref="D194:N194"/>
     <mergeCell ref="O194:U194"/>
@@ -11553,510 +12057,6 @@
     <mergeCell ref="O15:U15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:N16"/>
-    <mergeCell ref="B1:U1"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:N3"/>
-    <mergeCell ref="O3:U3"/>
-    <mergeCell ref="B5:U5"/>
-    <mergeCell ref="B8:U8"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:N13"/>
-    <mergeCell ref="O13:U13"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:N11"/>
-    <mergeCell ref="O11:U11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:N12"/>
-    <mergeCell ref="O12:U12"/>
-    <mergeCell ref="O16:U16"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:N21"/>
-    <mergeCell ref="O21:U21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:N22"/>
-    <mergeCell ref="O22:U22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:N19"/>
-    <mergeCell ref="O19:U19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:N20"/>
-    <mergeCell ref="O20:U20"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:N25"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:N26"/>
-    <mergeCell ref="O26:U26"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:N23"/>
-    <mergeCell ref="O23:U23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:N24"/>
-    <mergeCell ref="O24:U24"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:N29"/>
-    <mergeCell ref="O29:U29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:N30"/>
-    <mergeCell ref="O30:U30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:N27"/>
-    <mergeCell ref="O27:U27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:N28"/>
-    <mergeCell ref="O28:U28"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:N33"/>
-    <mergeCell ref="O33:U33"/>
-    <mergeCell ref="B35:U35"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:N37"/>
-    <mergeCell ref="O37:U37"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:N31"/>
-    <mergeCell ref="O31:U31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:N32"/>
-    <mergeCell ref="O32:U32"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:N40"/>
-    <mergeCell ref="O40:U40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:N41"/>
-    <mergeCell ref="O41:U41"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:N38"/>
-    <mergeCell ref="O38:U38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:N39"/>
-    <mergeCell ref="O39:U39"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:N44"/>
-    <mergeCell ref="O44:U44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:N45"/>
-    <mergeCell ref="O45:U45"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:N42"/>
-    <mergeCell ref="O42:U42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:N43"/>
-    <mergeCell ref="O43:U43"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:N48"/>
-    <mergeCell ref="O48:U48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:N49"/>
-    <mergeCell ref="O49:U49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:N46"/>
-    <mergeCell ref="O46:U46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:N47"/>
-    <mergeCell ref="O47:U47"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:N52"/>
-    <mergeCell ref="O52:U52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:N53"/>
-    <mergeCell ref="O53:U53"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:N50"/>
-    <mergeCell ref="O50:U50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:N51"/>
-    <mergeCell ref="O51:U51"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:N56"/>
-    <mergeCell ref="O56:U56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:N57"/>
-    <mergeCell ref="O57:U57"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:N54"/>
-    <mergeCell ref="O54:U54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:N55"/>
-    <mergeCell ref="O55:U55"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:N60"/>
-    <mergeCell ref="O60:U60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="D61:N61"/>
-    <mergeCell ref="O61:U61"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:N58"/>
-    <mergeCell ref="O58:U58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:N59"/>
-    <mergeCell ref="O59:U59"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="D64:N64"/>
-    <mergeCell ref="O64:U64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:N65"/>
-    <mergeCell ref="O65:U65"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:N62"/>
-    <mergeCell ref="O62:U62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D63:N63"/>
-    <mergeCell ref="O63:U63"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="D71:N71"/>
-    <mergeCell ref="O71:U71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="D72:N72"/>
-    <mergeCell ref="O72:U72"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="D66:N66"/>
-    <mergeCell ref="O66:U66"/>
-    <mergeCell ref="B68:U68"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="D70:N70"/>
-    <mergeCell ref="O70:U70"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="D75:N75"/>
-    <mergeCell ref="O75:U75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="D76:N76"/>
-    <mergeCell ref="O76:U76"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="D73:N73"/>
-    <mergeCell ref="O73:U73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="D74:N74"/>
-    <mergeCell ref="O74:U74"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="D79:N79"/>
-    <mergeCell ref="O79:U79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="D80:N80"/>
-    <mergeCell ref="O80:U80"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="D77:N77"/>
-    <mergeCell ref="O77:U77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="D78:N78"/>
-    <mergeCell ref="O78:U78"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="D83:N83"/>
-    <mergeCell ref="O83:U83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="D84:N84"/>
-    <mergeCell ref="O84:U84"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="D81:N81"/>
-    <mergeCell ref="O81:U81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:N82"/>
-    <mergeCell ref="O82:U82"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="D87:N87"/>
-    <mergeCell ref="O87:U87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="D88:N88"/>
-    <mergeCell ref="O88:U88"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="D85:N85"/>
-    <mergeCell ref="O85:U85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="D86:N86"/>
-    <mergeCell ref="O86:U86"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="D91:N91"/>
-    <mergeCell ref="O91:U91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="D92:N92"/>
-    <mergeCell ref="O92:U92"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="D89:N89"/>
-    <mergeCell ref="O89:U89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="D90:N90"/>
-    <mergeCell ref="O90:U90"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="D95:N95"/>
-    <mergeCell ref="O95:U95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="D96:N96"/>
-    <mergeCell ref="O96:U96"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="D93:N93"/>
-    <mergeCell ref="O93:U93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="D94:N94"/>
-    <mergeCell ref="O94:U94"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:N99"/>
-    <mergeCell ref="O99:U99"/>
-    <mergeCell ref="B101:U101"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="D103:N103"/>
-    <mergeCell ref="O103:U103"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="D97:N97"/>
-    <mergeCell ref="O97:U97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="D98:N98"/>
-    <mergeCell ref="O98:U98"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="D106:N106"/>
-    <mergeCell ref="O106:U106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="D107:N107"/>
-    <mergeCell ref="O107:U107"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="D104:N104"/>
-    <mergeCell ref="O104:U104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="D105:N105"/>
-    <mergeCell ref="O105:U105"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="D110:N110"/>
-    <mergeCell ref="O110:U110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="D111:N111"/>
-    <mergeCell ref="O111:U111"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="D108:N108"/>
-    <mergeCell ref="O108:U108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="D109:N109"/>
-    <mergeCell ref="O109:U109"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="D114:N114"/>
-    <mergeCell ref="O114:U114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="D115:N115"/>
-    <mergeCell ref="O115:U115"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="D112:N112"/>
-    <mergeCell ref="O112:U112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="D113:N113"/>
-    <mergeCell ref="O113:U113"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="D118:N118"/>
-    <mergeCell ref="O118:U118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="D119:N119"/>
-    <mergeCell ref="O119:U119"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="D116:N116"/>
-    <mergeCell ref="O116:U116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="D117:N117"/>
-    <mergeCell ref="O117:U117"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="D122:N122"/>
-    <mergeCell ref="O122:U122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="D123:N123"/>
-    <mergeCell ref="O123:U123"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="D120:N120"/>
-    <mergeCell ref="O120:U120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="D121:N121"/>
-    <mergeCell ref="O121:U121"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="D126:N126"/>
-    <mergeCell ref="O126:U126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="D127:N127"/>
-    <mergeCell ref="O127:U127"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="D124:N124"/>
-    <mergeCell ref="O124:U124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="D125:N125"/>
-    <mergeCell ref="O125:U125"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="D130:N130"/>
-    <mergeCell ref="O130:U130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="D131:N131"/>
-    <mergeCell ref="O131:U131"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="D128:N128"/>
-    <mergeCell ref="O128:U128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="D129:N129"/>
-    <mergeCell ref="O129:U129"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="D137:N137"/>
-    <mergeCell ref="O137:U137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="D138:N138"/>
-    <mergeCell ref="O138:U138"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="D132:N132"/>
-    <mergeCell ref="O132:U132"/>
-    <mergeCell ref="B134:U134"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="D136:N136"/>
-    <mergeCell ref="O136:U136"/>
-    <mergeCell ref="B135:U135"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="D141:N141"/>
-    <mergeCell ref="O141:U141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="D142:N142"/>
-    <mergeCell ref="O142:U142"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="D139:N139"/>
-    <mergeCell ref="O139:U139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="D140:N140"/>
-    <mergeCell ref="O140:U140"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="D145:N145"/>
-    <mergeCell ref="O145:U145"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="D146:N146"/>
-    <mergeCell ref="O146:U146"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="D143:N143"/>
-    <mergeCell ref="O143:U143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="D144:N144"/>
-    <mergeCell ref="O144:U144"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="D149:N149"/>
-    <mergeCell ref="O149:U149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="D150:N150"/>
-    <mergeCell ref="O150:U150"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="D147:N147"/>
-    <mergeCell ref="O147:U147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="D148:N148"/>
-    <mergeCell ref="O148:U148"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="D153:N153"/>
-    <mergeCell ref="O153:U153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="D154:N154"/>
-    <mergeCell ref="O154:U154"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="D151:N151"/>
-    <mergeCell ref="O151:U151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="D152:N152"/>
-    <mergeCell ref="O152:U152"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="D157:N157"/>
-    <mergeCell ref="O157:U157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="D158:N158"/>
-    <mergeCell ref="O158:U158"/>
-    <mergeCell ref="B155:C155"/>
-    <mergeCell ref="D155:N155"/>
-    <mergeCell ref="O155:U155"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="D156:N156"/>
-    <mergeCell ref="O156:U156"/>
-    <mergeCell ref="B161:C161"/>
-    <mergeCell ref="D161:N161"/>
-    <mergeCell ref="O161:U161"/>
-    <mergeCell ref="B162:C162"/>
-    <mergeCell ref="D162:N162"/>
-    <mergeCell ref="O162:U162"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="D159:N159"/>
-    <mergeCell ref="O159:U159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="D160:N160"/>
-    <mergeCell ref="O160:U160"/>
-    <mergeCell ref="B165:C165"/>
-    <mergeCell ref="D165:N165"/>
-    <mergeCell ref="O165:U165"/>
-    <mergeCell ref="B167:U167"/>
-    <mergeCell ref="B169:C169"/>
-    <mergeCell ref="D169:N169"/>
-    <mergeCell ref="O169:U169"/>
-    <mergeCell ref="B163:C163"/>
-    <mergeCell ref="D163:N163"/>
-    <mergeCell ref="O163:U163"/>
-    <mergeCell ref="B164:C164"/>
-    <mergeCell ref="D164:N164"/>
-    <mergeCell ref="O164:U164"/>
-    <mergeCell ref="B168:U168"/>
-    <mergeCell ref="B172:C172"/>
-    <mergeCell ref="D172:N172"/>
-    <mergeCell ref="O172:U172"/>
-    <mergeCell ref="B173:C173"/>
-    <mergeCell ref="D173:N173"/>
-    <mergeCell ref="O173:U173"/>
-    <mergeCell ref="B170:C170"/>
-    <mergeCell ref="D170:N170"/>
-    <mergeCell ref="O170:U170"/>
-    <mergeCell ref="B171:C171"/>
-    <mergeCell ref="D171:N171"/>
-    <mergeCell ref="O171:U171"/>
-    <mergeCell ref="B176:C176"/>
-    <mergeCell ref="D176:N176"/>
-    <mergeCell ref="O176:U176"/>
-    <mergeCell ref="B177:C177"/>
-    <mergeCell ref="D177:N177"/>
-    <mergeCell ref="O177:U177"/>
-    <mergeCell ref="B174:C174"/>
-    <mergeCell ref="D174:N174"/>
-    <mergeCell ref="O174:U174"/>
-    <mergeCell ref="B175:C175"/>
-    <mergeCell ref="D175:N175"/>
-    <mergeCell ref="O175:U175"/>
-    <mergeCell ref="B180:C180"/>
-    <mergeCell ref="D180:N180"/>
-    <mergeCell ref="O180:U180"/>
-    <mergeCell ref="B181:C181"/>
-    <mergeCell ref="D181:N181"/>
-    <mergeCell ref="O181:U181"/>
-    <mergeCell ref="B178:C178"/>
-    <mergeCell ref="D178:N178"/>
-    <mergeCell ref="O178:U178"/>
-    <mergeCell ref="B179:C179"/>
-    <mergeCell ref="D179:N179"/>
-    <mergeCell ref="O179:U179"/>
-    <mergeCell ref="O187:U187"/>
-    <mergeCell ref="B184:C184"/>
-    <mergeCell ref="D184:N184"/>
-    <mergeCell ref="O184:U184"/>
-    <mergeCell ref="B185:C185"/>
-    <mergeCell ref="D185:N185"/>
-    <mergeCell ref="O185:U185"/>
-    <mergeCell ref="B182:C182"/>
-    <mergeCell ref="D182:N182"/>
-    <mergeCell ref="O182:U182"/>
-    <mergeCell ref="B183:C183"/>
-    <mergeCell ref="D183:N183"/>
-    <mergeCell ref="O183:U183"/>
-    <mergeCell ref="B193:C193"/>
-    <mergeCell ref="D193:N193"/>
-    <mergeCell ref="O193:U193"/>
-    <mergeCell ref="B192:C192"/>
-    <mergeCell ref="D192:N192"/>
-    <mergeCell ref="O192:U192"/>
-    <mergeCell ref="V3:AI3"/>
-    <mergeCell ref="B190:C190"/>
-    <mergeCell ref="D190:N190"/>
-    <mergeCell ref="O190:U190"/>
-    <mergeCell ref="B191:C191"/>
-    <mergeCell ref="D191:N191"/>
-    <mergeCell ref="O191:U191"/>
-    <mergeCell ref="B188:C188"/>
-    <mergeCell ref="D188:N188"/>
-    <mergeCell ref="O188:U188"/>
-    <mergeCell ref="B189:C189"/>
-    <mergeCell ref="D189:N189"/>
-    <mergeCell ref="O189:U189"/>
-    <mergeCell ref="B186:C186"/>
-    <mergeCell ref="D186:N186"/>
-    <mergeCell ref="O186:U186"/>
-    <mergeCell ref="B187:C187"/>
-    <mergeCell ref="D187:N187"/>
   </mergeCells>
   <pageMargins left="0.39370078740157477" right="0.39370078740157477" top="0.39370078740157477" bottom="0.39370078740157477" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>

--- a/Журнал.xlsx
+++ b/Журнал.xlsx
@@ -1293,8 +1293,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1307,24 +1325,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1718,70 +1718,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
     </row>
     <row r="2" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="24" t="s">
+      <c r="B3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="23" t="s">
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="T3" s="23"/>
-      <c r="U3" s="23"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="30"/>
-      <c r="AF3" s="30"/>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="31"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
+      <c r="Y3" s="22"/>
+      <c r="Z3" s="22"/>
+      <c r="AA3" s="22"/>
+      <c r="AB3" s="22"/>
+      <c r="AC3" s="22"/>
+      <c r="AD3" s="22"/>
+      <c r="AE3" s="22"/>
+      <c r="AF3" s="22"/>
+      <c r="AG3" s="22"/>
+      <c r="AH3" s="22"/>
+      <c r="AI3" s="23"/>
     </row>
     <row r="4" spans="1:35" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4"/>
@@ -1808,28 +1808,28 @@
       <c r="V4"/>
     </row>
     <row r="5" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
+      <c r="B5" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="31"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="31"/>
+      <c r="U5" s="31"/>
       <c r="V5" s="8"/>
       <c r="W5" s="9"/>
       <c r="X5" s="9"/>
@@ -1870,28 +1870,28 @@
       <c r="V6"/>
     </row>
     <row r="7" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
-      <c r="T7" s="21"/>
-      <c r="U7" s="21"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="24"/>
       <c r="V7" s="8"/>
       <c r="W7" s="9"/>
       <c r="X7" s="9"/>
@@ -1909,26 +1909,26 @@
     </row>
     <row r="8" spans="1:35" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="27"/>
-      <c r="R8" s="27"/>
-      <c r="S8" s="27"/>
-      <c r="T8" s="27"/>
-      <c r="U8" s="28"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="27"/>
       <c r="V8" s="10">
         <v>0</v>
       </c>
@@ -3301,28 +3301,28 @@
       <c r="V34"/>
     </row>
     <row r="35" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
-      <c r="M35" s="21"/>
-      <c r="N35" s="21"/>
-      <c r="O35" s="21"/>
-      <c r="P35" s="21"/>
-      <c r="Q35" s="21"/>
-      <c r="R35" s="21"/>
-      <c r="S35" s="21"/>
-      <c r="T35" s="21"/>
-      <c r="U35" s="21"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="24"/>
+      <c r="Q35" s="24"/>
+      <c r="R35" s="24"/>
+      <c r="S35" s="24"/>
+      <c r="T35" s="24"/>
+      <c r="U35" s="24"/>
       <c r="V35" s="8"/>
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
@@ -4993,28 +4993,28 @@
     </row>
     <row r="68" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
-      <c r="B68" s="21" t="s">
+      <c r="B68" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="21"/>
-      <c r="L68" s="21"/>
-      <c r="M68" s="21"/>
-      <c r="N68" s="21"/>
-      <c r="O68" s="21"/>
-      <c r="P68" s="21"/>
-      <c r="Q68" s="21"/>
-      <c r="R68" s="21"/>
-      <c r="S68" s="21"/>
-      <c r="T68" s="21"/>
-      <c r="U68" s="21"/>
+      <c r="C68" s="24"/>
+      <c r="D68" s="24"/>
+      <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="24"/>
+      <c r="J68" s="24"/>
+      <c r="K68" s="24"/>
+      <c r="L68" s="24"/>
+      <c r="M68" s="24"/>
+      <c r="N68" s="24"/>
+      <c r="O68" s="24"/>
+      <c r="P68" s="24"/>
+      <c r="Q68" s="24"/>
+      <c r="R68" s="24"/>
+      <c r="S68" s="24"/>
+      <c r="T68" s="24"/>
+      <c r="U68" s="24"/>
       <c r="V68" s="8"/>
       <c r="W68" s="9"/>
       <c r="X68" s="9"/>
@@ -6685,28 +6685,28 @@
       <c r="V100"/>
     </row>
     <row r="101" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B101" s="21" t="s">
+      <c r="B101" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="C101" s="21"/>
-      <c r="D101" s="21"/>
-      <c r="E101" s="21"/>
-      <c r="F101" s="21"/>
-      <c r="G101" s="21"/>
-      <c r="H101" s="21"/>
-      <c r="I101" s="21"/>
-      <c r="J101" s="21"/>
-      <c r="K101" s="21"/>
-      <c r="L101" s="21"/>
-      <c r="M101" s="21"/>
-      <c r="N101" s="21"/>
-      <c r="O101" s="21"/>
-      <c r="P101" s="21"/>
-      <c r="Q101" s="21"/>
-      <c r="R101" s="21"/>
-      <c r="S101" s="21"/>
-      <c r="T101" s="21"/>
-      <c r="U101" s="21"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+      <c r="I101" s="24"/>
+      <c r="J101" s="24"/>
+      <c r="K101" s="24"/>
+      <c r="L101" s="24"/>
+      <c r="M101" s="24"/>
+      <c r="N101" s="24"/>
+      <c r="O101" s="24"/>
+      <c r="P101" s="24"/>
+      <c r="Q101" s="24"/>
+      <c r="R101" s="24"/>
+      <c r="S101" s="24"/>
+      <c r="T101" s="24"/>
+      <c r="U101" s="24"/>
       <c r="V101" s="8"/>
       <c r="W101" s="9"/>
       <c r="X101" s="9"/>
@@ -8377,28 +8377,28 @@
       <c r="V133"/>
     </row>
     <row r="134" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B134" s="21" t="s">
+      <c r="B134" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="C134" s="21"/>
-      <c r="D134" s="21"/>
-      <c r="E134" s="21"/>
-      <c r="F134" s="21"/>
-      <c r="G134" s="21"/>
-      <c r="H134" s="21"/>
-      <c r="I134" s="21"/>
-      <c r="J134" s="21"/>
-      <c r="K134" s="21"/>
-      <c r="L134" s="21"/>
-      <c r="M134" s="21"/>
-      <c r="N134" s="21"/>
-      <c r="O134" s="21"/>
-      <c r="P134" s="21"/>
-      <c r="Q134" s="21"/>
-      <c r="R134" s="21"/>
-      <c r="S134" s="21"/>
-      <c r="T134" s="21"/>
-      <c r="U134" s="21"/>
+      <c r="C134" s="24"/>
+      <c r="D134" s="24"/>
+      <c r="E134" s="24"/>
+      <c r="F134" s="24"/>
+      <c r="G134" s="24"/>
+      <c r="H134" s="24"/>
+      <c r="I134" s="24"/>
+      <c r="J134" s="24"/>
+      <c r="K134" s="24"/>
+      <c r="L134" s="24"/>
+      <c r="M134" s="24"/>
+      <c r="N134" s="24"/>
+      <c r="O134" s="24"/>
+      <c r="P134" s="24"/>
+      <c r="Q134" s="24"/>
+      <c r="R134" s="24"/>
+      <c r="S134" s="24"/>
+      <c r="T134" s="24"/>
+      <c r="U134" s="24"/>
       <c r="V134" s="8"/>
       <c r="W134" s="9"/>
       <c r="X134" s="9"/>
@@ -8417,26 +8417,26 @@
     </row>
     <row r="135" spans="1:36" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135"/>
-      <c r="B135" s="26"/>
-      <c r="C135" s="27"/>
-      <c r="D135" s="27"/>
-      <c r="E135" s="27"/>
-      <c r="F135" s="27"/>
-      <c r="G135" s="27"/>
-      <c r="H135" s="27"/>
-      <c r="I135" s="27"/>
-      <c r="J135" s="27"/>
-      <c r="K135" s="27"/>
-      <c r="L135" s="27"/>
-      <c r="M135" s="27"/>
-      <c r="N135" s="27"/>
-      <c r="O135" s="27"/>
-      <c r="P135" s="27"/>
-      <c r="Q135" s="27"/>
-      <c r="R135" s="27"/>
-      <c r="S135" s="27"/>
-      <c r="T135" s="27"/>
-      <c r="U135" s="28"/>
+      <c r="B135" s="25"/>
+      <c r="C135" s="26"/>
+      <c r="D135" s="26"/>
+      <c r="E135" s="26"/>
+      <c r="F135" s="26"/>
+      <c r="G135" s="26"/>
+      <c r="H135" s="26"/>
+      <c r="I135" s="26"/>
+      <c r="J135" s="26"/>
+      <c r="K135" s="26"/>
+      <c r="L135" s="26"/>
+      <c r="M135" s="26"/>
+      <c r="N135" s="26"/>
+      <c r="O135" s="26"/>
+      <c r="P135" s="26"/>
+      <c r="Q135" s="26"/>
+      <c r="R135" s="26"/>
+      <c r="S135" s="26"/>
+      <c r="T135" s="26"/>
+      <c r="U135" s="27"/>
       <c r="V135" s="10">
         <v>0</v>
       </c>
@@ -9868,7 +9868,7 @@
         <v>3</v>
       </c>
       <c r="W162" s="12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X162" s="12">
         <v>3</v>
@@ -9882,7 +9882,7 @@
       <c r="AE162" s="6"/>
       <c r="AF162" s="17">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG162" s="7"/>
       <c r="AH162" s="7"/>
@@ -10069,28 +10069,28 @@
       <c r="V166"/>
     </row>
     <row r="167" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B167" s="21" t="s">
+      <c r="B167" s="24" t="s">
         <v>299</v>
       </c>
-      <c r="C167" s="21"/>
-      <c r="D167" s="21"/>
-      <c r="E167" s="21"/>
-      <c r="F167" s="21"/>
-      <c r="G167" s="21"/>
-      <c r="H167" s="21"/>
-      <c r="I167" s="21"/>
-      <c r="J167" s="21"/>
-      <c r="K167" s="21"/>
-      <c r="L167" s="21"/>
-      <c r="M167" s="21"/>
-      <c r="N167" s="21"/>
-      <c r="O167" s="21"/>
-      <c r="P167" s="21"/>
-      <c r="Q167" s="21"/>
-      <c r="R167" s="21"/>
-      <c r="S167" s="21"/>
-      <c r="T167" s="21"/>
-      <c r="U167" s="21"/>
+      <c r="C167" s="24"/>
+      <c r="D167" s="24"/>
+      <c r="E167" s="24"/>
+      <c r="F167" s="24"/>
+      <c r="G167" s="24"/>
+      <c r="H167" s="24"/>
+      <c r="I167" s="24"/>
+      <c r="J167" s="24"/>
+      <c r="K167" s="24"/>
+      <c r="L167" s="24"/>
+      <c r="M167" s="24"/>
+      <c r="N167" s="24"/>
+      <c r="O167" s="24"/>
+      <c r="P167" s="24"/>
+      <c r="Q167" s="24"/>
+      <c r="R167" s="24"/>
+      <c r="S167" s="24"/>
+      <c r="T167" s="24"/>
+      <c r="U167" s="24"/>
       <c r="V167" s="8"/>
       <c r="W167" s="9"/>
       <c r="X167" s="9"/>
@@ -10109,26 +10109,26 @@
     </row>
     <row r="168" spans="1:36" ht="19.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168"/>
-      <c r="B168" s="26"/>
-      <c r="C168" s="27"/>
-      <c r="D168" s="27"/>
-      <c r="E168" s="27"/>
-      <c r="F168" s="27"/>
-      <c r="G168" s="27"/>
-      <c r="H168" s="27"/>
-      <c r="I168" s="27"/>
-      <c r="J168" s="27"/>
-      <c r="K168" s="27"/>
-      <c r="L168" s="27"/>
-      <c r="M168" s="27"/>
-      <c r="N168" s="27"/>
-      <c r="O168" s="27"/>
-      <c r="P168" s="27"/>
-      <c r="Q168" s="27"/>
-      <c r="R168" s="27"/>
-      <c r="S168" s="27"/>
-      <c r="T168" s="27"/>
-      <c r="U168" s="28"/>
+      <c r="B168" s="25"/>
+      <c r="C168" s="26"/>
+      <c r="D168" s="26"/>
+      <c r="E168" s="26"/>
+      <c r="F168" s="26"/>
+      <c r="G168" s="26"/>
+      <c r="H168" s="26"/>
+      <c r="I168" s="26"/>
+      <c r="J168" s="26"/>
+      <c r="K168" s="26"/>
+      <c r="L168" s="26"/>
+      <c r="M168" s="26"/>
+      <c r="N168" s="26"/>
+      <c r="O168" s="26"/>
+      <c r="P168" s="26"/>
+      <c r="Q168" s="26"/>
+      <c r="R168" s="26"/>
+      <c r="S168" s="26"/>
+      <c r="T168" s="26"/>
+      <c r="U168" s="27"/>
       <c r="V168" s="10">
         <v>0</v>
       </c>
@@ -11529,6 +11529,510 @@
     </row>
   </sheetData>
   <mergeCells count="528">
+    <mergeCell ref="B194:C194"/>
+    <mergeCell ref="D194:N194"/>
+    <mergeCell ref="O194:U194"/>
+    <mergeCell ref="B7:U7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:N9"/>
+    <mergeCell ref="O9:U9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:N10"/>
+    <mergeCell ref="O10:U10"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:N14"/>
+    <mergeCell ref="O14:U14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:N17"/>
+    <mergeCell ref="O17:U17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:N18"/>
+    <mergeCell ref="O18:U18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:N15"/>
+    <mergeCell ref="O15:U15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:N16"/>
+    <mergeCell ref="B1:U1"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:N3"/>
+    <mergeCell ref="O3:U3"/>
+    <mergeCell ref="B5:U5"/>
+    <mergeCell ref="B8:U8"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:N13"/>
+    <mergeCell ref="O13:U13"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:N11"/>
+    <mergeCell ref="O11:U11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:N12"/>
+    <mergeCell ref="O12:U12"/>
+    <mergeCell ref="O16:U16"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:N21"/>
+    <mergeCell ref="O21:U21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:N22"/>
+    <mergeCell ref="O22:U22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:N19"/>
+    <mergeCell ref="O19:U19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:N20"/>
+    <mergeCell ref="O20:U20"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:N25"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:N26"/>
+    <mergeCell ref="O26:U26"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:N23"/>
+    <mergeCell ref="O23:U23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:N24"/>
+    <mergeCell ref="O24:U24"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:N29"/>
+    <mergeCell ref="O29:U29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:N30"/>
+    <mergeCell ref="O30:U30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:N27"/>
+    <mergeCell ref="O27:U27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:N28"/>
+    <mergeCell ref="O28:U28"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:N33"/>
+    <mergeCell ref="O33:U33"/>
+    <mergeCell ref="B35:U35"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:N37"/>
+    <mergeCell ref="O37:U37"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:N31"/>
+    <mergeCell ref="O31:U31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:N32"/>
+    <mergeCell ref="O32:U32"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:N40"/>
+    <mergeCell ref="O40:U40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:N41"/>
+    <mergeCell ref="O41:U41"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:N38"/>
+    <mergeCell ref="O38:U38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:N39"/>
+    <mergeCell ref="O39:U39"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:N44"/>
+    <mergeCell ref="O44:U44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:N45"/>
+    <mergeCell ref="O45:U45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:N42"/>
+    <mergeCell ref="O42:U42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:N43"/>
+    <mergeCell ref="O43:U43"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:N48"/>
+    <mergeCell ref="O48:U48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:N49"/>
+    <mergeCell ref="O49:U49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:N46"/>
+    <mergeCell ref="O46:U46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:N47"/>
+    <mergeCell ref="O47:U47"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:N52"/>
+    <mergeCell ref="O52:U52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:N53"/>
+    <mergeCell ref="O53:U53"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:N50"/>
+    <mergeCell ref="O50:U50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:N51"/>
+    <mergeCell ref="O51:U51"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:N56"/>
+    <mergeCell ref="O56:U56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:N57"/>
+    <mergeCell ref="O57:U57"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:N54"/>
+    <mergeCell ref="O54:U54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:N55"/>
+    <mergeCell ref="O55:U55"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:N60"/>
+    <mergeCell ref="O60:U60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:N61"/>
+    <mergeCell ref="O61:U61"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:N58"/>
+    <mergeCell ref="O58:U58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:N59"/>
+    <mergeCell ref="O59:U59"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:N64"/>
+    <mergeCell ref="O64:U64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:N65"/>
+    <mergeCell ref="O65:U65"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:N62"/>
+    <mergeCell ref="O62:U62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D63:N63"/>
+    <mergeCell ref="O63:U63"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="D71:N71"/>
+    <mergeCell ref="O71:U71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="D72:N72"/>
+    <mergeCell ref="O72:U72"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="D66:N66"/>
+    <mergeCell ref="O66:U66"/>
+    <mergeCell ref="B68:U68"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="D70:N70"/>
+    <mergeCell ref="O70:U70"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="D75:N75"/>
+    <mergeCell ref="O75:U75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="D76:N76"/>
+    <mergeCell ref="O76:U76"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="D73:N73"/>
+    <mergeCell ref="O73:U73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="D74:N74"/>
+    <mergeCell ref="O74:U74"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="D79:N79"/>
+    <mergeCell ref="O79:U79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="D80:N80"/>
+    <mergeCell ref="O80:U80"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="D77:N77"/>
+    <mergeCell ref="O77:U77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="D78:N78"/>
+    <mergeCell ref="O78:U78"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="D83:N83"/>
+    <mergeCell ref="O83:U83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="D84:N84"/>
+    <mergeCell ref="O84:U84"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="D81:N81"/>
+    <mergeCell ref="O81:U81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:N82"/>
+    <mergeCell ref="O82:U82"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="D87:N87"/>
+    <mergeCell ref="O87:U87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="D88:N88"/>
+    <mergeCell ref="O88:U88"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="D85:N85"/>
+    <mergeCell ref="O85:U85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="D86:N86"/>
+    <mergeCell ref="O86:U86"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="D91:N91"/>
+    <mergeCell ref="O91:U91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="D92:N92"/>
+    <mergeCell ref="O92:U92"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="D89:N89"/>
+    <mergeCell ref="O89:U89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="D90:N90"/>
+    <mergeCell ref="O90:U90"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="D95:N95"/>
+    <mergeCell ref="O95:U95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="D96:N96"/>
+    <mergeCell ref="O96:U96"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="D93:N93"/>
+    <mergeCell ref="O93:U93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="D94:N94"/>
+    <mergeCell ref="O94:U94"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:N99"/>
+    <mergeCell ref="O99:U99"/>
+    <mergeCell ref="B101:U101"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="D103:N103"/>
+    <mergeCell ref="O103:U103"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="D97:N97"/>
+    <mergeCell ref="O97:U97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="D98:N98"/>
+    <mergeCell ref="O98:U98"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="D106:N106"/>
+    <mergeCell ref="O106:U106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="D107:N107"/>
+    <mergeCell ref="O107:U107"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="D104:N104"/>
+    <mergeCell ref="O104:U104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="D105:N105"/>
+    <mergeCell ref="O105:U105"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="D110:N110"/>
+    <mergeCell ref="O110:U110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="D111:N111"/>
+    <mergeCell ref="O111:U111"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="D108:N108"/>
+    <mergeCell ref="O108:U108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="D109:N109"/>
+    <mergeCell ref="O109:U109"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="D114:N114"/>
+    <mergeCell ref="O114:U114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="D115:N115"/>
+    <mergeCell ref="O115:U115"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="D112:N112"/>
+    <mergeCell ref="O112:U112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="D113:N113"/>
+    <mergeCell ref="O113:U113"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="D118:N118"/>
+    <mergeCell ref="O118:U118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="D119:N119"/>
+    <mergeCell ref="O119:U119"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="D116:N116"/>
+    <mergeCell ref="O116:U116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="D117:N117"/>
+    <mergeCell ref="O117:U117"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="D122:N122"/>
+    <mergeCell ref="O122:U122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="D123:N123"/>
+    <mergeCell ref="O123:U123"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="D120:N120"/>
+    <mergeCell ref="O120:U120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="D121:N121"/>
+    <mergeCell ref="O121:U121"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="D126:N126"/>
+    <mergeCell ref="O126:U126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="D127:N127"/>
+    <mergeCell ref="O127:U127"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="D124:N124"/>
+    <mergeCell ref="O124:U124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="D125:N125"/>
+    <mergeCell ref="O125:U125"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="D130:N130"/>
+    <mergeCell ref="O130:U130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="D131:N131"/>
+    <mergeCell ref="O131:U131"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="D128:N128"/>
+    <mergeCell ref="O128:U128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="D129:N129"/>
+    <mergeCell ref="O129:U129"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="D137:N137"/>
+    <mergeCell ref="O137:U137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="D138:N138"/>
+    <mergeCell ref="O138:U138"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="D132:N132"/>
+    <mergeCell ref="O132:U132"/>
+    <mergeCell ref="B134:U134"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="D136:N136"/>
+    <mergeCell ref="O136:U136"/>
+    <mergeCell ref="B135:U135"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="D141:N141"/>
+    <mergeCell ref="O141:U141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="D142:N142"/>
+    <mergeCell ref="O142:U142"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="D139:N139"/>
+    <mergeCell ref="O139:U139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="D140:N140"/>
+    <mergeCell ref="O140:U140"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="D145:N145"/>
+    <mergeCell ref="O145:U145"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="D146:N146"/>
+    <mergeCell ref="O146:U146"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="D143:N143"/>
+    <mergeCell ref="O143:U143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="D144:N144"/>
+    <mergeCell ref="O144:U144"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="D149:N149"/>
+    <mergeCell ref="O149:U149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="D150:N150"/>
+    <mergeCell ref="O150:U150"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="D147:N147"/>
+    <mergeCell ref="O147:U147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="D148:N148"/>
+    <mergeCell ref="O148:U148"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="D153:N153"/>
+    <mergeCell ref="O153:U153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="D154:N154"/>
+    <mergeCell ref="O154:U154"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="D151:N151"/>
+    <mergeCell ref="O151:U151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="D152:N152"/>
+    <mergeCell ref="O152:U152"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="D157:N157"/>
+    <mergeCell ref="O157:U157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="D158:N158"/>
+    <mergeCell ref="O158:U158"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="D155:N155"/>
+    <mergeCell ref="O155:U155"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="D156:N156"/>
+    <mergeCell ref="O156:U156"/>
+    <mergeCell ref="B161:C161"/>
+    <mergeCell ref="D161:N161"/>
+    <mergeCell ref="O161:U161"/>
+    <mergeCell ref="B162:C162"/>
+    <mergeCell ref="D162:N162"/>
+    <mergeCell ref="O162:U162"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="D159:N159"/>
+    <mergeCell ref="O159:U159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="D160:N160"/>
+    <mergeCell ref="O160:U160"/>
+    <mergeCell ref="B165:C165"/>
+    <mergeCell ref="D165:N165"/>
+    <mergeCell ref="O165:U165"/>
+    <mergeCell ref="B167:U167"/>
+    <mergeCell ref="B169:C169"/>
+    <mergeCell ref="D169:N169"/>
+    <mergeCell ref="O169:U169"/>
+    <mergeCell ref="B163:C163"/>
+    <mergeCell ref="D163:N163"/>
+    <mergeCell ref="O163:U163"/>
+    <mergeCell ref="B164:C164"/>
+    <mergeCell ref="D164:N164"/>
+    <mergeCell ref="O164:U164"/>
+    <mergeCell ref="B168:U168"/>
+    <mergeCell ref="B172:C172"/>
+    <mergeCell ref="D172:N172"/>
+    <mergeCell ref="O172:U172"/>
+    <mergeCell ref="B173:C173"/>
+    <mergeCell ref="D173:N173"/>
+    <mergeCell ref="O173:U173"/>
+    <mergeCell ref="B170:C170"/>
+    <mergeCell ref="D170:N170"/>
+    <mergeCell ref="O170:U170"/>
+    <mergeCell ref="B171:C171"/>
+    <mergeCell ref="D171:N171"/>
+    <mergeCell ref="O171:U171"/>
+    <mergeCell ref="B176:C176"/>
+    <mergeCell ref="D176:N176"/>
+    <mergeCell ref="O176:U176"/>
+    <mergeCell ref="B177:C177"/>
+    <mergeCell ref="D177:N177"/>
+    <mergeCell ref="O177:U177"/>
+    <mergeCell ref="B174:C174"/>
+    <mergeCell ref="D174:N174"/>
+    <mergeCell ref="O174:U174"/>
+    <mergeCell ref="B175:C175"/>
+    <mergeCell ref="D175:N175"/>
+    <mergeCell ref="O175:U175"/>
+    <mergeCell ref="B180:C180"/>
+    <mergeCell ref="D180:N180"/>
+    <mergeCell ref="O180:U180"/>
+    <mergeCell ref="B181:C181"/>
+    <mergeCell ref="D181:N181"/>
+    <mergeCell ref="O181:U181"/>
+    <mergeCell ref="B178:C178"/>
+    <mergeCell ref="D178:N178"/>
+    <mergeCell ref="O178:U178"/>
+    <mergeCell ref="B179:C179"/>
+    <mergeCell ref="D179:N179"/>
+    <mergeCell ref="O179:U179"/>
+    <mergeCell ref="O187:U187"/>
+    <mergeCell ref="B184:C184"/>
+    <mergeCell ref="D184:N184"/>
+    <mergeCell ref="O184:U184"/>
+    <mergeCell ref="B185:C185"/>
+    <mergeCell ref="D185:N185"/>
+    <mergeCell ref="O185:U185"/>
+    <mergeCell ref="B182:C182"/>
+    <mergeCell ref="D182:N182"/>
+    <mergeCell ref="O182:U182"/>
+    <mergeCell ref="B183:C183"/>
+    <mergeCell ref="D183:N183"/>
+    <mergeCell ref="O183:U183"/>
     <mergeCell ref="B193:C193"/>
     <mergeCell ref="D193:N193"/>
     <mergeCell ref="O193:U193"/>
@@ -11553,510 +12057,6 @@
     <mergeCell ref="O186:U186"/>
     <mergeCell ref="B187:C187"/>
     <mergeCell ref="D187:N187"/>
-    <mergeCell ref="O187:U187"/>
-    <mergeCell ref="B184:C184"/>
-    <mergeCell ref="D184:N184"/>
-    <mergeCell ref="O184:U184"/>
-    <mergeCell ref="B185:C185"/>
-    <mergeCell ref="D185:N185"/>
-    <mergeCell ref="O185:U185"/>
-    <mergeCell ref="B182:C182"/>
-    <mergeCell ref="D182:N182"/>
-    <mergeCell ref="O182:U182"/>
-    <mergeCell ref="B183:C183"/>
-    <mergeCell ref="D183:N183"/>
-    <mergeCell ref="O183:U183"/>
-    <mergeCell ref="B180:C180"/>
-    <mergeCell ref="D180:N180"/>
-    <mergeCell ref="O180:U180"/>
-    <mergeCell ref="B181:C181"/>
-    <mergeCell ref="D181:N181"/>
-    <mergeCell ref="O181:U181"/>
-    <mergeCell ref="B178:C178"/>
-    <mergeCell ref="D178:N178"/>
-    <mergeCell ref="O178:U178"/>
-    <mergeCell ref="B179:C179"/>
-    <mergeCell ref="D179:N179"/>
-    <mergeCell ref="O179:U179"/>
-    <mergeCell ref="B176:C176"/>
-    <mergeCell ref="D176:N176"/>
-    <mergeCell ref="O176:U176"/>
-    <mergeCell ref="B177:C177"/>
-    <mergeCell ref="D177:N177"/>
-    <mergeCell ref="O177:U177"/>
-    <mergeCell ref="B174:C174"/>
-    <mergeCell ref="D174:N174"/>
-    <mergeCell ref="O174:U174"/>
-    <mergeCell ref="B175:C175"/>
-    <mergeCell ref="D175:N175"/>
-    <mergeCell ref="O175:U175"/>
-    <mergeCell ref="B172:C172"/>
-    <mergeCell ref="D172:N172"/>
-    <mergeCell ref="O172:U172"/>
-    <mergeCell ref="B173:C173"/>
-    <mergeCell ref="D173:N173"/>
-    <mergeCell ref="O173:U173"/>
-    <mergeCell ref="B170:C170"/>
-    <mergeCell ref="D170:N170"/>
-    <mergeCell ref="O170:U170"/>
-    <mergeCell ref="B171:C171"/>
-    <mergeCell ref="D171:N171"/>
-    <mergeCell ref="O171:U171"/>
-    <mergeCell ref="B165:C165"/>
-    <mergeCell ref="D165:N165"/>
-    <mergeCell ref="O165:U165"/>
-    <mergeCell ref="B167:U167"/>
-    <mergeCell ref="B169:C169"/>
-    <mergeCell ref="D169:N169"/>
-    <mergeCell ref="O169:U169"/>
-    <mergeCell ref="B163:C163"/>
-    <mergeCell ref="D163:N163"/>
-    <mergeCell ref="O163:U163"/>
-    <mergeCell ref="B164:C164"/>
-    <mergeCell ref="D164:N164"/>
-    <mergeCell ref="O164:U164"/>
-    <mergeCell ref="B168:U168"/>
-    <mergeCell ref="B161:C161"/>
-    <mergeCell ref="D161:N161"/>
-    <mergeCell ref="O161:U161"/>
-    <mergeCell ref="B162:C162"/>
-    <mergeCell ref="D162:N162"/>
-    <mergeCell ref="O162:U162"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="D159:N159"/>
-    <mergeCell ref="O159:U159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="D160:N160"/>
-    <mergeCell ref="O160:U160"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="D157:N157"/>
-    <mergeCell ref="O157:U157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="D158:N158"/>
-    <mergeCell ref="O158:U158"/>
-    <mergeCell ref="B155:C155"/>
-    <mergeCell ref="D155:N155"/>
-    <mergeCell ref="O155:U155"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="D156:N156"/>
-    <mergeCell ref="O156:U156"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="D153:N153"/>
-    <mergeCell ref="O153:U153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="D154:N154"/>
-    <mergeCell ref="O154:U154"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="D151:N151"/>
-    <mergeCell ref="O151:U151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="D152:N152"/>
-    <mergeCell ref="O152:U152"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="D149:N149"/>
-    <mergeCell ref="O149:U149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="D150:N150"/>
-    <mergeCell ref="O150:U150"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="D147:N147"/>
-    <mergeCell ref="O147:U147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="D148:N148"/>
-    <mergeCell ref="O148:U148"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="D145:N145"/>
-    <mergeCell ref="O145:U145"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="D146:N146"/>
-    <mergeCell ref="O146:U146"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="D143:N143"/>
-    <mergeCell ref="O143:U143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="D144:N144"/>
-    <mergeCell ref="O144:U144"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="D141:N141"/>
-    <mergeCell ref="O141:U141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="D142:N142"/>
-    <mergeCell ref="O142:U142"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="D139:N139"/>
-    <mergeCell ref="O139:U139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="D140:N140"/>
-    <mergeCell ref="O140:U140"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="D137:N137"/>
-    <mergeCell ref="O137:U137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="D138:N138"/>
-    <mergeCell ref="O138:U138"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="D132:N132"/>
-    <mergeCell ref="O132:U132"/>
-    <mergeCell ref="B134:U134"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="D136:N136"/>
-    <mergeCell ref="O136:U136"/>
-    <mergeCell ref="B135:U135"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="D130:N130"/>
-    <mergeCell ref="O130:U130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="D131:N131"/>
-    <mergeCell ref="O131:U131"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="D128:N128"/>
-    <mergeCell ref="O128:U128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="D129:N129"/>
-    <mergeCell ref="O129:U129"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="D126:N126"/>
-    <mergeCell ref="O126:U126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="D127:N127"/>
-    <mergeCell ref="O127:U127"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="D124:N124"/>
-    <mergeCell ref="O124:U124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="D125:N125"/>
-    <mergeCell ref="O125:U125"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="D122:N122"/>
-    <mergeCell ref="O122:U122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="D123:N123"/>
-    <mergeCell ref="O123:U123"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="D120:N120"/>
-    <mergeCell ref="O120:U120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="D121:N121"/>
-    <mergeCell ref="O121:U121"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="D118:N118"/>
-    <mergeCell ref="O118:U118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="D119:N119"/>
-    <mergeCell ref="O119:U119"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="D116:N116"/>
-    <mergeCell ref="O116:U116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="D117:N117"/>
-    <mergeCell ref="O117:U117"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="D114:N114"/>
-    <mergeCell ref="O114:U114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="D115:N115"/>
-    <mergeCell ref="O115:U115"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="D112:N112"/>
-    <mergeCell ref="O112:U112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="D113:N113"/>
-    <mergeCell ref="O113:U113"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="D110:N110"/>
-    <mergeCell ref="O110:U110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="D111:N111"/>
-    <mergeCell ref="O111:U111"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="D108:N108"/>
-    <mergeCell ref="O108:U108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="D109:N109"/>
-    <mergeCell ref="O109:U109"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="D106:N106"/>
-    <mergeCell ref="O106:U106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="D107:N107"/>
-    <mergeCell ref="O107:U107"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="D104:N104"/>
-    <mergeCell ref="O104:U104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="D105:N105"/>
-    <mergeCell ref="O105:U105"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:N99"/>
-    <mergeCell ref="O99:U99"/>
-    <mergeCell ref="B101:U101"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="D103:N103"/>
-    <mergeCell ref="O103:U103"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="D97:N97"/>
-    <mergeCell ref="O97:U97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="D98:N98"/>
-    <mergeCell ref="O98:U98"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="D95:N95"/>
-    <mergeCell ref="O95:U95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="D96:N96"/>
-    <mergeCell ref="O96:U96"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="D93:N93"/>
-    <mergeCell ref="O93:U93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="D94:N94"/>
-    <mergeCell ref="O94:U94"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="D91:N91"/>
-    <mergeCell ref="O91:U91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="D92:N92"/>
-    <mergeCell ref="O92:U92"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="D89:N89"/>
-    <mergeCell ref="O89:U89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="D90:N90"/>
-    <mergeCell ref="O90:U90"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="D87:N87"/>
-    <mergeCell ref="O87:U87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="D88:N88"/>
-    <mergeCell ref="O88:U88"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="D85:N85"/>
-    <mergeCell ref="O85:U85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="D86:N86"/>
-    <mergeCell ref="O86:U86"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="D83:N83"/>
-    <mergeCell ref="O83:U83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="D84:N84"/>
-    <mergeCell ref="O84:U84"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="D81:N81"/>
-    <mergeCell ref="O81:U81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:N82"/>
-    <mergeCell ref="O82:U82"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="D79:N79"/>
-    <mergeCell ref="O79:U79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="D80:N80"/>
-    <mergeCell ref="O80:U80"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="D77:N77"/>
-    <mergeCell ref="O77:U77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="D78:N78"/>
-    <mergeCell ref="O78:U78"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="D75:N75"/>
-    <mergeCell ref="O75:U75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="D76:N76"/>
-    <mergeCell ref="O76:U76"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="D73:N73"/>
-    <mergeCell ref="O73:U73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="D74:N74"/>
-    <mergeCell ref="O74:U74"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="D71:N71"/>
-    <mergeCell ref="O71:U71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="D72:N72"/>
-    <mergeCell ref="O72:U72"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="D66:N66"/>
-    <mergeCell ref="O66:U66"/>
-    <mergeCell ref="B68:U68"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="D70:N70"/>
-    <mergeCell ref="O70:U70"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="D64:N64"/>
-    <mergeCell ref="O64:U64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:N65"/>
-    <mergeCell ref="O65:U65"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:N62"/>
-    <mergeCell ref="O62:U62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D63:N63"/>
-    <mergeCell ref="O63:U63"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:N60"/>
-    <mergeCell ref="O60:U60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="D61:N61"/>
-    <mergeCell ref="O61:U61"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:N58"/>
-    <mergeCell ref="O58:U58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:N59"/>
-    <mergeCell ref="O59:U59"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:N56"/>
-    <mergeCell ref="O56:U56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:N57"/>
-    <mergeCell ref="O57:U57"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:N54"/>
-    <mergeCell ref="O54:U54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:N55"/>
-    <mergeCell ref="O55:U55"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:N52"/>
-    <mergeCell ref="O52:U52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:N53"/>
-    <mergeCell ref="O53:U53"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:N50"/>
-    <mergeCell ref="O50:U50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:N51"/>
-    <mergeCell ref="O51:U51"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:N48"/>
-    <mergeCell ref="O48:U48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:N49"/>
-    <mergeCell ref="O49:U49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:N46"/>
-    <mergeCell ref="O46:U46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:N47"/>
-    <mergeCell ref="O47:U47"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:N44"/>
-    <mergeCell ref="O44:U44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:N45"/>
-    <mergeCell ref="O45:U45"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:N42"/>
-    <mergeCell ref="O42:U42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:N43"/>
-    <mergeCell ref="O43:U43"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:N40"/>
-    <mergeCell ref="O40:U40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:N41"/>
-    <mergeCell ref="O41:U41"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:N38"/>
-    <mergeCell ref="O38:U38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:N39"/>
-    <mergeCell ref="O39:U39"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:N33"/>
-    <mergeCell ref="O33:U33"/>
-    <mergeCell ref="B35:U35"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:N37"/>
-    <mergeCell ref="O37:U37"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:N31"/>
-    <mergeCell ref="O31:U31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:N32"/>
-    <mergeCell ref="O32:U32"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:N29"/>
-    <mergeCell ref="O29:U29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:N30"/>
-    <mergeCell ref="O30:U30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:N27"/>
-    <mergeCell ref="O27:U27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:N28"/>
-    <mergeCell ref="O28:U28"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:N25"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:N26"/>
-    <mergeCell ref="O26:U26"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:N23"/>
-    <mergeCell ref="O23:U23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:N24"/>
-    <mergeCell ref="O24:U24"/>
-    <mergeCell ref="O16:U16"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:N21"/>
-    <mergeCell ref="O21:U21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:N22"/>
-    <mergeCell ref="O22:U22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:N19"/>
-    <mergeCell ref="O19:U19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:N20"/>
-    <mergeCell ref="O20:U20"/>
-    <mergeCell ref="B1:U1"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:N3"/>
-    <mergeCell ref="O3:U3"/>
-    <mergeCell ref="B5:U5"/>
-    <mergeCell ref="B8:U8"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:N13"/>
-    <mergeCell ref="O13:U13"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:N11"/>
-    <mergeCell ref="O11:U11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:N12"/>
-    <mergeCell ref="O12:U12"/>
-    <mergeCell ref="B194:C194"/>
-    <mergeCell ref="D194:N194"/>
-    <mergeCell ref="O194:U194"/>
-    <mergeCell ref="B7:U7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:N9"/>
-    <mergeCell ref="O9:U9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:N10"/>
-    <mergeCell ref="O10:U10"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:N14"/>
-    <mergeCell ref="O14:U14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:N17"/>
-    <mergeCell ref="O17:U17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:N18"/>
-    <mergeCell ref="O18:U18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:N15"/>
-    <mergeCell ref="O15:U15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:N16"/>
   </mergeCells>
   <pageMargins left="0.39370078740157477" right="0.39370078740157477" top="0.39370078740157477" bottom="0.39370078740157477" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>

--- a/Журнал.xlsx
+++ b/Журнал.xlsx
@@ -1293,26 +1293,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1325,6 +1307,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1718,70 +1718,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
     </row>
     <row r="2" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30" t="s">
+      <c r="B3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="29" t="s">
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="22"/>
-      <c r="Z3" s="22"/>
-      <c r="AA3" s="22"/>
-      <c r="AB3" s="22"/>
-      <c r="AC3" s="22"/>
-      <c r="AD3" s="22"/>
-      <c r="AE3" s="22"/>
-      <c r="AF3" s="22"/>
-      <c r="AG3" s="22"/>
-      <c r="AH3" s="22"/>
-      <c r="AI3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+      <c r="Y3" s="30"/>
+      <c r="Z3" s="30"/>
+      <c r="AA3" s="30"/>
+      <c r="AB3" s="30"/>
+      <c r="AC3" s="30"/>
+      <c r="AD3" s="30"/>
+      <c r="AE3" s="30"/>
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="31"/>
     </row>
     <row r="4" spans="1:35" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4"/>
@@ -1808,28 +1808,28 @@
       <c r="V4"/>
     </row>
     <row r="5" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="31" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="31"/>
-      <c r="N5" s="31"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
-      <c r="Q5" s="31"/>
-      <c r="R5" s="31"/>
-      <c r="S5" s="31"/>
-      <c r="T5" s="31"/>
-      <c r="U5" s="31"/>
+      <c r="B5" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
       <c r="V5" s="8"/>
       <c r="W5" s="9"/>
       <c r="X5" s="9"/>
@@ -1870,28 +1870,28 @@
       <c r="V6"/>
     </row>
     <row r="7" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
       <c r="V7" s="8"/>
       <c r="W7" s="9"/>
       <c r="X7" s="9"/>
@@ -1909,38 +1909,38 @@
     </row>
     <row r="8" spans="1:35" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="27"/>
-      <c r="V8" s="10">
-        <v>0</v>
-      </c>
-      <c r="W8" s="14">
+      <c r="B8" s="26"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="17">
+        <v>0</v>
+      </c>
+      <c r="W8" s="17">
         <f t="shared" ref="W8" si="0">V8+1</f>
         <v>1</v>
       </c>
-      <c r="X8" s="14">
+      <c r="X8" s="17">
         <f t="shared" ref="X8" si="1">W8+1</f>
         <v>2</v>
       </c>
-      <c r="Y8" s="14">
+      <c r="Y8" s="17">
         <f t="shared" ref="Y8" si="2">X8+1</f>
         <v>3</v>
       </c>
@@ -2013,7 +2013,9 @@
       <c r="X9" s="13">
         <v>0</v>
       </c>
-      <c r="Y9" s="4"/>
+      <c r="Y9" s="13">
+        <v>0</v>
+      </c>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
       <c r="AB9" s="4"/>
@@ -2065,7 +2067,9 @@
       <c r="X10" s="12">
         <v>3</v>
       </c>
-      <c r="Y10" s="7"/>
+      <c r="Y10" s="12">
+        <v>3</v>
+      </c>
       <c r="Z10" s="7"/>
       <c r="AA10" s="7"/>
       <c r="AB10" s="7"/>
@@ -2117,7 +2121,9 @@
       <c r="X11" s="12">
         <v>0</v>
       </c>
-      <c r="Y11" s="7"/>
+      <c r="Y11" s="12">
+        <v>0</v>
+      </c>
       <c r="Z11" s="7"/>
       <c r="AA11" s="7"/>
       <c r="AB11" s="7"/>
@@ -2169,7 +2175,9 @@
       <c r="X12" s="12">
         <v>3</v>
       </c>
-      <c r="Y12" s="7"/>
+      <c r="Y12" s="12">
+        <v>3</v>
+      </c>
       <c r="Z12" s="7"/>
       <c r="AA12" s="7"/>
       <c r="AB12" s="7"/>
@@ -2221,7 +2229,9 @@
       <c r="X13" s="12">
         <v>0</v>
       </c>
-      <c r="Y13" s="7"/>
+      <c r="Y13" s="12">
+        <v>0</v>
+      </c>
       <c r="Z13" s="7"/>
       <c r="AA13" s="7"/>
       <c r="AB13" s="7"/>
@@ -2273,7 +2283,9 @@
       <c r="X14" s="12">
         <v>0</v>
       </c>
-      <c r="Y14" s="7"/>
+      <c r="Y14" s="12">
+        <v>0</v>
+      </c>
       <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
       <c r="AB14" s="7"/>
@@ -2325,7 +2337,9 @@
       <c r="X15" s="12">
         <v>3</v>
       </c>
-      <c r="Y15" s="7"/>
+      <c r="Y15" s="12">
+        <v>2</v>
+      </c>
       <c r="Z15" s="7"/>
       <c r="AA15" s="7"/>
       <c r="AB15" s="7"/>
@@ -2377,7 +2391,9 @@
       <c r="X16" s="12">
         <v>2</v>
       </c>
-      <c r="Y16" s="7"/>
+      <c r="Y16" s="12">
+        <v>3</v>
+      </c>
       <c r="Z16" s="7"/>
       <c r="AA16" s="7"/>
       <c r="AB16" s="7"/>
@@ -2429,7 +2445,7 @@
       <c r="X17" s="12">
         <v>0</v>
       </c>
-      <c r="Y17" s="7"/>
+      <c r="Y17" s="12"/>
       <c r="Z17" s="7"/>
       <c r="AA17" s="7"/>
       <c r="AB17" s="7"/>
@@ -2481,7 +2497,9 @@
       <c r="X18" s="12">
         <v>2</v>
       </c>
-      <c r="Y18" s="7"/>
+      <c r="Y18" s="12">
+        <v>2</v>
+      </c>
       <c r="Z18" s="7"/>
       <c r="AA18" s="7"/>
       <c r="AB18" s="7"/>
@@ -2533,7 +2551,9 @@
       <c r="X19" s="12">
         <v>3</v>
       </c>
-      <c r="Y19" s="7"/>
+      <c r="Y19" s="12">
+        <v>3</v>
+      </c>
       <c r="Z19" s="7"/>
       <c r="AA19" s="7"/>
       <c r="AB19" s="7"/>
@@ -2585,7 +2605,9 @@
       <c r="X20" s="12">
         <v>0</v>
       </c>
-      <c r="Y20" s="7"/>
+      <c r="Y20" s="12">
+        <v>0</v>
+      </c>
       <c r="Z20" s="7"/>
       <c r="AA20" s="7"/>
       <c r="AB20" s="7"/>
@@ -2637,7 +2659,9 @@
       <c r="X21" s="12">
         <v>3</v>
       </c>
-      <c r="Y21" s="7"/>
+      <c r="Y21" s="12">
+        <v>3</v>
+      </c>
       <c r="Z21" s="7"/>
       <c r="AA21" s="7"/>
       <c r="AB21" s="7"/>
@@ -2689,7 +2713,9 @@
       <c r="X22" s="12">
         <v>0</v>
       </c>
-      <c r="Y22" s="7"/>
+      <c r="Y22" s="12">
+        <v>0</v>
+      </c>
       <c r="Z22" s="7"/>
       <c r="AA22" s="7"/>
       <c r="AB22" s="7"/>
@@ -2741,7 +2767,9 @@
       <c r="X23" s="12">
         <v>3</v>
       </c>
-      <c r="Y23" s="7"/>
+      <c r="Y23" s="12">
+        <v>3</v>
+      </c>
       <c r="Z23" s="7"/>
       <c r="AA23" s="7"/>
       <c r="AB23" s="7"/>
@@ -2793,7 +2821,9 @@
       <c r="X24" s="12">
         <v>3</v>
       </c>
-      <c r="Y24" s="7"/>
+      <c r="Y24" s="12">
+        <v>0</v>
+      </c>
       <c r="Z24" s="7"/>
       <c r="AA24" s="7"/>
       <c r="AB24" s="7"/>
@@ -2845,7 +2875,9 @@
       <c r="X25" s="12">
         <v>2</v>
       </c>
-      <c r="Y25" s="7"/>
+      <c r="Y25" s="12">
+        <v>1</v>
+      </c>
       <c r="Z25" s="7"/>
       <c r="AA25" s="7"/>
       <c r="AB25" s="7"/>
@@ -2897,7 +2929,9 @@
       <c r="X26" s="12">
         <v>0</v>
       </c>
-      <c r="Y26" s="7"/>
+      <c r="Y26" s="12">
+        <v>0</v>
+      </c>
       <c r="Z26" s="7"/>
       <c r="AA26" s="7"/>
       <c r="AB26" s="7"/>
@@ -2949,7 +2983,9 @@
       <c r="X27" s="12">
         <v>3</v>
       </c>
-      <c r="Y27" s="7"/>
+      <c r="Y27" s="12">
+        <v>3</v>
+      </c>
       <c r="Z27" s="7"/>
       <c r="AA27" s="7"/>
       <c r="AB27" s="7"/>
@@ -3001,7 +3037,9 @@
       <c r="X28" s="12">
         <v>3</v>
       </c>
-      <c r="Y28" s="7"/>
+      <c r="Y28" s="12">
+        <v>3</v>
+      </c>
       <c r="Z28" s="7"/>
       <c r="AA28" s="7"/>
       <c r="AB28" s="7"/>
@@ -3053,7 +3091,9 @@
       <c r="X29" s="12">
         <v>0</v>
       </c>
-      <c r="Y29" s="7"/>
+      <c r="Y29" s="12">
+        <v>0</v>
+      </c>
       <c r="Z29" s="7"/>
       <c r="AA29" s="7"/>
       <c r="AB29" s="7"/>
@@ -3105,7 +3145,9 @@
       <c r="X30" s="12">
         <v>0</v>
       </c>
-      <c r="Y30" s="7"/>
+      <c r="Y30" s="12">
+        <v>0</v>
+      </c>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
       <c r="AB30" s="7"/>
@@ -3157,7 +3199,9 @@
       <c r="X31" s="12">
         <v>0</v>
       </c>
-      <c r="Y31" s="7"/>
+      <c r="Y31" s="12">
+        <v>0</v>
+      </c>
       <c r="Z31" s="7"/>
       <c r="AA31" s="7"/>
       <c r="AB31" s="7"/>
@@ -3209,7 +3253,9 @@
       <c r="X32" s="12">
         <v>0</v>
       </c>
-      <c r="Y32" s="7"/>
+      <c r="Y32" s="12">
+        <v>0</v>
+      </c>
       <c r="Z32" s="7"/>
       <c r="AA32" s="7"/>
       <c r="AB32" s="7"/>
@@ -3261,7 +3307,9 @@
       <c r="X33" s="12">
         <v>3</v>
       </c>
-      <c r="Y33" s="7"/>
+      <c r="Y33" s="12">
+        <v>3</v>
+      </c>
       <c r="Z33" s="7"/>
       <c r="AA33" s="7"/>
       <c r="AB33" s="7"/>
@@ -3301,28 +3349,28 @@
       <c r="V34"/>
     </row>
     <row r="35" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="24"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="24"/>
-      <c r="Q35" s="24"/>
-      <c r="R35" s="24"/>
-      <c r="S35" s="24"/>
-      <c r="T35" s="24"/>
-      <c r="U35" s="24"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="21"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="21"/>
+      <c r="R35" s="21"/>
+      <c r="S35" s="21"/>
+      <c r="T35" s="21"/>
+      <c r="U35" s="21"/>
       <c r="V35" s="8"/>
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
@@ -3360,18 +3408,18 @@
       <c r="S36"/>
       <c r="T36"/>
       <c r="U36"/>
-      <c r="V36" s="10">
-        <v>0</v>
-      </c>
-      <c r="W36" s="14">
+      <c r="V36" s="17">
+        <v>0</v>
+      </c>
+      <c r="W36" s="17">
         <f t="shared" ref="W36" si="7">V36+1</f>
         <v>1</v>
       </c>
-      <c r="X36" s="14">
+      <c r="X36" s="17">
         <f t="shared" ref="X36" si="8">W36+1</f>
         <v>2</v>
       </c>
-      <c r="Y36" s="14">
+      <c r="Y36" s="17">
         <f t="shared" ref="Y36" si="9">X36+1</f>
         <v>3</v>
       </c>
@@ -3444,7 +3492,9 @@
       <c r="X37" s="13">
         <v>0</v>
       </c>
-      <c r="Y37" s="4"/>
+      <c r="Y37" s="13">
+        <v>0</v>
+      </c>
       <c r="Z37" s="4"/>
       <c r="AA37" s="4"/>
       <c r="AB37" s="4"/>
@@ -3496,7 +3546,9 @@
       <c r="X38" s="13">
         <v>0</v>
       </c>
-      <c r="Y38" s="7"/>
+      <c r="Y38" s="13">
+        <v>0</v>
+      </c>
       <c r="Z38" s="7"/>
       <c r="AA38" s="7"/>
       <c r="AB38" s="7"/>
@@ -3548,7 +3600,9 @@
       <c r="X39" s="13">
         <v>0</v>
       </c>
-      <c r="Y39" s="7"/>
+      <c r="Y39" s="13">
+        <v>0</v>
+      </c>
       <c r="Z39" s="7"/>
       <c r="AA39" s="7"/>
       <c r="AB39" s="7"/>
@@ -3600,7 +3654,9 @@
       <c r="X40" s="13">
         <v>0</v>
       </c>
-      <c r="Y40" s="7"/>
+      <c r="Y40" s="13">
+        <v>0</v>
+      </c>
       <c r="Z40" s="7"/>
       <c r="AA40" s="7"/>
       <c r="AB40" s="7"/>
@@ -3652,7 +3708,9 @@
       <c r="X41" s="13">
         <v>0</v>
       </c>
-      <c r="Y41" s="7"/>
+      <c r="Y41" s="13">
+        <v>0</v>
+      </c>
       <c r="Z41" s="7"/>
       <c r="AA41" s="7"/>
       <c r="AB41" s="7"/>
@@ -3704,7 +3762,9 @@
       <c r="X42" s="13">
         <v>0</v>
       </c>
-      <c r="Y42" s="7"/>
+      <c r="Y42" s="13">
+        <v>0</v>
+      </c>
       <c r="Z42" s="7"/>
       <c r="AA42" s="7"/>
       <c r="AB42" s="7"/>
@@ -3756,7 +3816,9 @@
       <c r="X43" s="13">
         <v>0</v>
       </c>
-      <c r="Y43" s="7"/>
+      <c r="Y43" s="13">
+        <v>0</v>
+      </c>
       <c r="Z43" s="7"/>
       <c r="AA43" s="7"/>
       <c r="AB43" s="7"/>
@@ -3808,7 +3870,9 @@
       <c r="X44" s="13">
         <v>0</v>
       </c>
-      <c r="Y44" s="7"/>
+      <c r="Y44" s="13">
+        <v>0</v>
+      </c>
       <c r="Z44" s="7"/>
       <c r="AA44" s="7"/>
       <c r="AB44" s="7"/>
@@ -3860,7 +3924,9 @@
       <c r="X45" s="13">
         <v>0</v>
       </c>
-      <c r="Y45" s="7"/>
+      <c r="Y45" s="13">
+        <v>0</v>
+      </c>
       <c r="Z45" s="7"/>
       <c r="AA45" s="7"/>
       <c r="AB45" s="7"/>
@@ -3912,7 +3978,9 @@
       <c r="X46" s="13">
         <v>0</v>
       </c>
-      <c r="Y46" s="7"/>
+      <c r="Y46" s="13">
+        <v>0</v>
+      </c>
       <c r="Z46" s="7"/>
       <c r="AA46" s="7"/>
       <c r="AB46" s="7"/>
@@ -3964,7 +4032,9 @@
       <c r="X47" s="13">
         <v>0</v>
       </c>
-      <c r="Y47" s="7"/>
+      <c r="Y47" s="13">
+        <v>0</v>
+      </c>
       <c r="Z47" s="7"/>
       <c r="AA47" s="7"/>
       <c r="AB47" s="7"/>
@@ -4016,7 +4086,9 @@
       <c r="X48" s="13">
         <v>0</v>
       </c>
-      <c r="Y48" s="7"/>
+      <c r="Y48" s="13">
+        <v>0</v>
+      </c>
       <c r="Z48" s="7"/>
       <c r="AA48" s="7"/>
       <c r="AB48" s="7"/>
@@ -4068,7 +4140,9 @@
       <c r="X49" s="13">
         <v>0</v>
       </c>
-      <c r="Y49" s="7"/>
+      <c r="Y49" s="13">
+        <v>0</v>
+      </c>
       <c r="Z49" s="7"/>
       <c r="AA49" s="7"/>
       <c r="AB49" s="7"/>
@@ -4120,7 +4194,9 @@
       <c r="X50" s="13">
         <v>0</v>
       </c>
-      <c r="Y50" s="7"/>
+      <c r="Y50" s="13">
+        <v>0</v>
+      </c>
       <c r="Z50" s="7"/>
       <c r="AA50" s="7"/>
       <c r="AB50" s="7"/>
@@ -4172,7 +4248,9 @@
       <c r="X51" s="13">
         <v>0</v>
       </c>
-      <c r="Y51" s="7"/>
+      <c r="Y51" s="13">
+        <v>0</v>
+      </c>
       <c r="Z51" s="7"/>
       <c r="AA51" s="7"/>
       <c r="AB51" s="7"/>
@@ -4224,7 +4302,9 @@
       <c r="X52" s="13">
         <v>0</v>
       </c>
-      <c r="Y52" s="7"/>
+      <c r="Y52" s="13">
+        <v>0</v>
+      </c>
       <c r="Z52" s="7"/>
       <c r="AA52" s="7"/>
       <c r="AB52" s="7"/>
@@ -4276,7 +4356,9 @@
       <c r="X53" s="13">
         <v>0</v>
       </c>
-      <c r="Y53" s="7"/>
+      <c r="Y53" s="13">
+        <v>0</v>
+      </c>
       <c r="Z53" s="7"/>
       <c r="AA53" s="7"/>
       <c r="AB53" s="7"/>
@@ -4328,7 +4410,9 @@
       <c r="X54" s="13">
         <v>0</v>
       </c>
-      <c r="Y54" s="7"/>
+      <c r="Y54" s="13">
+        <v>0</v>
+      </c>
       <c r="Z54" s="7"/>
       <c r="AA54" s="7"/>
       <c r="AB54" s="7"/>
@@ -4380,7 +4464,9 @@
       <c r="X55" s="13">
         <v>0</v>
       </c>
-      <c r="Y55" s="7"/>
+      <c r="Y55" s="13">
+        <v>0</v>
+      </c>
       <c r="Z55" s="7"/>
       <c r="AA55" s="7"/>
       <c r="AB55" s="7"/>
@@ -4432,7 +4518,9 @@
       <c r="X56" s="13">
         <v>0</v>
       </c>
-      <c r="Y56" s="7"/>
+      <c r="Y56" s="13">
+        <v>0</v>
+      </c>
       <c r="Z56" s="7"/>
       <c r="AA56" s="7"/>
       <c r="AB56" s="7"/>
@@ -4484,7 +4572,9 @@
       <c r="X57" s="13">
         <v>0</v>
       </c>
-      <c r="Y57" s="7"/>
+      <c r="Y57" s="13">
+        <v>0</v>
+      </c>
       <c r="Z57" s="7"/>
       <c r="AA57" s="7"/>
       <c r="AB57" s="7"/>
@@ -4536,7 +4626,9 @@
       <c r="X58" s="13">
         <v>0</v>
       </c>
-      <c r="Y58" s="7"/>
+      <c r="Y58" s="13">
+        <v>0</v>
+      </c>
       <c r="Z58" s="7"/>
       <c r="AA58" s="7"/>
       <c r="AB58" s="7"/>
@@ -4588,7 +4680,9 @@
       <c r="X59" s="13">
         <v>0</v>
       </c>
-      <c r="Y59" s="7"/>
+      <c r="Y59" s="13">
+        <v>0</v>
+      </c>
       <c r="Z59" s="7"/>
       <c r="AA59" s="7"/>
       <c r="AB59" s="7"/>
@@ -4640,7 +4734,9 @@
       <c r="X60" s="13">
         <v>0</v>
       </c>
-      <c r="Y60" s="7"/>
+      <c r="Y60" s="13">
+        <v>0</v>
+      </c>
       <c r="Z60" s="7"/>
       <c r="AA60" s="7"/>
       <c r="AB60" s="7"/>
@@ -4692,7 +4788,9 @@
       <c r="X61" s="12">
         <v>0</v>
       </c>
-      <c r="Y61" s="7"/>
+      <c r="Y61" s="13">
+        <v>0</v>
+      </c>
       <c r="Z61" s="7"/>
       <c r="AA61" s="7"/>
       <c r="AB61" s="7"/>
@@ -4744,7 +4842,9 @@
       <c r="X62" s="12">
         <v>3</v>
       </c>
-      <c r="Y62" s="7"/>
+      <c r="Y62" s="12">
+        <v>3</v>
+      </c>
       <c r="Z62" s="7"/>
       <c r="AA62" s="7"/>
       <c r="AB62" s="7"/>
@@ -4796,7 +4896,9 @@
       <c r="X63" s="12">
         <v>0</v>
       </c>
-      <c r="Y63" s="7"/>
+      <c r="Y63" s="12">
+        <v>0</v>
+      </c>
       <c r="Z63" s="7"/>
       <c r="AA63" s="7"/>
       <c r="AB63" s="7"/>
@@ -4848,7 +4950,9 @@
       <c r="X64" s="12">
         <v>0</v>
       </c>
-      <c r="Y64" s="7"/>
+      <c r="Y64" s="12">
+        <v>0</v>
+      </c>
       <c r="Z64" s="7"/>
       <c r="AA64" s="7"/>
       <c r="AB64" s="7"/>
@@ -4900,7 +5004,9 @@
       <c r="X65" s="12">
         <v>0</v>
       </c>
-      <c r="Y65" s="7"/>
+      <c r="Y65" s="12">
+        <v>0</v>
+      </c>
       <c r="Z65" s="7"/>
       <c r="AA65" s="7"/>
       <c r="AB65" s="7"/>
@@ -4952,7 +5058,9 @@
       <c r="X66" s="12">
         <v>0</v>
       </c>
-      <c r="Y66" s="7"/>
+      <c r="Y66" s="12">
+        <v>0</v>
+      </c>
       <c r="Z66" s="7"/>
       <c r="AA66" s="7"/>
       <c r="AB66" s="7"/>
@@ -4993,28 +5101,28 @@
     </row>
     <row r="68" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
-      <c r="B68" s="24" t="s">
+      <c r="B68" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="C68" s="24"/>
-      <c r="D68" s="24"/>
-      <c r="E68" s="24"/>
-      <c r="F68" s="24"/>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="24"/>
-      <c r="J68" s="24"/>
-      <c r="K68" s="24"/>
-      <c r="L68" s="24"/>
-      <c r="M68" s="24"/>
-      <c r="N68" s="24"/>
-      <c r="O68" s="24"/>
-      <c r="P68" s="24"/>
-      <c r="Q68" s="24"/>
-      <c r="R68" s="24"/>
-      <c r="S68" s="24"/>
-      <c r="T68" s="24"/>
-      <c r="U68" s="24"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="21"/>
+      <c r="P68" s="21"/>
+      <c r="Q68" s="21"/>
+      <c r="R68" s="21"/>
+      <c r="S68" s="21"/>
+      <c r="T68" s="21"/>
+      <c r="U68" s="21"/>
       <c r="V68" s="8"/>
       <c r="W68" s="9"/>
       <c r="X68" s="9"/>
@@ -5053,18 +5161,18 @@
       <c r="S69"/>
       <c r="T69"/>
       <c r="U69"/>
-      <c r="V69" s="10">
-        <v>0</v>
-      </c>
-      <c r="W69" s="14">
+      <c r="V69" s="17">
+        <v>0</v>
+      </c>
+      <c r="W69" s="17">
         <f t="shared" ref="W69" si="13">V69+1</f>
         <v>1</v>
       </c>
-      <c r="X69" s="14">
+      <c r="X69" s="17">
         <f t="shared" ref="X69" si="14">W69+1</f>
         <v>2</v>
       </c>
-      <c r="Y69" s="14">
+      <c r="Y69" s="17">
         <f t="shared" ref="Y69" si="15">X69+1</f>
         <v>3</v>
       </c>
@@ -5137,7 +5245,9 @@
       <c r="X70" s="13">
         <v>0</v>
       </c>
-      <c r="Y70" s="4"/>
+      <c r="Y70" s="13">
+        <v>0</v>
+      </c>
       <c r="Z70" s="4"/>
       <c r="AA70" s="4"/>
       <c r="AB70" s="4"/>
@@ -5189,7 +5299,9 @@
       <c r="X71" s="12">
         <v>0</v>
       </c>
-      <c r="Y71" s="7"/>
+      <c r="Y71" s="13">
+        <v>0</v>
+      </c>
       <c r="Z71" s="7"/>
       <c r="AA71" s="7"/>
       <c r="AB71" s="7"/>
@@ -5241,7 +5353,9 @@
       <c r="X72" s="12">
         <v>3</v>
       </c>
-      <c r="Y72" s="7"/>
+      <c r="Y72" s="13">
+        <v>0</v>
+      </c>
       <c r="Z72" s="7"/>
       <c r="AA72" s="7"/>
       <c r="AB72" s="7"/>
@@ -5293,7 +5407,9 @@
       <c r="X73" s="12">
         <v>0</v>
       </c>
-      <c r="Y73" s="7"/>
+      <c r="Y73" s="13">
+        <v>0</v>
+      </c>
       <c r="Z73" s="7"/>
       <c r="AA73" s="7"/>
       <c r="AB73" s="7"/>
@@ -5345,7 +5461,9 @@
       <c r="X74" s="12">
         <v>0</v>
       </c>
-      <c r="Y74" s="7"/>
+      <c r="Y74" s="13">
+        <v>0</v>
+      </c>
       <c r="Z74" s="7"/>
       <c r="AA74" s="7"/>
       <c r="AB74" s="7"/>
@@ -5397,7 +5515,9 @@
       <c r="X75" s="12">
         <v>0</v>
       </c>
-      <c r="Y75" s="7"/>
+      <c r="Y75" s="13">
+        <v>0</v>
+      </c>
       <c r="Z75" s="7"/>
       <c r="AA75" s="7"/>
       <c r="AB75" s="7"/>
@@ -5449,7 +5569,9 @@
       <c r="X76" s="12">
         <v>0</v>
       </c>
-      <c r="Y76" s="7"/>
+      <c r="Y76" s="13">
+        <v>0</v>
+      </c>
       <c r="Z76" s="7"/>
       <c r="AA76" s="7"/>
       <c r="AB76" s="7"/>
@@ -5501,7 +5623,9 @@
       <c r="X77" s="12">
         <v>0</v>
       </c>
-      <c r="Y77" s="7"/>
+      <c r="Y77" s="13">
+        <v>0</v>
+      </c>
       <c r="Z77" s="7"/>
       <c r="AA77" s="7"/>
       <c r="AB77" s="7"/>
@@ -5553,7 +5677,9 @@
       <c r="X78" s="12">
         <v>0</v>
       </c>
-      <c r="Y78" s="7"/>
+      <c r="Y78" s="13">
+        <v>0</v>
+      </c>
       <c r="Z78" s="7"/>
       <c r="AA78" s="7"/>
       <c r="AB78" s="7"/>
@@ -5605,7 +5731,9 @@
       <c r="X79" s="12">
         <v>0</v>
       </c>
-      <c r="Y79" s="7"/>
+      <c r="Y79" s="13">
+        <v>0</v>
+      </c>
       <c r="Z79" s="7"/>
       <c r="AA79" s="7"/>
       <c r="AB79" s="7"/>
@@ -5657,7 +5785,9 @@
       <c r="X80" s="12">
         <v>0</v>
       </c>
-      <c r="Y80" s="7"/>
+      <c r="Y80" s="13">
+        <v>0</v>
+      </c>
       <c r="Z80" s="7"/>
       <c r="AA80" s="7"/>
       <c r="AB80" s="7"/>
@@ -5709,7 +5839,9 @@
       <c r="X81" s="12">
         <v>0</v>
       </c>
-      <c r="Y81" s="7"/>
+      <c r="Y81" s="13">
+        <v>0</v>
+      </c>
       <c r="Z81" s="7"/>
       <c r="AA81" s="7"/>
       <c r="AB81" s="7"/>
@@ -5761,7 +5893,9 @@
       <c r="X82" s="12">
         <v>0</v>
       </c>
-      <c r="Y82" s="7"/>
+      <c r="Y82" s="13">
+        <v>0</v>
+      </c>
       <c r="Z82" s="7"/>
       <c r="AA82" s="7"/>
       <c r="AB82" s="7"/>
@@ -5813,7 +5947,9 @@
       <c r="X83" s="12">
         <v>0</v>
       </c>
-      <c r="Y83" s="7"/>
+      <c r="Y83" s="13">
+        <v>0</v>
+      </c>
       <c r="Z83" s="7"/>
       <c r="AA83" s="7"/>
       <c r="AB83" s="7"/>
@@ -5865,7 +6001,9 @@
       <c r="X84" s="12">
         <v>0</v>
       </c>
-      <c r="Y84" s="7"/>
+      <c r="Y84" s="13">
+        <v>0</v>
+      </c>
       <c r="Z84" s="7"/>
       <c r="AA84" s="7"/>
       <c r="AB84" s="7"/>
@@ -5917,7 +6055,9 @@
       <c r="X85" s="12">
         <v>0</v>
       </c>
-      <c r="Y85" s="7"/>
+      <c r="Y85" s="13">
+        <v>0</v>
+      </c>
       <c r="Z85" s="7"/>
       <c r="AA85" s="7"/>
       <c r="AB85" s="7"/>
@@ -5969,7 +6109,9 @@
       <c r="X86" s="12">
         <v>0</v>
       </c>
-      <c r="Y86" s="7"/>
+      <c r="Y86" s="13">
+        <v>0</v>
+      </c>
       <c r="Z86" s="7"/>
       <c r="AA86" s="7"/>
       <c r="AB86" s="7"/>
@@ -6021,7 +6163,9 @@
       <c r="X87" s="12">
         <v>0</v>
       </c>
-      <c r="Y87" s="7"/>
+      <c r="Y87" s="13">
+        <v>0</v>
+      </c>
       <c r="Z87" s="7"/>
       <c r="AA87" s="7"/>
       <c r="AB87" s="7"/>
@@ -6073,7 +6217,9 @@
       <c r="X88" s="12">
         <v>0</v>
       </c>
-      <c r="Y88" s="7"/>
+      <c r="Y88" s="13">
+        <v>0</v>
+      </c>
       <c r="Z88" s="7"/>
       <c r="AA88" s="7"/>
       <c r="AB88" s="7"/>
@@ -6125,7 +6271,9 @@
       <c r="X89" s="12">
         <v>0</v>
       </c>
-      <c r="Y89" s="7"/>
+      <c r="Y89" s="13">
+        <v>0</v>
+      </c>
       <c r="Z89" s="7"/>
       <c r="AA89" s="7"/>
       <c r="AB89" s="7"/>
@@ -6177,7 +6325,9 @@
       <c r="X90" s="12">
         <v>0</v>
       </c>
-      <c r="Y90" s="7"/>
+      <c r="Y90" s="13">
+        <v>0</v>
+      </c>
       <c r="Z90" s="7"/>
       <c r="AA90" s="7"/>
       <c r="AB90" s="7"/>
@@ -6229,7 +6379,9 @@
       <c r="X91" s="12">
         <v>0</v>
       </c>
-      <c r="Y91" s="7"/>
+      <c r="Y91" s="13">
+        <v>0</v>
+      </c>
       <c r="Z91" s="7"/>
       <c r="AA91" s="7"/>
       <c r="AB91" s="7"/>
@@ -6281,7 +6433,9 @@
       <c r="X92" s="12">
         <v>0</v>
       </c>
-      <c r="Y92" s="7"/>
+      <c r="Y92" s="13">
+        <v>0</v>
+      </c>
       <c r="Z92" s="7"/>
       <c r="AA92" s="7"/>
       <c r="AB92" s="7"/>
@@ -6333,7 +6487,9 @@
       <c r="X93" s="12">
         <v>0</v>
       </c>
-      <c r="Y93" s="7"/>
+      <c r="Y93" s="13">
+        <v>0</v>
+      </c>
       <c r="Z93" s="7"/>
       <c r="AA93" s="7"/>
       <c r="AB93" s="7"/>
@@ -6385,7 +6541,9 @@
       <c r="X94" s="12">
         <v>0</v>
       </c>
-      <c r="Y94" s="7"/>
+      <c r="Y94" s="13">
+        <v>0</v>
+      </c>
       <c r="Z94" s="7"/>
       <c r="AA94" s="7"/>
       <c r="AB94" s="7"/>
@@ -6437,7 +6595,9 @@
       <c r="X95" s="12">
         <v>0</v>
       </c>
-      <c r="Y95" s="7"/>
+      <c r="Y95" s="13">
+        <v>0</v>
+      </c>
       <c r="Z95" s="7"/>
       <c r="AA95" s="7"/>
       <c r="AB95" s="7"/>
@@ -6489,7 +6649,9 @@
       <c r="X96" s="12">
         <v>0</v>
       </c>
-      <c r="Y96" s="7"/>
+      <c r="Y96" s="13">
+        <v>0</v>
+      </c>
       <c r="Z96" s="7"/>
       <c r="AA96" s="7"/>
       <c r="AB96" s="7"/>
@@ -6541,7 +6703,9 @@
       <c r="X97" s="12">
         <v>0</v>
       </c>
-      <c r="Y97" s="7"/>
+      <c r="Y97" s="13">
+        <v>0</v>
+      </c>
       <c r="Z97" s="7"/>
       <c r="AA97" s="7"/>
       <c r="AB97" s="7"/>
@@ -6593,7 +6757,9 @@
       <c r="X98" s="12">
         <v>0</v>
       </c>
-      <c r="Y98" s="7"/>
+      <c r="Y98" s="13">
+        <v>0</v>
+      </c>
       <c r="Z98" s="7"/>
       <c r="AA98" s="7"/>
       <c r="AB98" s="7"/>
@@ -6645,7 +6811,9 @@
       <c r="X99" s="12">
         <v>0</v>
       </c>
-      <c r="Y99" s="7"/>
+      <c r="Y99" s="13">
+        <v>0</v>
+      </c>
       <c r="Z99" s="7"/>
       <c r="AA99" s="7"/>
       <c r="AB99" s="7"/>
@@ -6685,28 +6853,28 @@
       <c r="V100"/>
     </row>
     <row r="101" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B101" s="24" t="s">
+      <c r="B101" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="C101" s="24"/>
-      <c r="D101" s="24"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="24"/>
-      <c r="H101" s="24"/>
-      <c r="I101" s="24"/>
-      <c r="J101" s="24"/>
-      <c r="K101" s="24"/>
-      <c r="L101" s="24"/>
-      <c r="M101" s="24"/>
-      <c r="N101" s="24"/>
-      <c r="O101" s="24"/>
-      <c r="P101" s="24"/>
-      <c r="Q101" s="24"/>
-      <c r="R101" s="24"/>
-      <c r="S101" s="24"/>
-      <c r="T101" s="24"/>
-      <c r="U101" s="24"/>
+      <c r="C101" s="21"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="21"/>
+      <c r="F101" s="21"/>
+      <c r="G101" s="21"/>
+      <c r="H101" s="21"/>
+      <c r="I101" s="21"/>
+      <c r="J101" s="21"/>
+      <c r="K101" s="21"/>
+      <c r="L101" s="21"/>
+      <c r="M101" s="21"/>
+      <c r="N101" s="21"/>
+      <c r="O101" s="21"/>
+      <c r="P101" s="21"/>
+      <c r="Q101" s="21"/>
+      <c r="R101" s="21"/>
+      <c r="S101" s="21"/>
+      <c r="T101" s="21"/>
+      <c r="U101" s="21"/>
       <c r="V101" s="8"/>
       <c r="W101" s="9"/>
       <c r="X101" s="9"/>
@@ -6745,18 +6913,18 @@
       <c r="S102"/>
       <c r="T102"/>
       <c r="U102"/>
-      <c r="V102" s="10">
-        <v>0</v>
-      </c>
-      <c r="W102" s="14">
+      <c r="V102" s="17">
+        <v>0</v>
+      </c>
+      <c r="W102" s="17">
         <f t="shared" ref="W102" si="20">V102+1</f>
         <v>1</v>
       </c>
-      <c r="X102" s="14">
+      <c r="X102" s="17">
         <f t="shared" ref="X102" si="21">W102+1</f>
         <v>2</v>
       </c>
-      <c r="Y102" s="14">
+      <c r="Y102" s="17">
         <f t="shared" ref="Y102" si="22">X102+1</f>
         <v>3</v>
       </c>
@@ -6829,7 +6997,9 @@
       <c r="X103" s="13">
         <v>0</v>
       </c>
-      <c r="Y103" s="4"/>
+      <c r="Y103" s="13">
+        <v>0</v>
+      </c>
       <c r="Z103" s="4"/>
       <c r="AA103" s="4"/>
       <c r="AB103" s="4"/>
@@ -6881,7 +7051,9 @@
       <c r="X104" s="13">
         <v>0</v>
       </c>
-      <c r="Y104" s="7"/>
+      <c r="Y104" s="13">
+        <v>0</v>
+      </c>
       <c r="Z104" s="7"/>
       <c r="AA104" s="7"/>
       <c r="AB104" s="7"/>
@@ -6933,7 +7105,9 @@
       <c r="X105" s="13">
         <v>0</v>
       </c>
-      <c r="Y105" s="7"/>
+      <c r="Y105" s="13">
+        <v>0</v>
+      </c>
       <c r="Z105" s="7"/>
       <c r="AA105" s="7"/>
       <c r="AB105" s="7"/>
@@ -6985,7 +7159,9 @@
       <c r="X106" s="13">
         <v>0</v>
       </c>
-      <c r="Y106" s="7"/>
+      <c r="Y106" s="13">
+        <v>0</v>
+      </c>
       <c r="Z106" s="7"/>
       <c r="AA106" s="7"/>
       <c r="AB106" s="7"/>
@@ -7037,7 +7213,9 @@
       <c r="X107" s="13">
         <v>0</v>
       </c>
-      <c r="Y107" s="7"/>
+      <c r="Y107" s="13">
+        <v>0</v>
+      </c>
       <c r="Z107" s="7"/>
       <c r="AA107" s="7"/>
       <c r="AB107" s="7"/>
@@ -7089,7 +7267,9 @@
       <c r="X108" s="13">
         <v>0</v>
       </c>
-      <c r="Y108" s="7"/>
+      <c r="Y108" s="13">
+        <v>0</v>
+      </c>
       <c r="Z108" s="7"/>
       <c r="AA108" s="7"/>
       <c r="AB108" s="7"/>
@@ -7141,7 +7321,9 @@
       <c r="X109" s="13">
         <v>0</v>
       </c>
-      <c r="Y109" s="7"/>
+      <c r="Y109" s="13">
+        <v>0</v>
+      </c>
       <c r="Z109" s="7"/>
       <c r="AA109" s="7"/>
       <c r="AB109" s="7"/>
@@ -7193,7 +7375,9 @@
       <c r="X110" s="13">
         <v>0</v>
       </c>
-      <c r="Y110" s="7"/>
+      <c r="Y110" s="13">
+        <v>0</v>
+      </c>
       <c r="Z110" s="7"/>
       <c r="AA110" s="7"/>
       <c r="AB110" s="7"/>
@@ -7245,7 +7429,9 @@
       <c r="X111" s="13">
         <v>0</v>
       </c>
-      <c r="Y111" s="7"/>
+      <c r="Y111" s="13">
+        <v>0</v>
+      </c>
       <c r="Z111" s="7"/>
       <c r="AA111" s="7"/>
       <c r="AB111" s="7"/>
@@ -7297,7 +7483,9 @@
       <c r="X112" s="13">
         <v>0</v>
       </c>
-      <c r="Y112" s="7"/>
+      <c r="Y112" s="13">
+        <v>0</v>
+      </c>
       <c r="Z112" s="7"/>
       <c r="AA112" s="7"/>
       <c r="AB112" s="7"/>
@@ -7349,7 +7537,9 @@
       <c r="X113" s="12">
         <v>2</v>
       </c>
-      <c r="Y113" s="7"/>
+      <c r="Y113" s="12">
+        <v>0</v>
+      </c>
       <c r="Z113" s="7"/>
       <c r="AA113" s="7"/>
       <c r="AB113" s="7"/>
@@ -7401,7 +7591,9 @@
       <c r="X114" s="12">
         <v>0</v>
       </c>
-      <c r="Y114" s="7"/>
+      <c r="Y114" s="12">
+        <v>0</v>
+      </c>
       <c r="Z114" s="7"/>
       <c r="AA114" s="7"/>
       <c r="AB114" s="7"/>
@@ -7453,7 +7645,9 @@
       <c r="X115" s="12">
         <v>0</v>
       </c>
-      <c r="Y115" s="7"/>
+      <c r="Y115" s="12">
+        <v>0</v>
+      </c>
       <c r="Z115" s="7"/>
       <c r="AA115" s="7"/>
       <c r="AB115" s="7"/>
@@ -7505,7 +7699,9 @@
       <c r="X116" s="12">
         <v>0</v>
       </c>
-      <c r="Y116" s="7"/>
+      <c r="Y116" s="12">
+        <v>0</v>
+      </c>
       <c r="Z116" s="7"/>
       <c r="AA116" s="7"/>
       <c r="AB116" s="7"/>
@@ -7557,7 +7753,9 @@
       <c r="X117" s="12">
         <v>2</v>
       </c>
-      <c r="Y117" s="7"/>
+      <c r="Y117" s="12">
+        <v>2</v>
+      </c>
       <c r="Z117" s="7"/>
       <c r="AA117" s="7"/>
       <c r="AB117" s="7"/>
@@ -7609,7 +7807,9 @@
       <c r="X118" s="12">
         <v>0</v>
       </c>
-      <c r="Y118" s="7"/>
+      <c r="Y118" s="12">
+        <v>0</v>
+      </c>
       <c r="Z118" s="7"/>
       <c r="AA118" s="7"/>
       <c r="AB118" s="7"/>
@@ -7661,7 +7861,9 @@
       <c r="X119" s="12">
         <v>0</v>
       </c>
-      <c r="Y119" s="7"/>
+      <c r="Y119" s="12">
+        <v>0</v>
+      </c>
       <c r="Z119" s="7"/>
       <c r="AA119" s="7"/>
       <c r="AB119" s="7"/>
@@ -7713,7 +7915,9 @@
       <c r="X120" s="12">
         <v>0</v>
       </c>
-      <c r="Y120" s="7"/>
+      <c r="Y120" s="12">
+        <v>0</v>
+      </c>
       <c r="Z120" s="7"/>
       <c r="AA120" s="7"/>
       <c r="AB120" s="7"/>
@@ -7765,7 +7969,9 @@
       <c r="X121" s="12">
         <v>0</v>
       </c>
-      <c r="Y121" s="7"/>
+      <c r="Y121" s="12">
+        <v>0</v>
+      </c>
       <c r="Z121" s="7"/>
       <c r="AA121" s="7"/>
       <c r="AB121" s="7"/>
@@ -7817,7 +8023,9 @@
       <c r="X122" s="12">
         <v>0</v>
       </c>
-      <c r="Y122" s="7"/>
+      <c r="Y122" s="12">
+        <v>0</v>
+      </c>
       <c r="Z122" s="7"/>
       <c r="AA122" s="7"/>
       <c r="AB122" s="7"/>
@@ -7869,7 +8077,9 @@
       <c r="X123" s="12">
         <v>0</v>
       </c>
-      <c r="Y123" s="7"/>
+      <c r="Y123" s="12">
+        <v>0</v>
+      </c>
       <c r="Z123" s="7"/>
       <c r="AA123" s="7"/>
       <c r="AB123" s="7"/>
@@ -7921,7 +8131,9 @@
       <c r="X124" s="12">
         <v>0</v>
       </c>
-      <c r="Y124" s="7"/>
+      <c r="Y124" s="12">
+        <v>0</v>
+      </c>
       <c r="Z124" s="7"/>
       <c r="AA124" s="7"/>
       <c r="AB124" s="7"/>
@@ -7973,7 +8185,9 @@
       <c r="X125" s="12">
         <v>0</v>
       </c>
-      <c r="Y125" s="7"/>
+      <c r="Y125" s="12">
+        <v>0</v>
+      </c>
       <c r="Z125" s="7"/>
       <c r="AA125" s="7"/>
       <c r="AB125" s="7"/>
@@ -8025,7 +8239,9 @@
       <c r="X126" s="12">
         <v>0</v>
       </c>
-      <c r="Y126" s="7"/>
+      <c r="Y126" s="12">
+        <v>0</v>
+      </c>
       <c r="Z126" s="7"/>
       <c r="AA126" s="7"/>
       <c r="AB126" s="7"/>
@@ -8077,7 +8293,9 @@
       <c r="X127" s="12">
         <v>0</v>
       </c>
-      <c r="Y127" s="7"/>
+      <c r="Y127" s="12">
+        <v>2</v>
+      </c>
       <c r="Z127" s="7"/>
       <c r="AA127" s="7"/>
       <c r="AB127" s="7"/>
@@ -8129,7 +8347,9 @@
       <c r="X128" s="12">
         <v>0</v>
       </c>
-      <c r="Y128" s="7"/>
+      <c r="Y128" s="12">
+        <v>0</v>
+      </c>
       <c r="Z128" s="7"/>
       <c r="AA128" s="7"/>
       <c r="AB128" s="7"/>
@@ -8181,7 +8401,9 @@
       <c r="X129" s="12">
         <v>2</v>
       </c>
-      <c r="Y129" s="7"/>
+      <c r="Y129" s="12">
+        <v>2</v>
+      </c>
       <c r="Z129" s="7"/>
       <c r="AA129" s="7"/>
       <c r="AB129" s="7"/>
@@ -8233,7 +8455,9 @@
       <c r="X130" s="12">
         <v>0</v>
       </c>
-      <c r="Y130" s="7"/>
+      <c r="Y130" s="12">
+        <v>0</v>
+      </c>
       <c r="Z130" s="7"/>
       <c r="AA130" s="7"/>
       <c r="AB130" s="7"/>
@@ -8285,7 +8509,9 @@
       <c r="X131" s="12">
         <v>0</v>
       </c>
-      <c r="Y131" s="7"/>
+      <c r="Y131" s="12">
+        <v>0</v>
+      </c>
       <c r="Z131" s="7"/>
       <c r="AA131" s="7"/>
       <c r="AB131" s="7"/>
@@ -8337,7 +8563,9 @@
       <c r="X132" s="12">
         <v>0</v>
       </c>
-      <c r="Y132" s="7"/>
+      <c r="Y132" s="12">
+        <v>0</v>
+      </c>
       <c r="Z132" s="7"/>
       <c r="AA132" s="7"/>
       <c r="AB132" s="7"/>
@@ -8377,28 +8605,28 @@
       <c r="V133"/>
     </row>
     <row r="134" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B134" s="24" t="s">
+      <c r="B134" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="C134" s="24"/>
-      <c r="D134" s="24"/>
-      <c r="E134" s="24"/>
-      <c r="F134" s="24"/>
-      <c r="G134" s="24"/>
-      <c r="H134" s="24"/>
-      <c r="I134" s="24"/>
-      <c r="J134" s="24"/>
-      <c r="K134" s="24"/>
-      <c r="L134" s="24"/>
-      <c r="M134" s="24"/>
-      <c r="N134" s="24"/>
-      <c r="O134" s="24"/>
-      <c r="P134" s="24"/>
-      <c r="Q134" s="24"/>
-      <c r="R134" s="24"/>
-      <c r="S134" s="24"/>
-      <c r="T134" s="24"/>
-      <c r="U134" s="24"/>
+      <c r="C134" s="21"/>
+      <c r="D134" s="21"/>
+      <c r="E134" s="21"/>
+      <c r="F134" s="21"/>
+      <c r="G134" s="21"/>
+      <c r="H134" s="21"/>
+      <c r="I134" s="21"/>
+      <c r="J134" s="21"/>
+      <c r="K134" s="21"/>
+      <c r="L134" s="21"/>
+      <c r="M134" s="21"/>
+      <c r="N134" s="21"/>
+      <c r="O134" s="21"/>
+      <c r="P134" s="21"/>
+      <c r="Q134" s="21"/>
+      <c r="R134" s="21"/>
+      <c r="S134" s="21"/>
+      <c r="T134" s="21"/>
+      <c r="U134" s="21"/>
       <c r="V134" s="8"/>
       <c r="W134" s="9"/>
       <c r="X134" s="9"/>
@@ -8417,38 +8645,38 @@
     </row>
     <row r="135" spans="1:36" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135"/>
-      <c r="B135" s="25"/>
-      <c r="C135" s="26"/>
-      <c r="D135" s="26"/>
-      <c r="E135" s="26"/>
-      <c r="F135" s="26"/>
-      <c r="G135" s="26"/>
-      <c r="H135" s="26"/>
-      <c r="I135" s="26"/>
-      <c r="J135" s="26"/>
-      <c r="K135" s="26"/>
-      <c r="L135" s="26"/>
-      <c r="M135" s="26"/>
-      <c r="N135" s="26"/>
-      <c r="O135" s="26"/>
-      <c r="P135" s="26"/>
-      <c r="Q135" s="26"/>
-      <c r="R135" s="26"/>
-      <c r="S135" s="26"/>
-      <c r="T135" s="26"/>
-      <c r="U135" s="27"/>
-      <c r="V135" s="10">
-        <v>0</v>
-      </c>
-      <c r="W135" s="14">
+      <c r="B135" s="26"/>
+      <c r="C135" s="27"/>
+      <c r="D135" s="27"/>
+      <c r="E135" s="27"/>
+      <c r="F135" s="27"/>
+      <c r="G135" s="27"/>
+      <c r="H135" s="27"/>
+      <c r="I135" s="27"/>
+      <c r="J135" s="27"/>
+      <c r="K135" s="27"/>
+      <c r="L135" s="27"/>
+      <c r="M135" s="27"/>
+      <c r="N135" s="27"/>
+      <c r="O135" s="27"/>
+      <c r="P135" s="27"/>
+      <c r="Q135" s="27"/>
+      <c r="R135" s="27"/>
+      <c r="S135" s="27"/>
+      <c r="T135" s="27"/>
+      <c r="U135" s="28"/>
+      <c r="V135" s="17">
+        <v>0</v>
+      </c>
+      <c r="W135" s="17">
         <f t="shared" ref="W135" si="27">V135+1</f>
         <v>1</v>
       </c>
-      <c r="X135" s="14">
+      <c r="X135" s="17">
         <f t="shared" ref="X135" si="28">W135+1</f>
         <v>2</v>
       </c>
-      <c r="Y135" s="14">
+      <c r="Y135" s="17">
         <f t="shared" ref="Y135" si="29">X135+1</f>
         <v>3</v>
       </c>
@@ -8521,7 +8749,9 @@
       <c r="X136" s="13">
         <v>3</v>
       </c>
-      <c r="Y136" s="4"/>
+      <c r="Y136" s="13">
+        <v>3</v>
+      </c>
       <c r="Z136" s="4"/>
       <c r="AA136" s="4"/>
       <c r="AB136" s="4"/>
@@ -8573,7 +8803,9 @@
       <c r="X137" s="12">
         <v>0</v>
       </c>
-      <c r="Y137" s="7"/>
+      <c r="Y137" s="12">
+        <v>1</v>
+      </c>
       <c r="Z137" s="7"/>
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
@@ -8625,7 +8857,9 @@
       <c r="X138" s="12">
         <v>0</v>
       </c>
-      <c r="Y138" s="7"/>
+      <c r="Y138" s="12">
+        <v>0</v>
+      </c>
       <c r="Z138" s="7"/>
       <c r="AA138" s="7"/>
       <c r="AB138" s="7"/>
@@ -8677,7 +8911,9 @@
       <c r="X139" s="12">
         <v>0</v>
       </c>
-      <c r="Y139" s="7"/>
+      <c r="Y139" s="12">
+        <v>0</v>
+      </c>
       <c r="Z139" s="7"/>
       <c r="AA139" s="7"/>
       <c r="AB139" s="7"/>
@@ -8729,7 +8965,9 @@
       <c r="X140" s="12">
         <v>0</v>
       </c>
-      <c r="Y140" s="7"/>
+      <c r="Y140" s="12">
+        <v>0</v>
+      </c>
       <c r="Z140" s="7"/>
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
@@ -8781,7 +9019,9 @@
       <c r="X141" s="12">
         <v>3</v>
       </c>
-      <c r="Y141" s="7"/>
+      <c r="Y141" s="12">
+        <v>3</v>
+      </c>
       <c r="Z141" s="7"/>
       <c r="AA141" s="7"/>
       <c r="AB141" s="7"/>
@@ -8833,7 +9073,9 @@
       <c r="X142" s="12">
         <v>1</v>
       </c>
-      <c r="Y142" s="7"/>
+      <c r="Y142" s="12">
+        <v>2</v>
+      </c>
       <c r="Z142" s="7"/>
       <c r="AA142" s="7"/>
       <c r="AB142" s="7"/>
@@ -8885,7 +9127,9 @@
       <c r="X143" s="12">
         <v>3</v>
       </c>
-      <c r="Y143" s="7"/>
+      <c r="Y143" s="12">
+        <v>0</v>
+      </c>
       <c r="Z143" s="7"/>
       <c r="AA143" s="7"/>
       <c r="AB143" s="7"/>
@@ -8937,7 +9181,9 @@
       <c r="X144" s="12">
         <v>3</v>
       </c>
-      <c r="Y144" s="7"/>
+      <c r="Y144" s="12">
+        <v>3</v>
+      </c>
       <c r="Z144" s="7"/>
       <c r="AA144" s="7"/>
       <c r="AB144" s="7"/>
@@ -8989,7 +9235,9 @@
       <c r="X145" s="12">
         <v>0</v>
       </c>
-      <c r="Y145" s="7"/>
+      <c r="Y145" s="12">
+        <v>0</v>
+      </c>
       <c r="Z145" s="7"/>
       <c r="AA145" s="7"/>
       <c r="AB145" s="7"/>
@@ -9041,7 +9289,9 @@
       <c r="X146" s="12">
         <v>0</v>
       </c>
-      <c r="Y146" s="7"/>
+      <c r="Y146" s="12">
+        <v>0</v>
+      </c>
       <c r="Z146" s="7"/>
       <c r="AA146" s="7"/>
       <c r="AB146" s="7"/>
@@ -9093,7 +9343,9 @@
       <c r="X147" s="12">
         <v>3</v>
       </c>
-      <c r="Y147" s="7"/>
+      <c r="Y147" s="12">
+        <v>0</v>
+      </c>
       <c r="Z147" s="7"/>
       <c r="AA147" s="7"/>
       <c r="AB147" s="7"/>
@@ -9145,7 +9397,9 @@
       <c r="X148" s="12">
         <v>0</v>
       </c>
-      <c r="Y148" s="7"/>
+      <c r="Y148" s="12">
+        <v>0</v>
+      </c>
       <c r="Z148" s="7"/>
       <c r="AA148" s="7"/>
       <c r="AB148" s="7"/>
@@ -9197,7 +9451,9 @@
       <c r="X149" s="12">
         <v>3</v>
       </c>
-      <c r="Y149" s="7"/>
+      <c r="Y149" s="12">
+        <v>3</v>
+      </c>
       <c r="Z149" s="7"/>
       <c r="AA149" s="7"/>
       <c r="AB149" s="7"/>
@@ -9249,7 +9505,9 @@
       <c r="X150" s="12">
         <v>0</v>
       </c>
-      <c r="Y150" s="7"/>
+      <c r="Y150" s="12">
+        <v>3</v>
+      </c>
       <c r="Z150" s="7"/>
       <c r="AA150" s="7"/>
       <c r="AB150" s="7"/>
@@ -9301,7 +9559,9 @@
       <c r="X151" s="12">
         <v>3</v>
       </c>
-      <c r="Y151" s="7"/>
+      <c r="Y151" s="12">
+        <v>3</v>
+      </c>
       <c r="Z151" s="7"/>
       <c r="AA151" s="7"/>
       <c r="AB151" s="7"/>
@@ -9353,7 +9613,9 @@
       <c r="X152" s="12">
         <v>2</v>
       </c>
-      <c r="Y152" s="7"/>
+      <c r="Y152" s="12">
+        <v>2</v>
+      </c>
       <c r="Z152" s="7"/>
       <c r="AA152" s="7"/>
       <c r="AB152" s="7"/>
@@ -9405,7 +9667,9 @@
       <c r="X153" s="12">
         <v>0</v>
       </c>
-      <c r="Y153" s="7"/>
+      <c r="Y153" s="12">
+        <v>0</v>
+      </c>
       <c r="Z153" s="7"/>
       <c r="AA153" s="7"/>
       <c r="AB153" s="7"/>
@@ -9452,12 +9716,14 @@
         <v>2</v>
       </c>
       <c r="W154" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X154" s="12">
         <v>3</v>
       </c>
-      <c r="Y154" s="7"/>
+      <c r="Y154" s="12">
+        <v>3</v>
+      </c>
       <c r="Z154" s="7"/>
       <c r="AA154" s="7"/>
       <c r="AB154" s="7"/>
@@ -9509,7 +9775,9 @@
       <c r="X155" s="12">
         <v>3</v>
       </c>
-      <c r="Y155" s="7"/>
+      <c r="Y155" s="12">
+        <v>3</v>
+      </c>
       <c r="Z155" s="7"/>
       <c r="AA155" s="7"/>
       <c r="AB155" s="7"/>
@@ -9561,7 +9829,9 @@
       <c r="X156" s="12">
         <v>3</v>
       </c>
-      <c r="Y156" s="7"/>
+      <c r="Y156" s="12">
+        <v>3</v>
+      </c>
       <c r="Z156" s="7"/>
       <c r="AA156" s="7"/>
       <c r="AB156" s="7"/>
@@ -9613,7 +9883,9 @@
       <c r="X157" s="12">
         <v>0</v>
       </c>
-      <c r="Y157" s="7"/>
+      <c r="Y157" s="12">
+        <v>0</v>
+      </c>
       <c r="Z157" s="7"/>
       <c r="AA157" s="7"/>
       <c r="AB157" s="7"/>
@@ -9665,7 +9937,9 @@
       <c r="X158" s="12">
         <v>3</v>
       </c>
-      <c r="Y158" s="7"/>
+      <c r="Y158" s="12">
+        <v>3</v>
+      </c>
       <c r="Z158" s="7"/>
       <c r="AA158" s="7"/>
       <c r="AB158" s="7"/>
@@ -9717,7 +9991,9 @@
       <c r="X159" s="12">
         <v>0</v>
       </c>
-      <c r="Y159" s="7"/>
+      <c r="Y159" s="12">
+        <v>0</v>
+      </c>
       <c r="Z159" s="7"/>
       <c r="AA159" s="7"/>
       <c r="AB159" s="7"/>
@@ -9769,7 +10045,9 @@
       <c r="X160" s="12">
         <v>0</v>
       </c>
-      <c r="Y160" s="7"/>
+      <c r="Y160" s="12">
+        <v>0</v>
+      </c>
       <c r="Z160" s="7"/>
       <c r="AA160" s="7"/>
       <c r="AB160" s="7"/>
@@ -9821,7 +10099,9 @@
       <c r="X161" s="12">
         <v>0</v>
       </c>
-      <c r="Y161" s="7"/>
+      <c r="Y161" s="12">
+        <v>0</v>
+      </c>
       <c r="Z161" s="7"/>
       <c r="AA161" s="7"/>
       <c r="AB161" s="7"/>
@@ -9873,7 +10153,9 @@
       <c r="X162" s="12">
         <v>3</v>
       </c>
-      <c r="Y162" s="7"/>
+      <c r="Y162" s="12">
+        <v>0</v>
+      </c>
       <c r="Z162" s="7"/>
       <c r="AA162" s="7"/>
       <c r="AB162" s="7"/>
@@ -9925,7 +10207,9 @@
       <c r="X163" s="12">
         <v>3</v>
       </c>
-      <c r="Y163" s="7"/>
+      <c r="Y163" s="12">
+        <v>3</v>
+      </c>
       <c r="Z163" s="7"/>
       <c r="AA163" s="7"/>
       <c r="AB163" s="7"/>
@@ -9977,7 +10261,9 @@
       <c r="X164" s="12">
         <v>0</v>
       </c>
-      <c r="Y164" s="7"/>
+      <c r="Y164" s="12">
+        <v>0</v>
+      </c>
       <c r="Z164" s="7"/>
       <c r="AA164" s="7"/>
       <c r="AB164" s="7"/>
@@ -10029,7 +10315,9 @@
       <c r="X165" s="12">
         <v>3</v>
       </c>
-      <c r="Y165" s="7"/>
+      <c r="Y165" s="12">
+        <v>3</v>
+      </c>
       <c r="Z165" s="7"/>
       <c r="AA165" s="7"/>
       <c r="AB165" s="7"/>
@@ -10069,28 +10357,28 @@
       <c r="V166"/>
     </row>
     <row r="167" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B167" s="24" t="s">
+      <c r="B167" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="C167" s="24"/>
-      <c r="D167" s="24"/>
-      <c r="E167" s="24"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="24"/>
-      <c r="H167" s="24"/>
-      <c r="I167" s="24"/>
-      <c r="J167" s="24"/>
-      <c r="K167" s="24"/>
-      <c r="L167" s="24"/>
-      <c r="M167" s="24"/>
-      <c r="N167" s="24"/>
-      <c r="O167" s="24"/>
-      <c r="P167" s="24"/>
-      <c r="Q167" s="24"/>
-      <c r="R167" s="24"/>
-      <c r="S167" s="24"/>
-      <c r="T167" s="24"/>
-      <c r="U167" s="24"/>
+      <c r="C167" s="21"/>
+      <c r="D167" s="21"/>
+      <c r="E167" s="21"/>
+      <c r="F167" s="21"/>
+      <c r="G167" s="21"/>
+      <c r="H167" s="21"/>
+      <c r="I167" s="21"/>
+      <c r="J167" s="21"/>
+      <c r="K167" s="21"/>
+      <c r="L167" s="21"/>
+      <c r="M167" s="21"/>
+      <c r="N167" s="21"/>
+      <c r="O167" s="21"/>
+      <c r="P167" s="21"/>
+      <c r="Q167" s="21"/>
+      <c r="R167" s="21"/>
+      <c r="S167" s="21"/>
+      <c r="T167" s="21"/>
+      <c r="U167" s="21"/>
       <c r="V167" s="8"/>
       <c r="W167" s="9"/>
       <c r="X167" s="9"/>
@@ -10109,38 +10397,38 @@
     </row>
     <row r="168" spans="1:36" ht="19.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168"/>
-      <c r="B168" s="25"/>
-      <c r="C168" s="26"/>
-      <c r="D168" s="26"/>
-      <c r="E168" s="26"/>
-      <c r="F168" s="26"/>
-      <c r="G168" s="26"/>
-      <c r="H168" s="26"/>
-      <c r="I168" s="26"/>
-      <c r="J168" s="26"/>
-      <c r="K168" s="26"/>
-      <c r="L168" s="26"/>
-      <c r="M168" s="26"/>
-      <c r="N168" s="26"/>
-      <c r="O168" s="26"/>
-      <c r="P168" s="26"/>
-      <c r="Q168" s="26"/>
-      <c r="R168" s="26"/>
-      <c r="S168" s="26"/>
-      <c r="T168" s="26"/>
-      <c r="U168" s="27"/>
-      <c r="V168" s="10">
-        <v>0</v>
-      </c>
-      <c r="W168" s="14">
+      <c r="B168" s="26"/>
+      <c r="C168" s="27"/>
+      <c r="D168" s="27"/>
+      <c r="E168" s="27"/>
+      <c r="F168" s="27"/>
+      <c r="G168" s="27"/>
+      <c r="H168" s="27"/>
+      <c r="I168" s="27"/>
+      <c r="J168" s="27"/>
+      <c r="K168" s="27"/>
+      <c r="L168" s="27"/>
+      <c r="M168" s="27"/>
+      <c r="N168" s="27"/>
+      <c r="O168" s="27"/>
+      <c r="P168" s="27"/>
+      <c r="Q168" s="27"/>
+      <c r="R168" s="27"/>
+      <c r="S168" s="27"/>
+      <c r="T168" s="27"/>
+      <c r="U168" s="28"/>
+      <c r="V168" s="17">
+        <v>0</v>
+      </c>
+      <c r="W168" s="17">
         <f t="shared" ref="W168" si="34">V168+1</f>
         <v>1</v>
       </c>
-      <c r="X168" s="14">
+      <c r="X168" s="17">
         <f t="shared" ref="X168" si="35">W168+1</f>
         <v>2</v>
       </c>
-      <c r="Y168" s="14">
+      <c r="Y168" s="17">
         <f t="shared" ref="Y168" si="36">X168+1</f>
         <v>3</v>
       </c>
@@ -10214,7 +10502,9 @@
       <c r="X169" s="13">
         <v>0</v>
       </c>
-      <c r="Y169" s="4"/>
+      <c r="Y169" s="13">
+        <v>2</v>
+      </c>
       <c r="Z169" s="4"/>
       <c r="AA169" s="4"/>
       <c r="AB169" s="4"/>
@@ -10266,7 +10556,9 @@
       <c r="X170" s="12">
         <v>0</v>
       </c>
-      <c r="Y170" s="7"/>
+      <c r="Y170" s="12">
+        <v>0</v>
+      </c>
       <c r="Z170" s="7"/>
       <c r="AA170" s="7"/>
       <c r="AB170" s="7"/>
@@ -10318,7 +10610,9 @@
       <c r="X171" s="12">
         <v>3</v>
       </c>
-      <c r="Y171" s="7"/>
+      <c r="Y171" s="12">
+        <v>3</v>
+      </c>
       <c r="Z171" s="7"/>
       <c r="AA171" s="7"/>
       <c r="AB171" s="7"/>
@@ -10370,7 +10664,9 @@
       <c r="X172" s="12">
         <v>3</v>
       </c>
-      <c r="Y172" s="7"/>
+      <c r="Y172" s="12">
+        <v>2</v>
+      </c>
       <c r="Z172" s="7"/>
       <c r="AA172" s="7"/>
       <c r="AB172" s="7"/>
@@ -10422,7 +10718,9 @@
       <c r="X173" s="12">
         <v>3</v>
       </c>
-      <c r="Y173" s="7"/>
+      <c r="Y173" s="12">
+        <v>2</v>
+      </c>
       <c r="Z173" s="7"/>
       <c r="AA173" s="7"/>
       <c r="AB173" s="7"/>
@@ -10474,7 +10772,9 @@
       <c r="X174" s="12">
         <v>3</v>
       </c>
-      <c r="Y174" s="7"/>
+      <c r="Y174" s="12">
+        <v>3</v>
+      </c>
       <c r="Z174" s="7"/>
       <c r="AA174" s="7"/>
       <c r="AB174" s="7"/>
@@ -10526,7 +10826,9 @@
       <c r="X175" s="12">
         <v>3</v>
       </c>
-      <c r="Y175" s="7"/>
+      <c r="Y175" s="12">
+        <v>0</v>
+      </c>
       <c r="Z175" s="7"/>
       <c r="AA175" s="7"/>
       <c r="AB175" s="7"/>
@@ -10578,7 +10880,9 @@
       <c r="X176" s="12">
         <v>2</v>
       </c>
-      <c r="Y176" s="7"/>
+      <c r="Y176" s="12">
+        <v>0</v>
+      </c>
       <c r="Z176" s="7"/>
       <c r="AA176" s="7"/>
       <c r="AB176" s="7"/>
@@ -10630,7 +10934,9 @@
       <c r="X177" s="12">
         <v>0</v>
       </c>
-      <c r="Y177" s="7"/>
+      <c r="Y177" s="12">
+        <v>0</v>
+      </c>
       <c r="Z177" s="7"/>
       <c r="AA177" s="7"/>
       <c r="AB177" s="7"/>
@@ -10682,7 +10988,9 @@
       <c r="X178" s="12">
         <v>0</v>
       </c>
-      <c r="Y178" s="7"/>
+      <c r="Y178" s="12">
+        <v>0</v>
+      </c>
       <c r="Z178" s="7"/>
       <c r="AA178" s="7"/>
       <c r="AB178" s="7"/>
@@ -10734,7 +11042,9 @@
       <c r="X179" s="12">
         <v>0</v>
       </c>
-      <c r="Y179" s="7"/>
+      <c r="Y179" s="12">
+        <v>0</v>
+      </c>
       <c r="Z179" s="7"/>
       <c r="AA179" s="7"/>
       <c r="AB179" s="7"/>
@@ -10786,7 +11096,9 @@
       <c r="X180" s="12">
         <v>3</v>
       </c>
-      <c r="Y180" s="7"/>
+      <c r="Y180" s="12">
+        <v>0</v>
+      </c>
       <c r="Z180" s="7"/>
       <c r="AA180" s="7"/>
       <c r="AB180" s="7"/>
@@ -10838,7 +11150,9 @@
       <c r="X181" s="12">
         <v>3</v>
       </c>
-      <c r="Y181" s="7"/>
+      <c r="Y181" s="12">
+        <v>3</v>
+      </c>
       <c r="Z181" s="7"/>
       <c r="AA181" s="7"/>
       <c r="AB181" s="7"/>
@@ -10890,7 +11204,9 @@
       <c r="X182" s="12">
         <v>2</v>
       </c>
-      <c r="Y182" s="7"/>
+      <c r="Y182" s="12">
+        <v>2</v>
+      </c>
       <c r="Z182" s="7"/>
       <c r="AA182" s="7"/>
       <c r="AB182" s="7"/>
@@ -10942,7 +11258,9 @@
       <c r="X183" s="12">
         <v>0</v>
       </c>
-      <c r="Y183" s="7"/>
+      <c r="Y183" s="12">
+        <v>0</v>
+      </c>
       <c r="Z183" s="7"/>
       <c r="AA183" s="7"/>
       <c r="AB183" s="7"/>
@@ -10994,7 +11312,9 @@
       <c r="X184" s="12">
         <v>0</v>
       </c>
-      <c r="Y184" s="7"/>
+      <c r="Y184" s="12">
+        <v>0</v>
+      </c>
       <c r="Z184" s="7"/>
       <c r="AA184" s="7"/>
       <c r="AB184" s="7"/>
@@ -11046,7 +11366,9 @@
       <c r="X185" s="12">
         <v>3</v>
       </c>
-      <c r="Y185" s="7"/>
+      <c r="Y185" s="12">
+        <v>3</v>
+      </c>
       <c r="Z185" s="7"/>
       <c r="AA185" s="7"/>
       <c r="AB185" s="7"/>
@@ -11098,7 +11420,9 @@
       <c r="X186" s="12">
         <v>0</v>
       </c>
-      <c r="Y186" s="7"/>
+      <c r="Y186" s="12">
+        <v>0</v>
+      </c>
       <c r="Z186" s="7"/>
       <c r="AA186" s="7"/>
       <c r="AB186" s="7"/>
@@ -11150,7 +11474,9 @@
       <c r="X187" s="12">
         <v>0</v>
       </c>
-      <c r="Y187" s="7"/>
+      <c r="Y187" s="12">
+        <v>0</v>
+      </c>
       <c r="Z187" s="7"/>
       <c r="AA187" s="7"/>
       <c r="AB187" s="7"/>
@@ -11202,7 +11528,9 @@
       <c r="X188" s="12">
         <v>3</v>
       </c>
-      <c r="Y188" s="7"/>
+      <c r="Y188" s="12">
+        <v>0</v>
+      </c>
       <c r="Z188" s="7"/>
       <c r="AA188" s="7"/>
       <c r="AB188" s="7"/>
@@ -11254,7 +11582,9 @@
       <c r="X189" s="12">
         <v>0</v>
       </c>
-      <c r="Y189" s="7"/>
+      <c r="Y189" s="12">
+        <v>0</v>
+      </c>
       <c r="Z189" s="7"/>
       <c r="AA189" s="7"/>
       <c r="AB189" s="7"/>
@@ -11306,7 +11636,9 @@
       <c r="X190" s="12">
         <v>0</v>
       </c>
-      <c r="Y190" s="7"/>
+      <c r="Y190" s="12">
+        <v>0</v>
+      </c>
       <c r="Z190" s="7"/>
       <c r="AA190" s="7"/>
       <c r="AB190" s="7"/>
@@ -11358,7 +11690,9 @@
       <c r="X191" s="12">
         <v>1</v>
       </c>
-      <c r="Y191" s="7"/>
+      <c r="Y191" s="12">
+        <v>2</v>
+      </c>
       <c r="Z191" s="7"/>
       <c r="AA191" s="7"/>
       <c r="AB191" s="7"/>
@@ -11410,7 +11744,9 @@
       <c r="X192" s="12">
         <v>0</v>
       </c>
-      <c r="Y192" s="7"/>
+      <c r="Y192" s="12">
+        <v>0</v>
+      </c>
       <c r="Z192" s="7"/>
       <c r="AA192" s="7"/>
       <c r="AB192" s="7"/>
@@ -11461,7 +11797,9 @@
       <c r="X193" s="12">
         <v>3</v>
       </c>
-      <c r="Y193" s="7"/>
+      <c r="Y193" s="12">
+        <v>3</v>
+      </c>
       <c r="Z193" s="7"/>
       <c r="AA193" s="7"/>
       <c r="AB193" s="7"/>
@@ -11512,7 +11850,9 @@
       <c r="X194" s="12">
         <v>3</v>
       </c>
-      <c r="Y194" s="7"/>
+      <c r="Y194" s="12">
+        <v>2</v>
+      </c>
       <c r="Z194" s="7"/>
       <c r="AA194" s="7"/>
       <c r="AB194" s="7"/>
@@ -11529,6 +11869,510 @@
     </row>
   </sheetData>
   <mergeCells count="528">
+    <mergeCell ref="B193:C193"/>
+    <mergeCell ref="D193:N193"/>
+    <mergeCell ref="O193:U193"/>
+    <mergeCell ref="B192:C192"/>
+    <mergeCell ref="D192:N192"/>
+    <mergeCell ref="O192:U192"/>
+    <mergeCell ref="V3:AI3"/>
+    <mergeCell ref="B190:C190"/>
+    <mergeCell ref="D190:N190"/>
+    <mergeCell ref="O190:U190"/>
+    <mergeCell ref="B191:C191"/>
+    <mergeCell ref="D191:N191"/>
+    <mergeCell ref="O191:U191"/>
+    <mergeCell ref="B188:C188"/>
+    <mergeCell ref="D188:N188"/>
+    <mergeCell ref="O188:U188"/>
+    <mergeCell ref="B189:C189"/>
+    <mergeCell ref="D189:N189"/>
+    <mergeCell ref="O189:U189"/>
+    <mergeCell ref="B186:C186"/>
+    <mergeCell ref="D186:N186"/>
+    <mergeCell ref="O186:U186"/>
+    <mergeCell ref="B187:C187"/>
+    <mergeCell ref="D187:N187"/>
+    <mergeCell ref="O187:U187"/>
+    <mergeCell ref="B184:C184"/>
+    <mergeCell ref="D184:N184"/>
+    <mergeCell ref="O184:U184"/>
+    <mergeCell ref="B185:C185"/>
+    <mergeCell ref="D185:N185"/>
+    <mergeCell ref="O185:U185"/>
+    <mergeCell ref="B182:C182"/>
+    <mergeCell ref="D182:N182"/>
+    <mergeCell ref="O182:U182"/>
+    <mergeCell ref="B183:C183"/>
+    <mergeCell ref="D183:N183"/>
+    <mergeCell ref="O183:U183"/>
+    <mergeCell ref="B180:C180"/>
+    <mergeCell ref="D180:N180"/>
+    <mergeCell ref="O180:U180"/>
+    <mergeCell ref="B181:C181"/>
+    <mergeCell ref="D181:N181"/>
+    <mergeCell ref="O181:U181"/>
+    <mergeCell ref="B178:C178"/>
+    <mergeCell ref="D178:N178"/>
+    <mergeCell ref="O178:U178"/>
+    <mergeCell ref="B179:C179"/>
+    <mergeCell ref="D179:N179"/>
+    <mergeCell ref="O179:U179"/>
+    <mergeCell ref="B176:C176"/>
+    <mergeCell ref="D176:N176"/>
+    <mergeCell ref="O176:U176"/>
+    <mergeCell ref="B177:C177"/>
+    <mergeCell ref="D177:N177"/>
+    <mergeCell ref="O177:U177"/>
+    <mergeCell ref="B174:C174"/>
+    <mergeCell ref="D174:N174"/>
+    <mergeCell ref="O174:U174"/>
+    <mergeCell ref="B175:C175"/>
+    <mergeCell ref="D175:N175"/>
+    <mergeCell ref="O175:U175"/>
+    <mergeCell ref="B172:C172"/>
+    <mergeCell ref="D172:N172"/>
+    <mergeCell ref="O172:U172"/>
+    <mergeCell ref="B173:C173"/>
+    <mergeCell ref="D173:N173"/>
+    <mergeCell ref="O173:U173"/>
+    <mergeCell ref="B170:C170"/>
+    <mergeCell ref="D170:N170"/>
+    <mergeCell ref="O170:U170"/>
+    <mergeCell ref="B171:C171"/>
+    <mergeCell ref="D171:N171"/>
+    <mergeCell ref="O171:U171"/>
+    <mergeCell ref="B165:C165"/>
+    <mergeCell ref="D165:N165"/>
+    <mergeCell ref="O165:U165"/>
+    <mergeCell ref="B167:U167"/>
+    <mergeCell ref="B169:C169"/>
+    <mergeCell ref="D169:N169"/>
+    <mergeCell ref="O169:U169"/>
+    <mergeCell ref="B163:C163"/>
+    <mergeCell ref="D163:N163"/>
+    <mergeCell ref="O163:U163"/>
+    <mergeCell ref="B164:C164"/>
+    <mergeCell ref="D164:N164"/>
+    <mergeCell ref="O164:U164"/>
+    <mergeCell ref="B168:U168"/>
+    <mergeCell ref="B161:C161"/>
+    <mergeCell ref="D161:N161"/>
+    <mergeCell ref="O161:U161"/>
+    <mergeCell ref="B162:C162"/>
+    <mergeCell ref="D162:N162"/>
+    <mergeCell ref="O162:U162"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="D159:N159"/>
+    <mergeCell ref="O159:U159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="D160:N160"/>
+    <mergeCell ref="O160:U160"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="D157:N157"/>
+    <mergeCell ref="O157:U157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="D158:N158"/>
+    <mergeCell ref="O158:U158"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="D155:N155"/>
+    <mergeCell ref="O155:U155"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="D156:N156"/>
+    <mergeCell ref="O156:U156"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="D153:N153"/>
+    <mergeCell ref="O153:U153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="D154:N154"/>
+    <mergeCell ref="O154:U154"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="D151:N151"/>
+    <mergeCell ref="O151:U151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="D152:N152"/>
+    <mergeCell ref="O152:U152"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="D149:N149"/>
+    <mergeCell ref="O149:U149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="D150:N150"/>
+    <mergeCell ref="O150:U150"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="D147:N147"/>
+    <mergeCell ref="O147:U147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="D148:N148"/>
+    <mergeCell ref="O148:U148"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="D145:N145"/>
+    <mergeCell ref="O145:U145"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="D146:N146"/>
+    <mergeCell ref="O146:U146"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="D143:N143"/>
+    <mergeCell ref="O143:U143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="D144:N144"/>
+    <mergeCell ref="O144:U144"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="D141:N141"/>
+    <mergeCell ref="O141:U141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="D142:N142"/>
+    <mergeCell ref="O142:U142"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="D139:N139"/>
+    <mergeCell ref="O139:U139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="D140:N140"/>
+    <mergeCell ref="O140:U140"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="D137:N137"/>
+    <mergeCell ref="O137:U137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="D138:N138"/>
+    <mergeCell ref="O138:U138"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="D132:N132"/>
+    <mergeCell ref="O132:U132"/>
+    <mergeCell ref="B134:U134"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="D136:N136"/>
+    <mergeCell ref="O136:U136"/>
+    <mergeCell ref="B135:U135"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="D130:N130"/>
+    <mergeCell ref="O130:U130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="D131:N131"/>
+    <mergeCell ref="O131:U131"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="D128:N128"/>
+    <mergeCell ref="O128:U128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="D129:N129"/>
+    <mergeCell ref="O129:U129"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="D126:N126"/>
+    <mergeCell ref="O126:U126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="D127:N127"/>
+    <mergeCell ref="O127:U127"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="D124:N124"/>
+    <mergeCell ref="O124:U124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="D125:N125"/>
+    <mergeCell ref="O125:U125"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="D122:N122"/>
+    <mergeCell ref="O122:U122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="D123:N123"/>
+    <mergeCell ref="O123:U123"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="D120:N120"/>
+    <mergeCell ref="O120:U120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="D121:N121"/>
+    <mergeCell ref="O121:U121"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="D118:N118"/>
+    <mergeCell ref="O118:U118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="D119:N119"/>
+    <mergeCell ref="O119:U119"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="D116:N116"/>
+    <mergeCell ref="O116:U116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="D117:N117"/>
+    <mergeCell ref="O117:U117"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="D114:N114"/>
+    <mergeCell ref="O114:U114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="D115:N115"/>
+    <mergeCell ref="O115:U115"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="D112:N112"/>
+    <mergeCell ref="O112:U112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="D113:N113"/>
+    <mergeCell ref="O113:U113"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="D110:N110"/>
+    <mergeCell ref="O110:U110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="D111:N111"/>
+    <mergeCell ref="O111:U111"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="D108:N108"/>
+    <mergeCell ref="O108:U108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="D109:N109"/>
+    <mergeCell ref="O109:U109"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="D106:N106"/>
+    <mergeCell ref="O106:U106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="D107:N107"/>
+    <mergeCell ref="O107:U107"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="D104:N104"/>
+    <mergeCell ref="O104:U104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="D105:N105"/>
+    <mergeCell ref="O105:U105"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:N99"/>
+    <mergeCell ref="O99:U99"/>
+    <mergeCell ref="B101:U101"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="D103:N103"/>
+    <mergeCell ref="O103:U103"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="D97:N97"/>
+    <mergeCell ref="O97:U97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="D98:N98"/>
+    <mergeCell ref="O98:U98"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="D95:N95"/>
+    <mergeCell ref="O95:U95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="D96:N96"/>
+    <mergeCell ref="O96:U96"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="D93:N93"/>
+    <mergeCell ref="O93:U93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="D94:N94"/>
+    <mergeCell ref="O94:U94"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="D91:N91"/>
+    <mergeCell ref="O91:U91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="D92:N92"/>
+    <mergeCell ref="O92:U92"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="D89:N89"/>
+    <mergeCell ref="O89:U89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="D90:N90"/>
+    <mergeCell ref="O90:U90"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="D87:N87"/>
+    <mergeCell ref="O87:U87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="D88:N88"/>
+    <mergeCell ref="O88:U88"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="D85:N85"/>
+    <mergeCell ref="O85:U85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="D86:N86"/>
+    <mergeCell ref="O86:U86"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="D83:N83"/>
+    <mergeCell ref="O83:U83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="D84:N84"/>
+    <mergeCell ref="O84:U84"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="D81:N81"/>
+    <mergeCell ref="O81:U81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:N82"/>
+    <mergeCell ref="O82:U82"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="D79:N79"/>
+    <mergeCell ref="O79:U79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="D80:N80"/>
+    <mergeCell ref="O80:U80"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="D77:N77"/>
+    <mergeCell ref="O77:U77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="D78:N78"/>
+    <mergeCell ref="O78:U78"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="D75:N75"/>
+    <mergeCell ref="O75:U75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="D76:N76"/>
+    <mergeCell ref="O76:U76"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="D73:N73"/>
+    <mergeCell ref="O73:U73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="D74:N74"/>
+    <mergeCell ref="O74:U74"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="D71:N71"/>
+    <mergeCell ref="O71:U71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="D72:N72"/>
+    <mergeCell ref="O72:U72"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="D66:N66"/>
+    <mergeCell ref="O66:U66"/>
+    <mergeCell ref="B68:U68"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="D70:N70"/>
+    <mergeCell ref="O70:U70"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:N64"/>
+    <mergeCell ref="O64:U64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:N65"/>
+    <mergeCell ref="O65:U65"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:N62"/>
+    <mergeCell ref="O62:U62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D63:N63"/>
+    <mergeCell ref="O63:U63"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:N60"/>
+    <mergeCell ref="O60:U60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:N61"/>
+    <mergeCell ref="O61:U61"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:N58"/>
+    <mergeCell ref="O58:U58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:N59"/>
+    <mergeCell ref="O59:U59"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:N56"/>
+    <mergeCell ref="O56:U56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:N57"/>
+    <mergeCell ref="O57:U57"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:N54"/>
+    <mergeCell ref="O54:U54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:N55"/>
+    <mergeCell ref="O55:U55"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:N52"/>
+    <mergeCell ref="O52:U52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:N53"/>
+    <mergeCell ref="O53:U53"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:N50"/>
+    <mergeCell ref="O50:U50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:N51"/>
+    <mergeCell ref="O51:U51"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:N48"/>
+    <mergeCell ref="O48:U48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:N49"/>
+    <mergeCell ref="O49:U49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:N46"/>
+    <mergeCell ref="O46:U46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:N47"/>
+    <mergeCell ref="O47:U47"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:N44"/>
+    <mergeCell ref="O44:U44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:N45"/>
+    <mergeCell ref="O45:U45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:N42"/>
+    <mergeCell ref="O42:U42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:N43"/>
+    <mergeCell ref="O43:U43"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:N40"/>
+    <mergeCell ref="O40:U40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:N41"/>
+    <mergeCell ref="O41:U41"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:N38"/>
+    <mergeCell ref="O38:U38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:N39"/>
+    <mergeCell ref="O39:U39"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:N33"/>
+    <mergeCell ref="O33:U33"/>
+    <mergeCell ref="B35:U35"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:N37"/>
+    <mergeCell ref="O37:U37"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:N31"/>
+    <mergeCell ref="O31:U31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:N32"/>
+    <mergeCell ref="O32:U32"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:N29"/>
+    <mergeCell ref="O29:U29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:N30"/>
+    <mergeCell ref="O30:U30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:N27"/>
+    <mergeCell ref="O27:U27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:N28"/>
+    <mergeCell ref="O28:U28"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:N25"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:N26"/>
+    <mergeCell ref="O26:U26"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:N23"/>
+    <mergeCell ref="O23:U23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:N24"/>
+    <mergeCell ref="O24:U24"/>
+    <mergeCell ref="O16:U16"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:N21"/>
+    <mergeCell ref="O21:U21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:N22"/>
+    <mergeCell ref="O22:U22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:N19"/>
+    <mergeCell ref="O19:U19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:N20"/>
+    <mergeCell ref="O20:U20"/>
+    <mergeCell ref="B1:U1"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:N3"/>
+    <mergeCell ref="O3:U3"/>
+    <mergeCell ref="B5:U5"/>
+    <mergeCell ref="B8:U8"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:N13"/>
+    <mergeCell ref="O13:U13"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:N11"/>
+    <mergeCell ref="O11:U11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:N12"/>
+    <mergeCell ref="O12:U12"/>
     <mergeCell ref="B194:C194"/>
     <mergeCell ref="D194:N194"/>
     <mergeCell ref="O194:U194"/>
@@ -11553,510 +12397,6 @@
     <mergeCell ref="O15:U15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:N16"/>
-    <mergeCell ref="B1:U1"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:N3"/>
-    <mergeCell ref="O3:U3"/>
-    <mergeCell ref="B5:U5"/>
-    <mergeCell ref="B8:U8"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:N13"/>
-    <mergeCell ref="O13:U13"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:N11"/>
-    <mergeCell ref="O11:U11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:N12"/>
-    <mergeCell ref="O12:U12"/>
-    <mergeCell ref="O16:U16"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:N21"/>
-    <mergeCell ref="O21:U21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:N22"/>
-    <mergeCell ref="O22:U22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:N19"/>
-    <mergeCell ref="O19:U19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:N20"/>
-    <mergeCell ref="O20:U20"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:N25"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:N26"/>
-    <mergeCell ref="O26:U26"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:N23"/>
-    <mergeCell ref="O23:U23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:N24"/>
-    <mergeCell ref="O24:U24"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:N29"/>
-    <mergeCell ref="O29:U29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:N30"/>
-    <mergeCell ref="O30:U30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:N27"/>
-    <mergeCell ref="O27:U27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:N28"/>
-    <mergeCell ref="O28:U28"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:N33"/>
-    <mergeCell ref="O33:U33"/>
-    <mergeCell ref="B35:U35"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:N37"/>
-    <mergeCell ref="O37:U37"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:N31"/>
-    <mergeCell ref="O31:U31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:N32"/>
-    <mergeCell ref="O32:U32"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:N40"/>
-    <mergeCell ref="O40:U40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:N41"/>
-    <mergeCell ref="O41:U41"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:N38"/>
-    <mergeCell ref="O38:U38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:N39"/>
-    <mergeCell ref="O39:U39"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:N44"/>
-    <mergeCell ref="O44:U44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:N45"/>
-    <mergeCell ref="O45:U45"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:N42"/>
-    <mergeCell ref="O42:U42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:N43"/>
-    <mergeCell ref="O43:U43"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:N48"/>
-    <mergeCell ref="O48:U48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:N49"/>
-    <mergeCell ref="O49:U49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:N46"/>
-    <mergeCell ref="O46:U46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:N47"/>
-    <mergeCell ref="O47:U47"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:N52"/>
-    <mergeCell ref="O52:U52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:N53"/>
-    <mergeCell ref="O53:U53"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:N50"/>
-    <mergeCell ref="O50:U50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:N51"/>
-    <mergeCell ref="O51:U51"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:N56"/>
-    <mergeCell ref="O56:U56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:N57"/>
-    <mergeCell ref="O57:U57"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:N54"/>
-    <mergeCell ref="O54:U54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:N55"/>
-    <mergeCell ref="O55:U55"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:N60"/>
-    <mergeCell ref="O60:U60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="D61:N61"/>
-    <mergeCell ref="O61:U61"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:N58"/>
-    <mergeCell ref="O58:U58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:N59"/>
-    <mergeCell ref="O59:U59"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="D64:N64"/>
-    <mergeCell ref="O64:U64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:N65"/>
-    <mergeCell ref="O65:U65"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:N62"/>
-    <mergeCell ref="O62:U62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D63:N63"/>
-    <mergeCell ref="O63:U63"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="D71:N71"/>
-    <mergeCell ref="O71:U71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="D72:N72"/>
-    <mergeCell ref="O72:U72"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="D66:N66"/>
-    <mergeCell ref="O66:U66"/>
-    <mergeCell ref="B68:U68"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="D70:N70"/>
-    <mergeCell ref="O70:U70"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="D75:N75"/>
-    <mergeCell ref="O75:U75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="D76:N76"/>
-    <mergeCell ref="O76:U76"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="D73:N73"/>
-    <mergeCell ref="O73:U73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="D74:N74"/>
-    <mergeCell ref="O74:U74"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="D79:N79"/>
-    <mergeCell ref="O79:U79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="D80:N80"/>
-    <mergeCell ref="O80:U80"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="D77:N77"/>
-    <mergeCell ref="O77:U77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="D78:N78"/>
-    <mergeCell ref="O78:U78"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="D83:N83"/>
-    <mergeCell ref="O83:U83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="D84:N84"/>
-    <mergeCell ref="O84:U84"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="D81:N81"/>
-    <mergeCell ref="O81:U81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:N82"/>
-    <mergeCell ref="O82:U82"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="D87:N87"/>
-    <mergeCell ref="O87:U87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="D88:N88"/>
-    <mergeCell ref="O88:U88"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="D85:N85"/>
-    <mergeCell ref="O85:U85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="D86:N86"/>
-    <mergeCell ref="O86:U86"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="D91:N91"/>
-    <mergeCell ref="O91:U91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="D92:N92"/>
-    <mergeCell ref="O92:U92"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="D89:N89"/>
-    <mergeCell ref="O89:U89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="D90:N90"/>
-    <mergeCell ref="O90:U90"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="D95:N95"/>
-    <mergeCell ref="O95:U95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="D96:N96"/>
-    <mergeCell ref="O96:U96"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="D93:N93"/>
-    <mergeCell ref="O93:U93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="D94:N94"/>
-    <mergeCell ref="O94:U94"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:N99"/>
-    <mergeCell ref="O99:U99"/>
-    <mergeCell ref="B101:U101"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="D103:N103"/>
-    <mergeCell ref="O103:U103"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="D97:N97"/>
-    <mergeCell ref="O97:U97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="D98:N98"/>
-    <mergeCell ref="O98:U98"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="D106:N106"/>
-    <mergeCell ref="O106:U106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="D107:N107"/>
-    <mergeCell ref="O107:U107"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="D104:N104"/>
-    <mergeCell ref="O104:U104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="D105:N105"/>
-    <mergeCell ref="O105:U105"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="D110:N110"/>
-    <mergeCell ref="O110:U110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="D111:N111"/>
-    <mergeCell ref="O111:U111"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="D108:N108"/>
-    <mergeCell ref="O108:U108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="D109:N109"/>
-    <mergeCell ref="O109:U109"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="D114:N114"/>
-    <mergeCell ref="O114:U114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="D115:N115"/>
-    <mergeCell ref="O115:U115"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="D112:N112"/>
-    <mergeCell ref="O112:U112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="D113:N113"/>
-    <mergeCell ref="O113:U113"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="D118:N118"/>
-    <mergeCell ref="O118:U118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="D119:N119"/>
-    <mergeCell ref="O119:U119"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="D116:N116"/>
-    <mergeCell ref="O116:U116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="D117:N117"/>
-    <mergeCell ref="O117:U117"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="D122:N122"/>
-    <mergeCell ref="O122:U122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="D123:N123"/>
-    <mergeCell ref="O123:U123"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="D120:N120"/>
-    <mergeCell ref="O120:U120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="D121:N121"/>
-    <mergeCell ref="O121:U121"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="D126:N126"/>
-    <mergeCell ref="O126:U126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="D127:N127"/>
-    <mergeCell ref="O127:U127"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="D124:N124"/>
-    <mergeCell ref="O124:U124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="D125:N125"/>
-    <mergeCell ref="O125:U125"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="D130:N130"/>
-    <mergeCell ref="O130:U130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="D131:N131"/>
-    <mergeCell ref="O131:U131"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="D128:N128"/>
-    <mergeCell ref="O128:U128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="D129:N129"/>
-    <mergeCell ref="O129:U129"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="D137:N137"/>
-    <mergeCell ref="O137:U137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="D138:N138"/>
-    <mergeCell ref="O138:U138"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="D132:N132"/>
-    <mergeCell ref="O132:U132"/>
-    <mergeCell ref="B134:U134"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="D136:N136"/>
-    <mergeCell ref="O136:U136"/>
-    <mergeCell ref="B135:U135"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="D141:N141"/>
-    <mergeCell ref="O141:U141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="D142:N142"/>
-    <mergeCell ref="O142:U142"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="D139:N139"/>
-    <mergeCell ref="O139:U139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="D140:N140"/>
-    <mergeCell ref="O140:U140"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="D145:N145"/>
-    <mergeCell ref="O145:U145"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="D146:N146"/>
-    <mergeCell ref="O146:U146"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="D143:N143"/>
-    <mergeCell ref="O143:U143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="D144:N144"/>
-    <mergeCell ref="O144:U144"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="D149:N149"/>
-    <mergeCell ref="O149:U149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="D150:N150"/>
-    <mergeCell ref="O150:U150"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="D147:N147"/>
-    <mergeCell ref="O147:U147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="D148:N148"/>
-    <mergeCell ref="O148:U148"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="D153:N153"/>
-    <mergeCell ref="O153:U153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="D154:N154"/>
-    <mergeCell ref="O154:U154"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="D151:N151"/>
-    <mergeCell ref="O151:U151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="D152:N152"/>
-    <mergeCell ref="O152:U152"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="D157:N157"/>
-    <mergeCell ref="O157:U157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="D158:N158"/>
-    <mergeCell ref="O158:U158"/>
-    <mergeCell ref="B155:C155"/>
-    <mergeCell ref="D155:N155"/>
-    <mergeCell ref="O155:U155"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="D156:N156"/>
-    <mergeCell ref="O156:U156"/>
-    <mergeCell ref="B161:C161"/>
-    <mergeCell ref="D161:N161"/>
-    <mergeCell ref="O161:U161"/>
-    <mergeCell ref="B162:C162"/>
-    <mergeCell ref="D162:N162"/>
-    <mergeCell ref="O162:U162"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="D159:N159"/>
-    <mergeCell ref="O159:U159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="D160:N160"/>
-    <mergeCell ref="O160:U160"/>
-    <mergeCell ref="B165:C165"/>
-    <mergeCell ref="D165:N165"/>
-    <mergeCell ref="O165:U165"/>
-    <mergeCell ref="B167:U167"/>
-    <mergeCell ref="B169:C169"/>
-    <mergeCell ref="D169:N169"/>
-    <mergeCell ref="O169:U169"/>
-    <mergeCell ref="B163:C163"/>
-    <mergeCell ref="D163:N163"/>
-    <mergeCell ref="O163:U163"/>
-    <mergeCell ref="B164:C164"/>
-    <mergeCell ref="D164:N164"/>
-    <mergeCell ref="O164:U164"/>
-    <mergeCell ref="B168:U168"/>
-    <mergeCell ref="B172:C172"/>
-    <mergeCell ref="D172:N172"/>
-    <mergeCell ref="O172:U172"/>
-    <mergeCell ref="B173:C173"/>
-    <mergeCell ref="D173:N173"/>
-    <mergeCell ref="O173:U173"/>
-    <mergeCell ref="B170:C170"/>
-    <mergeCell ref="D170:N170"/>
-    <mergeCell ref="O170:U170"/>
-    <mergeCell ref="B171:C171"/>
-    <mergeCell ref="D171:N171"/>
-    <mergeCell ref="O171:U171"/>
-    <mergeCell ref="B176:C176"/>
-    <mergeCell ref="D176:N176"/>
-    <mergeCell ref="O176:U176"/>
-    <mergeCell ref="B177:C177"/>
-    <mergeCell ref="D177:N177"/>
-    <mergeCell ref="O177:U177"/>
-    <mergeCell ref="B174:C174"/>
-    <mergeCell ref="D174:N174"/>
-    <mergeCell ref="O174:U174"/>
-    <mergeCell ref="B175:C175"/>
-    <mergeCell ref="D175:N175"/>
-    <mergeCell ref="O175:U175"/>
-    <mergeCell ref="B180:C180"/>
-    <mergeCell ref="D180:N180"/>
-    <mergeCell ref="O180:U180"/>
-    <mergeCell ref="B181:C181"/>
-    <mergeCell ref="D181:N181"/>
-    <mergeCell ref="O181:U181"/>
-    <mergeCell ref="B178:C178"/>
-    <mergeCell ref="D178:N178"/>
-    <mergeCell ref="O178:U178"/>
-    <mergeCell ref="B179:C179"/>
-    <mergeCell ref="D179:N179"/>
-    <mergeCell ref="O179:U179"/>
-    <mergeCell ref="O187:U187"/>
-    <mergeCell ref="B184:C184"/>
-    <mergeCell ref="D184:N184"/>
-    <mergeCell ref="O184:U184"/>
-    <mergeCell ref="B185:C185"/>
-    <mergeCell ref="D185:N185"/>
-    <mergeCell ref="O185:U185"/>
-    <mergeCell ref="B182:C182"/>
-    <mergeCell ref="D182:N182"/>
-    <mergeCell ref="O182:U182"/>
-    <mergeCell ref="B183:C183"/>
-    <mergeCell ref="D183:N183"/>
-    <mergeCell ref="O183:U183"/>
-    <mergeCell ref="B193:C193"/>
-    <mergeCell ref="D193:N193"/>
-    <mergeCell ref="O193:U193"/>
-    <mergeCell ref="B192:C192"/>
-    <mergeCell ref="D192:N192"/>
-    <mergeCell ref="O192:U192"/>
-    <mergeCell ref="V3:AI3"/>
-    <mergeCell ref="B190:C190"/>
-    <mergeCell ref="D190:N190"/>
-    <mergeCell ref="O190:U190"/>
-    <mergeCell ref="B191:C191"/>
-    <mergeCell ref="D191:N191"/>
-    <mergeCell ref="O191:U191"/>
-    <mergeCell ref="B188:C188"/>
-    <mergeCell ref="D188:N188"/>
-    <mergeCell ref="O188:U188"/>
-    <mergeCell ref="B189:C189"/>
-    <mergeCell ref="D189:N189"/>
-    <mergeCell ref="O189:U189"/>
-    <mergeCell ref="B186:C186"/>
-    <mergeCell ref="D186:N186"/>
-    <mergeCell ref="O186:U186"/>
-    <mergeCell ref="B187:C187"/>
-    <mergeCell ref="D187:N187"/>
   </mergeCells>
   <pageMargins left="0.39370078740157477" right="0.39370078740157477" top="0.39370078740157477" bottom="0.39370078740157477" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>
